--- a/electricidad/el_nino_mapping_data.xlsx
+++ b/electricidad/el_nino_mapping_data.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H919"/>
+  <dimension ref="A1:H921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -22782,6 +22782,50 @@
         <v>1.38</v>
       </c>
       <c r="H919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B920" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C920" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D920" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B921" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C921" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D921" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E921" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F921" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G921" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H921" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22880,7 +22924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F919"/>
+  <dimension ref="A1:F921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -22927,7 +22971,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-1.186362366577398</v>
+        <v>-1.182218860186178</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -22941,7 +22985,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-1.394561507211044</v>
+        <v>-1.388530929937931</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -22955,7 +22999,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-1.032476045239486</v>
+        <v>-1.029727330369665</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -22969,7 +23013,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-1.503187145802511</v>
+        <v>-1.496172009808411</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -22983,7 +23027,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>-1.358352961013888</v>
+        <v>-1.352650569981105</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -22997,7 +23041,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>-1.403613643760333</v>
+        <v>-1.397501019927138</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -23011,7 +23055,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>-1.276883732070288</v>
+        <v>-1.271919760078245</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -23025,7 +23069,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>-0.5798692177750389</v>
+        <v>-0.5812228309093332</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -23039,7 +23083,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>-0.8423811777044182</v>
+        <v>-0.8413554405963258</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -23053,7 +23097,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>-0.7065991294650842</v>
+        <v>-0.7068040907582263</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -23067,7 +23111,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>-1.412665780309622</v>
+        <v>-1.406471109916344</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -23081,7 +23125,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>-0.7699640853101068</v>
+        <v>-0.7695947206826728</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -23097,10 +23141,10 @@
         <v>106.0506069196872</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1996794827049032</v>
+        <v>-0.2044790513626542</v>
       </c>
       <c r="E14" t="n">
-        <v>1.835522945230836</v>
+        <v>1.835522945230835</v>
       </c>
       <c r="F14" t="inlineStr"/>
     </row>
@@ -23115,7 +23159,7 @@
         <v>-46.08235568105732</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6070256274229058</v>
+        <v>-0.6081331008769533</v>
       </c>
       <c r="E15" t="n">
         <v>-0.8279210493994854</v>
@@ -23133,7 +23177,7 @@
         <v>-35.65018140156577</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E16" t="n">
         <v>-0.6452813935310294</v>
@@ -23151,7 +23195,7 @@
         <v>-34.99005532067515</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.00958461516983538</v>
+        <v>-0.01610716158931459</v>
       </c>
       <c r="E17" t="n">
         <v>-0.6337243396500688</v>
@@ -23169,7 +23213,7 @@
         <v>16.54224203707306</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3706051199003003</v>
+        <v>0.3606366179573645</v>
       </c>
       <c r="E18" t="n">
         <v>0.2684692782261845</v>
@@ -23187,7 +23231,7 @@
         <v>262.9978865225167</v>
       </c>
       <c r="D19" t="n">
-        <v>1.565487144406441</v>
+        <v>1.544688496532642</v>
       </c>
       <c r="E19" t="n">
         <v>4.583252840091086</v>
@@ -23205,7 +23249,7 @@
         <v>-28.91537647643108</v>
       </c>
       <c r="D20" t="n">
-        <v>1.900416196730132</v>
+        <v>1.876581826133287</v>
       </c>
       <c r="E20" t="n">
         <v>-0.5273728520406995</v>
@@ -23223,7 +23267,7 @@
         <v>155.1144342809428</v>
       </c>
       <c r="D21" t="n">
-        <v>1.275818774829195</v>
+        <v>1.257645616878029</v>
       </c>
       <c r="E21" t="n">
         <v>2.694500211596617</v>
@@ -23241,7 +23285,7 @@
         <v>-5.376424644833812</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7236384453225692</v>
+        <v>0.7104701275364238</v>
       </c>
       <c r="E22" t="n">
         <v>-0.1152683427747153</v>
@@ -23259,7 +23303,7 @@
         <v>66.66230640435327</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8684726301111922</v>
+        <v>0.8539915673637301</v>
       </c>
       <c r="E23" t="n">
         <v>1.14593844840104</v>
@@ -23277,7 +23321,7 @@
         <v>9.785173456877578</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8322640839140365</v>
+        <v>0.8181112074069035</v>
       </c>
       <c r="E24" t="n">
         <v>0.1501709592848901</v>
@@ -23295,7 +23339,7 @@
         <v>38.34706188566006</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2348230716609661</v>
+        <v>0.2260852681192649</v>
       </c>
       <c r="E25" t="n">
         <v>0.6502137436391709</v>
@@ -23313,7 +23357,7 @@
         <v>14.11273115971728</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02662393102732041</v>
+        <v>0.01977319836751201</v>
       </c>
       <c r="E26" t="n">
         <v>0.2259349973868352</v>
@@ -23331,7 +23375,7 @@
         <v>-35.56410293732351</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1443017061680767</v>
+        <v>0.1363843682271984</v>
       </c>
       <c r="E27" t="n">
         <v>-0.6437743883118204</v>
@@ -23349,7 +23393,7 @@
         <v>-51.2172999809051</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1544187999584585</v>
+        <v>-0.1596286014166209</v>
       </c>
       <c r="E28" t="n">
         <v>-0.9178202817840115</v>
@@ -23367,7 +23411,7 @@
         <v>-24.26827810322902</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7790162218593958</v>
+        <v>-0.7785648106718794</v>
       </c>
       <c r="E29" t="n">
         <v>-0.4460145057430327</v>
@@ -23385,7 +23429,7 @@
         <v>-61.23935907601621</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6251299005214837</v>
+        <v>-0.6260732808553665</v>
       </c>
       <c r="E30" t="n">
         <v>-1.09327991035088</v>
@@ -23403,7 +23447,7 @@
         <v>3.722971874491951</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E31" t="n">
         <v>0.04403791538159332</v>
@@ -23421,7 +23465,7 @@
         <v>30.59532292543887</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.896693997000152</v>
+        <v>-0.8951759805315658</v>
       </c>
       <c r="E32" t="n">
         <v>0.5145013889423987</v>
@@ -23439,7 +23483,7 @@
         <v>-66.4383041712529</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7880683584086847</v>
+        <v>-0.7875349006610861</v>
       </c>
       <c r="E33" t="n">
         <v>-1.184299626628022</v>
@@ -23457,7 +23501,7 @@
         <v>-6.247366104456786</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.014371772140908</v>
+        <v>-1.011787150391252</v>
       </c>
       <c r="E34" t="n">
         <v>-0.1305162138517755</v>
@@ -23475,7 +23519,7 @@
         <v>-21.96656550858099</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3716700771413932</v>
+        <v>-0.3749107611575804</v>
       </c>
       <c r="E35" t="n">
         <v>-0.4057176333047497</v>
@@ -23493,7 +23537,7 @@
         <v>-23.52002562886204</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5255563984793051</v>
+        <v>-0.5274022909740934</v>
       </c>
       <c r="E36" t="n">
         <v>-0.432914592842827</v>
@@ -23511,7 +23555,7 @@
         <v>-36.58764911482552</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.235888028902059</v>
+        <v>-0.2403594113194807</v>
       </c>
       <c r="E37" t="n">
         <v>-0.6616939625650941</v>
@@ -23529,7 +23573,7 @@
         <v>30.40640170351564</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1815752096063253</v>
+        <v>-0.1865388713842409</v>
       </c>
       <c r="E38" t="n">
         <v>0.5111938802645444</v>
@@ -23547,7 +23591,7 @@
         <v>43.96960787167768</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3706051199003003</v>
+        <v>0.3606366179573645</v>
       </c>
       <c r="E39" t="n">
         <v>0.7486495861087118</v>
@@ -23565,7 +23609,7 @@
         <v>34.87206415886958</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8865769032097701</v>
+        <v>0.8719317473421433</v>
       </c>
       <c r="E40" t="n">
         <v>0.5893757656720684</v>
@@ -23583,7 +23627,7 @@
         <v>67.67924876914215</v>
       </c>
       <c r="D41" t="n">
-        <v>1.547382871307863</v>
+        <v>1.526748316554228</v>
       </c>
       <c r="E41" t="n">
         <v>1.163742407438441</v>
@@ -23601,7 +23645,7 @@
         <v>76.37976690953158</v>
       </c>
       <c r="D42" t="n">
-        <v>1.130984590040572</v>
+        <v>1.114124177050723</v>
       </c>
       <c r="E42" t="n">
         <v>1.316065364903012</v>
@@ -23619,10 +23663,10 @@
         <v>-1.723297024873996</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4973350315903455</v>
+        <v>0.4862178778062575</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.05131178362628711</v>
+        <v>-0.05131178362628712</v>
       </c>
       <c r="F43" t="inlineStr"/>
     </row>
@@ -23637,7 +23681,7 @@
         <v>232.12411738032</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2167187985623882</v>
+        <v>0.2081450881408516</v>
       </c>
       <c r="E44" t="n">
         <v>4.04273516655316</v>
@@ -23655,7 +23699,7 @@
         <v>-78.28025961210004</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3706051199003003</v>
+        <v>0.3606366179573645</v>
       </c>
       <c r="E45" t="n">
         <v>-1.391620805184035</v>
@@ -23673,10 +23717,10 @@
         <v>82.08295483278863</v>
       </c>
       <c r="D46" t="n">
-        <v>0.5154393046889234</v>
+        <v>0.5041580577846708</v>
       </c>
       <c r="E46" t="n">
-        <v>1.415913033447481</v>
+        <v>1.41591303344748</v>
       </c>
       <c r="F46" t="inlineStr"/>
     </row>
@@ -23691,7 +23735,7 @@
         <v>42.37128505650901</v>
       </c>
       <c r="D47" t="n">
-        <v>0.05378034067518724</v>
+        <v>0.04668346833513194</v>
       </c>
       <c r="E47" t="n">
         <v>0.7206671999724887</v>
@@ -23709,7 +23753,7 @@
         <v>55.30720750137076</v>
       </c>
       <c r="D48" t="n">
-        <v>0.08998888687234299</v>
+        <v>0.0825638282919585</v>
       </c>
       <c r="E48" t="n">
         <v>0.9471408343628966</v>
@@ -23727,7 +23771,7 @@
         <v>-55.61660374717299</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3173572578456595</v>
+        <v>-0.3210902212223405</v>
       </c>
       <c r="E49" t="n">
         <v>-0.9948404028446358</v>
@@ -23745,7 +23789,7 @@
         <v>-13.20816098898545</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.5122392823518</v>
+        <v>-1.505142099797617</v>
       </c>
       <c r="E50" t="n">
         <v>-0.2523812391303971</v>
@@ -23763,7 +23807,7 @@
         <v>-39.04107595120957</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.887641860450863</v>
+        <v>-0.8862058905423591</v>
       </c>
       <c r="E51" t="n">
         <v>-0.7046469483081061</v>
@@ -23781,7 +23825,7 @@
         <v>-24.07389726942905</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9781632259437524</v>
+        <v>-0.9759067904344256</v>
       </c>
       <c r="E52" t="n">
         <v>-0.4426114137660857</v>
@@ -23799,7 +23843,7 @@
         <v>-50.3907226466976</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.580391395167896</v>
+        <v>-2.563612718524002</v>
       </c>
       <c r="E53" t="n">
         <v>-0.9033491086782185</v>
@@ -23817,7 +23861,7 @@
         <v>-58.13348094732275</v>
       </c>
       <c r="D54" t="n">
-        <v>-2.489870029675007</v>
+        <v>-2.473911818631935</v>
       </c>
       <c r="E54" t="n">
         <v>-1.038904235884906</v>
@@ -23835,7 +23879,7 @@
         <v>-17.57437814989432</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.010106792562692</v>
+        <v>-1.998497049203983</v>
       </c>
       <c r="E55" t="n">
         <v>-0.3288221016342978</v>
@@ -23853,7 +23897,7 @@
         <v>-48.75947399106044</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.345035844886383</v>
+        <v>-2.330390378804629</v>
       </c>
       <c r="E56" t="n">
         <v>-0.8747902785513917</v>
@@ -23871,7 +23915,7 @@
         <v>13.8649561619919</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.313092278267443</v>
+        <v>-1.307800120035071</v>
       </c>
       <c r="E57" t="n">
         <v>0.2215971154549416</v>
@@ -23889,7 +23933,7 @@
         <v>-40.97264494619829</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.331196551366021</v>
+        <v>-1.325740300013485</v>
       </c>
       <c r="E58" t="n">
         <v>-0.7384635896984293</v>
@@ -23907,7 +23951,7 @@
         <v>106.3755755546254</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.629917057492557</v>
+        <v>-1.621753269657304</v>
       </c>
       <c r="E59" t="n">
         <v>1.841212282665491</v>
@@ -23925,7 +23969,7 @@
         <v>-6.479296684882057</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.095841001084509</v>
+        <v>-1.092517960294112</v>
       </c>
       <c r="E60" t="n">
         <v>-0.1345767021315311</v>
@@ -23943,7 +23987,7 @@
         <v>-7.269935564022584</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.113945274183086</v>
+        <v>-1.110458140272525</v>
       </c>
       <c r="E61" t="n">
         <v>-0.1484186883688896</v>
@@ -23961,7 +24005,7 @@
         <v>63.80494070227773</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5436606715778831</v>
+        <v>-0.5453424709525067</v>
       </c>
       <c r="E62" t="n">
         <v>1.095913566287698</v>
@@ -23979,7 +24023,7 @@
         <v>-14.45663881691945</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8061726315072624</v>
+        <v>-0.8054750806394992</v>
       </c>
       <c r="E63" t="n">
         <v>-0.2742387689937092</v>
@@ -23997,7 +24041,7 @@
         <v>-1.981096047355345</v>
       </c>
       <c r="D64" t="n">
-        <v>-1.023423908690197</v>
+        <v>-1.020757240380459</v>
       </c>
       <c r="E64" t="n">
         <v>-0.05582515960024684</v>
@@ -24015,7 +24059,7 @@
         <v>-9.123020574074282</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9057461335494408</v>
+        <v>-0.9041460705207724</v>
       </c>
       <c r="E65" t="n">
         <v>-0.1808612836959427</v>
@@ -24033,7 +24077,7 @@
         <v>-28.07109408895738</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.738542696084024</v>
+        <v>-1.729394349527784</v>
       </c>
       <c r="E66" t="n">
         <v>-0.5125917104902622</v>
@@ -24051,7 +24095,7 @@
         <v>-26.32092342708502</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.521291418901089</v>
+        <v>-1.514112189786824</v>
       </c>
       <c r="E67" t="n">
         <v>-0.4819508719812822</v>
@@ -24069,7 +24113,7 @@
         <v>47.80505711386064</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.08678886453522</v>
+        <v>-1.083547870304905</v>
       </c>
       <c r="E68" t="n">
         <v>0.815798112477787</v>
@@ -24087,7 +24131,7 @@
         <v>-42.61206209435608</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.186362366577398</v>
+        <v>-1.182218860186178</v>
       </c>
       <c r="E69" t="n">
         <v>-0.7671654284275823</v>
@@ -24105,7 +24149,7 @@
         <v>-8.073533681085582</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.113945274183086</v>
+        <v>-1.110458140272525</v>
       </c>
       <c r="E70" t="n">
         <v>-0.1624875564327079</v>
@@ -24123,7 +24167,7 @@
         <v>-25.61610506488072</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.4307700534082</v>
+        <v>-1.424411289894758</v>
       </c>
       <c r="E71" t="n">
         <v>-0.4696113749911076</v>
@@ -24141,7 +24185,7 @@
         <v>-54.64430712741118</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.439822189957489</v>
+        <v>-1.433381379883965</v>
       </c>
       <c r="E72" t="n">
         <v>-0.977818072189706</v>
@@ -24159,7 +24203,7 @@
         <v>-27.16503571756656</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.313092278267443</v>
+        <v>-1.307800120035071</v>
       </c>
       <c r="E73" t="n">
         <v>-0.4967290355852933</v>
@@ -24177,7 +24221,7 @@
         <v>26.47082433762735</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9691110893944637</v>
+        <v>-0.966936700445219</v>
       </c>
       <c r="E74" t="n">
         <v>0.442292376465611</v>
@@ -24195,7 +24239,7 @@
         <v>-30.56424849349364</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E75" t="n">
         <v>-0.5562402204050737</v>
@@ -24213,7 +24257,7 @@
         <v>-12.93679587550124</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E76" t="n">
         <v>-0.247630356944802</v>
@@ -24231,7 +24275,7 @@
         <v>-1.678096707930743</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.8242769046058404</v>
+        <v>-0.8234152606179125</v>
       </c>
       <c r="E77" t="n">
         <v>-0.05052044616292723</v>
@@ -24249,7 +24293,7 @@
         <v>-51.40108615969241</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.8785897239015741</v>
+        <v>-0.8772358005531524</v>
       </c>
       <c r="E78" t="n">
         <v>-0.9210378894991244</v>
@@ -24267,7 +24311,7 @@
         <v>17.00536498130386</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.6341820370707725</v>
+        <v>-0.635043370844573</v>
       </c>
       <c r="E79" t="n">
         <v>0.276577330573947</v>
@@ -24285,7 +24329,7 @@
         <v>108.3522273325991</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08998888687234299</v>
+        <v>0.0825638282919585</v>
       </c>
       <c r="E80" t="n">
         <v>1.875818203811824</v>
@@ -24303,7 +24347,7 @@
         <v>-57.44297263445554</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.1725230730570364</v>
+        <v>-0.1775687813950342</v>
       </c>
       <c r="E81" t="n">
         <v>-1.026815269840282</v>
@@ -24321,7 +24365,7 @@
         <v>8.980061996047992</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.6975469929157951</v>
+        <v>-0.6978340007690196</v>
       </c>
       <c r="E82" t="n">
         <v>0.1360755965923074</v>
@@ -24339,7 +24383,7 @@
         <v>22.18109041439933</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.8604854508029961</v>
+        <v>-0.8592956205747392</v>
       </c>
       <c r="E83" t="n">
         <v>0.3671905322560268</v>
@@ -24357,7 +24401,7 @@
         <v>-61.61215399496047</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.7428076756622399</v>
+        <v>-0.7426844507150528</v>
       </c>
       <c r="E84" t="n">
         <v>-1.099806558955605</v>
@@ -24375,7 +24419,7 @@
         <v>-51.67957865082524</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.9781632259437524</v>
+        <v>-0.9759067904344256</v>
       </c>
       <c r="E85" t="n">
         <v>-0.9259135531316273</v>
@@ -24393,7 +24437,7 @@
         <v>-18.98794610603877</v>
       </c>
       <c r="D86" t="n">
-        <v>-1.285935868619576</v>
+        <v>-1.280889850067451</v>
       </c>
       <c r="E86" t="n">
         <v>-0.3535699210380092</v>
@@ -24411,7 +24455,7 @@
         <v>16.20840732438649</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2800837544074108</v>
+        <v>0.2709357180652981</v>
       </c>
       <c r="E87" t="n">
         <v>0.2626247193251811</v>
@@ -24429,7 +24473,7 @@
         <v>5.360893641397755</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9227854494069261</v>
+        <v>0.90781210729897</v>
       </c>
       <c r="E88" t="n">
         <v>0.07271357395789058</v>
@@ -24447,7 +24491,7 @@
         <v>63.27207121042506</v>
       </c>
       <c r="D89" t="n">
-        <v>1.239610228632039</v>
+        <v>1.221765256921202</v>
       </c>
       <c r="E89" t="n">
         <v>1.086584437190794</v>
@@ -24465,7 +24509,7 @@
         <v>40.59035621848865</v>
       </c>
       <c r="D90" t="n">
-        <v>2.389231570391735</v>
+        <v>2.360966685550447</v>
       </c>
       <c r="E90" t="n">
         <v>0.6894878675161965</v>
@@ -24483,7 +24527,7 @@
         <v>102.0321898878231</v>
       </c>
       <c r="D91" t="n">
-        <v>2.036198244969466</v>
+        <v>2.011133175971387</v>
       </c>
       <c r="E91" t="n">
         <v>1.765171138965635</v>
@@ -24501,7 +24545,7 @@
         <v>183.4315821295156</v>
       </c>
       <c r="D92" t="n">
-        <v>1.900416196730132</v>
+        <v>1.876581826133287</v>
       </c>
       <c r="E92" t="n">
         <v>3.190258238607989</v>
@@ -24519,7 +24563,7 @@
         <v>-55.0233423160132</v>
       </c>
       <c r="D93" t="n">
-        <v>1.302975184477062</v>
+        <v>1.284555886845649</v>
       </c>
       <c r="E93" t="n">
         <v>-0.98445397133725</v>
@@ -24537,7 +24581,7 @@
         <v>-25.35188844457347</v>
       </c>
       <c r="D94" t="n">
-        <v>1.040463224547682</v>
+        <v>1.024423277158656</v>
       </c>
       <c r="E94" t="n">
         <v>-0.4649856439292225</v>
@@ -24555,7 +24599,7 @@
         <v>-16.57074089577229</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7870034011675917</v>
+        <v>0.7732607574608702</v>
       </c>
       <c r="E95" t="n">
         <v>-0.3112510797362104</v>
@@ -24573,7 +24617,7 @@
         <v>-27.84489609837541</v>
       </c>
       <c r="D96" t="n">
-        <v>0.7236384453225692</v>
+        <v>0.7104701275364238</v>
       </c>
       <c r="E96" t="n">
         <v>-0.5086315846285573</v>
@@ -24591,7 +24635,7 @@
         <v>-34.9078517403838</v>
       </c>
       <c r="D97" t="n">
-        <v>0.8141598108154586</v>
+        <v>0.8001710274284901</v>
       </c>
       <c r="E97" t="n">
         <v>-0.6322851733542102</v>
@@ -24609,7 +24653,7 @@
         <v>72.58235560043434</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3434487102524335</v>
+        <v>0.3337263479897446</v>
       </c>
       <c r="E98" t="n">
         <v>1.249582781684674</v>
@@ -24627,7 +24671,7 @@
         <v>51.53488981397922</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4520743488439008</v>
+        <v>0.4413674278602243</v>
       </c>
       <c r="E99" t="n">
         <v>0.881097573792938</v>
@@ -24645,7 +24689,7 @@
         <v>55.38476226847433</v>
       </c>
       <c r="D100" t="n">
-        <v>0.6512213529282576</v>
+        <v>0.6387094076227705</v>
       </c>
       <c r="E100" t="n">
         <v>0.9484986122906102</v>
@@ -24663,7 +24707,7 @@
         <v>12.99438098446892</v>
       </c>
       <c r="D101" t="n">
-        <v>0.8594204935619033</v>
+        <v>0.8450214773745234</v>
       </c>
       <c r="E101" t="n">
         <v>0.2063556570043293</v>
@@ -24681,7 +24725,7 @@
         <v>69.29728759294443</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3253444371538556</v>
+        <v>0.3157861680113313</v>
       </c>
       <c r="E102" t="n">
         <v>1.192069968505169</v>
@@ -24699,7 +24743,7 @@
         <v>-42.15574703300277</v>
       </c>
       <c r="D103" t="n">
-        <v>0.1986145254638104</v>
+        <v>0.1902049081624383</v>
       </c>
       <c r="E103" t="n">
         <v>-0.7591765640221054</v>
@@ -24717,7 +24761,7 @@
         <v>-83.09256979983158</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2710316178581219</v>
+        <v>0.2619656280760914</v>
       </c>
       <c r="E104" t="n">
         <v>-1.475871571426256</v>
@@ -24735,7 +24779,7 @@
         <v>22.88875393782976</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.1634709365077474</v>
+        <v>-0.1685986914058275</v>
       </c>
       <c r="E105" t="n">
         <v>0.3795798404603651</v>
@@ -24753,7 +24797,7 @@
         <v>-54.17724126951424</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.1544187999584585</v>
+        <v>-0.1596286014166209</v>
       </c>
       <c r="E106" t="n">
         <v>-0.9696409898990179</v>
@@ -24771,7 +24815,7 @@
         <v>-27.67632900795312</v>
       </c>
       <c r="D107" t="n">
-        <v>0.04472820412589829</v>
+        <v>0.03771337834592529</v>
       </c>
       <c r="E107" t="n">
         <v>-0.505680422717277</v>
@@ -24789,7 +24833,7 @@
         <v>-72.07316547250134</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E108" t="n">
         <v>-1.282951077548439</v>
@@ -24807,7 +24851,7 @@
         <v>-53.34625260827912</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.235888028902059</v>
+        <v>-0.2403594113194807</v>
       </c>
       <c r="E109" t="n">
         <v>-0.9550925861768009</v>
@@ -24825,7 +24869,7 @@
         <v>-27.80338590628128</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.5798692177750389</v>
+        <v>-0.5812228309093332</v>
       </c>
       <c r="E110" t="n">
         <v>-0.5079048514475358</v>
@@ -24843,7 +24887,7 @@
         <v>-33.44626066198946</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.2087316192541921</v>
+        <v>-0.2134491413518607</v>
       </c>
       <c r="E111" t="n">
         <v>-0.6066965966657311</v>
@@ -24861,7 +24905,7 @@
         <v>44.59614282986442</v>
       </c>
       <c r="D112" t="n">
-        <v>0.5244914412382123</v>
+        <v>0.5131281477738775</v>
       </c>
       <c r="E112" t="n">
         <v>0.759618548674621</v>
@@ -24879,7 +24923,7 @@
         <v>-14.14970274647046</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3253444371538556</v>
+        <v>0.3157861680113313</v>
       </c>
       <c r="E113" t="n">
         <v>-0.2688651338550954</v>
@@ -24897,7 +24941,7 @@
         <v>21.56909681183705</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.1363145268598806</v>
+        <v>-0.1416884214382076</v>
       </c>
       <c r="E114" t="n">
         <v>0.3564761501942348</v>
@@ -24915,7 +24959,7 @@
         <v>8.681515200780355</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.3535658040428153</v>
+        <v>-0.3569705811791671</v>
       </c>
       <c r="E115" t="n">
         <v>0.1308488353738427</v>
@@ -24933,10 +24977,10 @@
         <v>-2.91723348664464</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.2992529847470816</v>
+        <v>-0.3031500412439272</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.07221443907130526</v>
+        <v>-0.07221443907130527</v>
       </c>
       <c r="F116" t="inlineStr"/>
     </row>
@@ -24951,7 +24995,7 @@
         <v>83.60724181121194</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.6975469929157951</v>
+        <v>-0.6978340007690196</v>
       </c>
       <c r="E117" t="n">
         <v>1.442599248777615</v>
@@ -24969,7 +25013,7 @@
         <v>-61.03239340332082</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.3354615309442374</v>
+        <v>-0.3390304012007538</v>
       </c>
       <c r="E118" t="n">
         <v>-1.089656491279749</v>
@@ -24987,7 +25031,7 @@
         <v>-8.663405190456263</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.04579316136699114</v>
+        <v>-0.05198752154614115</v>
       </c>
       <c r="E119" t="n">
         <v>-0.1728146394157693</v>
@@ -25005,7 +25049,7 @@
         <v>-2.228355625103974</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3072401640552777</v>
+        <v>0.297845988032918</v>
       </c>
       <c r="E120" t="n">
         <v>-0.06015401789769378</v>
@@ -25023,7 +25067,7 @@
         <v>29.79059400959762</v>
       </c>
       <c r="D121" t="n">
-        <v>0.008519657928742501</v>
+        <v>0.001833018389098698</v>
       </c>
       <c r="E121" t="n">
         <v>0.5004127235962322</v>
@@ -25041,7 +25085,7 @@
         <v>-9.747894899170625</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.08200170756414694</v>
+        <v>-0.08786788150296776</v>
       </c>
       <c r="E122" t="n">
         <v>-0.1918011729883398</v>
@@ -25059,7 +25103,7 @@
         <v>-27.32744316031557</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.1634709365077474</v>
+        <v>-0.1685986914058275</v>
       </c>
       <c r="E123" t="n">
         <v>-0.4995723584305095</v>
@@ -25077,7 +25121,7 @@
         <v>-13.71968684361275</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.00958461516983538</v>
+        <v>-0.01610716158931459</v>
       </c>
       <c r="E124" t="n">
         <v>-0.2613366978443692</v>
@@ -25095,7 +25139,7 @@
         <v>-28.11029355823888</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.7880683584086847</v>
+        <v>-0.7875349006610861</v>
       </c>
       <c r="E125" t="n">
         <v>-0.5132779890538666</v>
@@ -25113,7 +25157,7 @@
         <v>-38.03503837465029</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.7699640853101068</v>
+        <v>-0.7695947206826728</v>
       </c>
       <c r="E126" t="n">
         <v>-0.687033903141219</v>
@@ -25131,7 +25175,7 @@
         <v>-57.51910258494554</v>
       </c>
       <c r="D127" t="n">
-        <v>-1.059632454887353</v>
+        <v>-1.056637600337285</v>
       </c>
       <c r="E127" t="n">
         <v>-1.028148103014485</v>
@@ -25149,7 +25193,7 @@
         <v>60.52341776251863</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.9781632259437524</v>
+        <v>-0.9759067904344256</v>
       </c>
       <c r="E128" t="n">
         <v>1.038462817825772</v>
@@ -25167,7 +25211,7 @@
         <v>19.84286636049648</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.7065991294650842</v>
+        <v>-0.7068040907582263</v>
       </c>
       <c r="E129" t="n">
         <v>0.3262544411683136</v>
@@ -25185,7 +25229,7 @@
         <v>-60.69525477378933</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.02768888826841329</v>
+        <v>-0.03404734156772789</v>
       </c>
       <c r="E130" t="n">
         <v>-1.0837540895725</v>
@@ -25203,7 +25247,7 @@
         <v>-56.0289347007116</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.6070256274229058</v>
+        <v>-0.6081331008769533</v>
       </c>
       <c r="E131" t="n">
         <v>-1.00205922237742</v>
@@ -25221,7 +25265,7 @@
         <v>-39.32243695977625</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.3264093943949484</v>
+        <v>-0.3300603112115472</v>
       </c>
       <c r="E132" t="n">
         <v>-0.7095728320599183</v>
@@ -25239,7 +25283,7 @@
         <v>-48.05751556218531</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.04579316136699114</v>
+        <v>-0.05198752154614115</v>
       </c>
       <c r="E133" t="n">
         <v>-0.8625008513956594</v>
@@ -25257,7 +25301,7 @@
         <v>-4.39905867242391</v>
       </c>
       <c r="D134" t="n">
-        <v>0.1443017061680767</v>
+        <v>0.1363843682271984</v>
       </c>
       <c r="E134" t="n">
         <v>-0.09815726122296196</v>
@@ -25275,7 +25319,7 @@
         <v>-27.54577741550463</v>
       </c>
       <c r="D135" t="n">
-        <v>0.6240649432803909</v>
+        <v>0.6117991376551506</v>
       </c>
       <c r="E135" t="n">
         <v>-0.5033948111775287</v>
@@ -25293,7 +25337,7 @@
         <v>-36.01775825854497</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.4440871695357047</v>
+        <v>-0.4466714810712336</v>
       </c>
       <c r="E136" t="n">
         <v>-0.6517166877338751</v>
@@ -25311,7 +25355,7 @@
         <v>4.065906596093861</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E137" t="n">
         <v>0.05004179126218014</v>
@@ -25329,7 +25373,7 @@
         <v>-59.15680495504256</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.6160777639721947</v>
+        <v>-0.6171031908661599</v>
       </c>
       <c r="E138" t="n">
         <v>-1.056819920535545</v>
@@ -25347,10 +25391,10 @@
         <v>-1.788327101284346</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.6703905832679283</v>
+        <v>-0.6709237308013997</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.0524502874950381</v>
+        <v>-0.05245028749503811</v>
       </c>
       <c r="F139" t="inlineStr"/>
     </row>
@@ -25365,7 +25409,7 @@
         <v>-38.437952106411</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.16825809347882</v>
+        <v>-1.164278680207765</v>
       </c>
       <c r="E140" t="n">
         <v>-0.6940878521399543</v>
@@ -25383,7 +25427,7 @@
         <v>-60.37499525562681</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.8152247680565514</v>
+        <v>-0.8144451706287059</v>
       </c>
       <c r="E141" t="n">
         <v>-1.078147196261602</v>
@@ -25401,7 +25445,7 @@
         <v>-7.230687107256893</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.8152247680565514</v>
+        <v>-0.8144451706287059</v>
       </c>
       <c r="E142" t="n">
         <v>-0.147731552164585</v>
@@ -25419,7 +25463,7 @@
         <v>44.21567601506906</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.733755539112951</v>
+        <v>-0.7337143607258462</v>
       </c>
       <c r="E143" t="n">
         <v>0.7529575855559164</v>
@@ -25437,7 +25481,7 @@
         <v>-46.17938971272264</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.3897743502399711</v>
+        <v>-0.3928509411359937</v>
       </c>
       <c r="E144" t="n">
         <v>-0.8296198574979776</v>
@@ -25455,7 +25499,7 @@
         <v>-16.86315338212327</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.5798692177750389</v>
+        <v>-0.5812228309093332</v>
       </c>
       <c r="E145" t="n">
         <v>-0.3163704455029205</v>
@@ -25473,7 +25517,7 @@
         <v>7.984384440210072</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.4531393060849936</v>
+        <v>-0.4556415710604401</v>
       </c>
       <c r="E146" t="n">
         <v>0.1186439278641805</v>
@@ -25491,7 +25535,7 @@
         <v>-29.93653750982504</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.4440871695357047</v>
+        <v>-0.4466714810712336</v>
       </c>
       <c r="E147" t="n">
         <v>-0.5452506687573925</v>
@@ -25509,7 +25553,7 @@
         <v>-17.48615619629559</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.711386286436157</v>
+        <v>-1.702484079560164</v>
       </c>
       <c r="E148" t="n">
         <v>-0.3272775696111901</v>
@@ -25527,7 +25571,7 @@
         <v>-26.21373996022128</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.937689700168381</v>
+        <v>-1.92673632929033</v>
       </c>
       <c r="E149" t="n">
         <v>-0.4800743742370616</v>
@@ -25545,7 +25589,7 @@
         <v>-16.95815442617555</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.150153820380242</v>
+        <v>-1.146338500229352</v>
       </c>
       <c r="E150" t="n">
         <v>-0.3180336613894652</v>
@@ -25563,7 +25607,7 @@
         <v>-11.80295886847667</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.005319635591619</v>
+        <v>-1.002817060402046</v>
       </c>
       <c r="E151" t="n">
         <v>-0.2277798832826632</v>
@@ -25581,7 +25625,7 @@
         <v>-46.85927749346808</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.9781632259437524</v>
+        <v>-0.9759067904344256</v>
       </c>
       <c r="E152" t="n">
         <v>-0.8415228862413363</v>
@@ -25599,7 +25643,7 @@
         <v>-53.05917182221884</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.4802957157328605</v>
+        <v>-0.4825518410280601</v>
       </c>
       <c r="E153" t="n">
         <v>-0.9500665643171421</v>
@@ -25617,7 +25661,7 @@
         <v>-38.0507768235922</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.4531393060849936</v>
+        <v>-0.4556415710604401</v>
       </c>
       <c r="E154" t="n">
         <v>-0.6873094415689373</v>
@@ -25635,7 +25679,7 @@
         <v>-51.83000209292591</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.8423811777044182</v>
+        <v>-0.8413554405963258</v>
       </c>
       <c r="E155" t="n">
         <v>-0.928547067964084</v>
@@ -25653,7 +25697,7 @@
         <v>-40.43137810580532</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.5708170812257499</v>
+        <v>-0.5722527409201267</v>
       </c>
       <c r="E156" t="n">
         <v>-0.7289874453383107</v>
@@ -25671,7 +25715,7 @@
         <v>-61.28591988591376</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.7699640853101068</v>
+        <v>-0.7695947206826728</v>
       </c>
       <c r="E157" t="n">
         <v>-1.094095066431368</v>
@@ -25689,7 +25733,7 @@
         <v>8.351958493706892</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.5527128081271721</v>
+        <v>-0.5543125609417133</v>
       </c>
       <c r="E158" t="n">
         <v>0.1250791729854981</v>
@@ -25707,7 +25751,7 @@
         <v>5.073360309743532</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.5255563984793051</v>
+        <v>-0.5274022909740934</v>
       </c>
       <c r="E159" t="n">
         <v>0.06767962922718603</v>
@@ -25725,7 +25769,7 @@
         <v>21.4817643689135</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.4712435791835716</v>
+        <v>-0.4735817510388535</v>
       </c>
       <c r="E160" t="n">
         <v>0.3549471911398346</v>
@@ -25743,7 +25787,7 @@
         <v>-51.46670434414025</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.8785897239015741</v>
+        <v>-0.8772358005531524</v>
       </c>
       <c r="E161" t="n">
         <v>-0.9221866895771508</v>
@@ -25761,7 +25805,7 @@
         <v>-46.76919854580273</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.2992529847470816</v>
+        <v>-0.3031500412439272</v>
       </c>
       <c r="E162" t="n">
         <v>-0.8399458431857065</v>
@@ -25779,7 +25823,7 @@
         <v>-29.97886522516664</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.5708170812257499</v>
+        <v>-0.5722527409201267</v>
       </c>
       <c r="E163" t="n">
         <v>-0.5459917145985155</v>
@@ -25797,7 +25841,7 @@
         <v>-35.73880935414912</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.09105384411343591</v>
+        <v>-0.09683797149217441</v>
       </c>
       <c r="E164" t="n">
         <v>-0.6468330335177166</v>
@@ -25815,7 +25859,7 @@
         <v>-78.76418567578851</v>
       </c>
       <c r="D165" t="n">
-        <v>0.3525008468017224</v>
+        <v>0.3426964379789512</v>
       </c>
       <c r="E165" t="n">
         <v>-1.400093064884641</v>
@@ -25833,7 +25877,7 @@
         <v>-52.40726346447401</v>
       </c>
       <c r="D166" t="n">
-        <v>0.261979481308833</v>
+        <v>0.2529955380868847</v>
       </c>
       <c r="E166" t="n">
         <v>-0.9386533809359601</v>
@@ -25851,7 +25895,7 @@
         <v>-19.90634156550858</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1714581158159435</v>
+        <v>0.1632946381948183</v>
       </c>
       <c r="E167" t="n">
         <v>-0.3696485855785802</v>
@@ -25869,7 +25913,7 @@
         <v>-47.89824848906769</v>
       </c>
       <c r="D168" t="n">
-        <v>0.01757179447803145</v>
+        <v>0.01080310837830535</v>
       </c>
       <c r="E168" t="n">
         <v>-0.8597125080794857</v>
@@ -25887,7 +25931,7 @@
         <v>15.05299673226919</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.04579316136699114</v>
+        <v>-0.05198752154614115</v>
       </c>
       <c r="E169" t="n">
         <v>0.2423965495038697</v>
@@ -25905,7 +25949,7 @@
         <v>-15.29953060370868</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.3716700771413932</v>
+        <v>-0.3749107611575804</v>
       </c>
       <c r="E170" t="n">
         <v>-0.2889955648206513</v>
@@ -25923,7 +25967,7 @@
         <v>-46.51902419143547</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.9510068162958858</v>
+        <v>-0.9489965204668057</v>
       </c>
       <c r="E171" t="n">
         <v>-0.8355659548935243</v>
@@ -25941,7 +25985,7 @@
         <v>-19.74890204315446</v>
       </c>
       <c r="D172" t="n">
-        <v>-1.050580318338064</v>
+        <v>-1.047667510348079</v>
       </c>
       <c r="E172" t="n">
         <v>-0.366892237820915</v>
@@ -25959,7 +26003,7 @@
         <v>3.973524329141721</v>
       </c>
       <c r="D173" t="n">
-        <v>-1.005319635591619</v>
+        <v>-1.002817060402046</v>
       </c>
       <c r="E173" t="n">
         <v>0.04842442320520123</v>
@@ -25977,7 +26021,7 @@
         <v>-58.438682844362</v>
       </c>
       <c r="D174" t="n">
-        <v>-2.20020166009776</v>
+        <v>-2.186868938977323</v>
       </c>
       <c r="E174" t="n">
         <v>-1.044247510254395</v>
@@ -25995,7 +26039,7 @@
         <v>41.45667371159163</v>
       </c>
       <c r="D175" t="n">
-        <v>-1.485082872703933</v>
+        <v>-1.478231829829998</v>
       </c>
       <c r="E175" t="n">
         <v>0.704654785224253</v>
@@ -26013,7 +26057,7 @@
         <v>-0.1749044503465765</v>
       </c>
       <c r="D176" t="n">
-        <v>-1.385509370661755</v>
+        <v>-1.379560839948725</v>
       </c>
       <c r="E176" t="n">
         <v>-0.02420354335111182</v>
@@ -26031,7 +26075,7 @@
         <v>27.78494705279541</v>
       </c>
       <c r="D177" t="n">
-        <v>-1.294988005168866</v>
+        <v>-1.289859940056658</v>
       </c>
       <c r="E177" t="n">
         <v>0.4652991739017936</v>
@@ -26049,7 +26093,7 @@
         <v>27.21364287654172</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.896693997000152</v>
+        <v>-0.8951759805315658</v>
       </c>
       <c r="E178" t="n">
         <v>0.4552971555926947</v>
@@ -26067,7 +26111,7 @@
         <v>-18.67020719966512</v>
       </c>
       <c r="D179" t="n">
-        <v>-1.08678886453522</v>
+        <v>-1.083547870304905</v>
       </c>
       <c r="E179" t="n">
         <v>-0.3480071569428784</v>
@@ -26085,7 +26129,7 @@
         <v>-33.98103710640291</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.6613384467186394</v>
+        <v>-0.661953640812193</v>
       </c>
       <c r="E180" t="n">
         <v>-0.6160591114356616</v>
@@ -26103,7 +26147,7 @@
         <v>-45.72154733835231</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.9872153624930415</v>
+        <v>-0.9848768804236323</v>
       </c>
       <c r="E181" t="n">
         <v>-0.8216042538992742</v>
@@ -26121,7 +26165,7 @@
         <v>-16.12340348223603</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.4078786233385489</v>
+        <v>-0.4107911211144069</v>
       </c>
       <c r="E182" t="n">
         <v>-0.3034193900925698</v>
@@ -26139,7 +26183,7 @@
         <v>-55.02860178742976</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.07294957101485799</v>
+        <v>-0.07889779151376111</v>
       </c>
       <c r="E183" t="n">
         <v>-0.9845460507086096</v>
@@ -26157,7 +26201,7 @@
         <v>9.724078670994848</v>
       </c>
       <c r="D184" t="n">
-        <v>0.2076666620130993</v>
+        <v>0.1991749981516449</v>
       </c>
       <c r="E184" t="n">
         <v>0.149101351898162</v>
@@ -26175,7 +26219,7 @@
         <v>34.85093849514722</v>
       </c>
       <c r="D185" t="n">
-        <v>1.429705096167107</v>
+        <v>1.410137146694542</v>
       </c>
       <c r="E185" t="n">
         <v>0.5890059114260719</v>
@@ -26193,7 +26237,7 @@
         <v>80.34739157104171</v>
       </c>
       <c r="D186" t="n">
-        <v>1.601695690603597</v>
+        <v>1.580568856489468</v>
       </c>
       <c r="E186" t="n">
         <v>1.385527931706366</v>
@@ -26211,7 +26255,7 @@
         <v>90.37554869126971</v>
       </c>
       <c r="D187" t="n">
-        <v>1.330131594124928</v>
+        <v>1.311466156813269</v>
       </c>
       <c r="E187" t="n">
         <v>1.561094320492052</v>
@@ -26229,7 +26273,7 @@
         <v>-10.71235775517695</v>
       </c>
       <c r="D188" t="n">
-        <v>1.158140999688438</v>
+        <v>1.141034447018343</v>
       </c>
       <c r="E188" t="n">
         <v>-0.2086863552523279</v>
@@ -26247,7 +26291,7 @@
         <v>-39.11071469237484</v>
       </c>
       <c r="D189" t="n">
-        <v>1.465913642364262</v>
+        <v>1.446017506651369</v>
       </c>
       <c r="E189" t="n">
         <v>-0.7058661376526075</v>
@@ -26265,7 +26309,7 @@
         <v>120.4043790561992</v>
       </c>
       <c r="D190" t="n">
-        <v>0.5606999874353681</v>
+        <v>0.549008507730704</v>
       </c>
       <c r="E190" t="n">
         <v>2.086819360838124</v>
@@ -26283,7 +26327,7 @@
         <v>-5.425910422771029</v>
       </c>
       <c r="D191" t="n">
-        <v>0.5063871681396345</v>
+        <v>0.4951879677954642</v>
       </c>
       <c r="E191" t="n">
         <v>-0.1161347072746455</v>
@@ -26301,7 +26345,7 @@
         <v>38.63612560606714</v>
       </c>
       <c r="D192" t="n">
-        <v>0.6059606701818129</v>
+        <v>0.5938589576767372</v>
       </c>
       <c r="E192" t="n">
         <v>0.6552744814110649</v>
@@ -26319,7 +26363,7 @@
         <v>4.764237813813717</v>
       </c>
       <c r="D193" t="n">
-        <v>0.5335435777875013</v>
+        <v>0.5220982377630841</v>
       </c>
       <c r="E193" t="n">
         <v>0.06226771558720692</v>
@@ -26337,7 +26381,7 @@
         <v>15.437265249042</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5516478508860791</v>
+        <v>0.5400384177414974</v>
       </c>
       <c r="E194" t="n">
         <v>0.2491240703239964</v>
@@ -26355,7 +26399,7 @@
         <v>-38.14044714855463</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.3445136674935264</v>
+        <v>-0.3480004911899605</v>
       </c>
       <c r="E195" t="n">
         <v>-0.6888793307266506</v>
@@ -26373,7 +26417,7 @@
         <v>-24.64197059385144</v>
       </c>
       <c r="D196" t="n">
-        <v>-1.113945274183086</v>
+        <v>-1.110458140272525</v>
       </c>
       <c r="E196" t="n">
         <v>-0.4525568684432109</v>
@@ -26391,7 +26435,7 @@
         <v>-41.47311676031693</v>
       </c>
       <c r="D197" t="n">
-        <v>-1.204466639675976</v>
+        <v>-1.200159040164592</v>
       </c>
       <c r="E197" t="n">
         <v>-0.7472255215310084</v>
@@ -26409,7 +26453,7 @@
         <v>-28.52889693451624</v>
       </c>
       <c r="D198" t="n">
-        <v>-1.34024868791531</v>
+        <v>-1.334710390002691</v>
       </c>
       <c r="E198" t="n">
         <v>-0.5206066220444953</v>
@@ -26427,7 +26471,7 @@
         <v>-11.81921638757925</v>
       </c>
       <c r="D199" t="n">
-        <v>-1.195414503126687</v>
+        <v>-1.191188950175385</v>
       </c>
       <c r="E199" t="n">
         <v>-0.2280645092498509</v>
@@ -26445,7 +26489,7 @@
         <v>-29.47679816890156</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.9510068162958858</v>
+        <v>-0.9489965204668057</v>
       </c>
       <c r="E200" t="n">
         <v>-0.5372018543141251</v>
@@ -26463,7 +26507,7 @@
         <v>67.46688427524957</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.8514333142537072</v>
+        <v>-0.8503255305855325</v>
       </c>
       <c r="E201" t="n">
         <v>1.16002446935151</v>
@@ -26481,7 +26525,7 @@
         <v>-8.270197881645608</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.5889213543243279</v>
+        <v>-0.5901929208985399</v>
       </c>
       <c r="E202" t="n">
         <v>-0.1659306240952698</v>
@@ -26499,7 +26543,7 @@
         <v>126.467664294684</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E203" t="n">
         <v>2.192971376680705</v>
@@ -26517,7 +26561,7 @@
         <v>-25.40522557711146</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.6070256274229058</v>
+        <v>-0.6081331008769533</v>
       </c>
       <c r="E204" t="n">
         <v>-0.4659194354160941</v>
@@ -26535,7 +26579,7 @@
         <v>-35.72150359362902</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.3445136674935264</v>
+        <v>-0.3480004911899605</v>
       </c>
       <c r="E205" t="n">
         <v>-0.6465300556282322</v>
@@ -26553,7 +26597,7 @@
         <v>49.48222758326399</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.7247034025636621</v>
+        <v>-0.7247442707366395</v>
       </c>
       <c r="E206" t="n">
         <v>0.8451609115605008</v>
@@ -26571,7 +26615,7 @@
         <v>31.9775989054176</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E207" t="n">
         <v>0.5387013689786652</v>
@@ -26589,7 +26633,7 @@
         <v>-38.77219782318121</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.7247034025636621</v>
+        <v>-0.7247442707366395</v>
       </c>
       <c r="E208" t="n">
         <v>-0.6999396066305237</v>
@@ -26607,7 +26651,7 @@
         <v>-69.1932310969579</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.4350350329864158</v>
+        <v>-0.4377013910820269</v>
       </c>
       <c r="E209" t="n">
         <v>-1.232531077922184</v>
@@ -26625,7 +26669,7 @@
         <v>-45.34193085082509</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.5255563984793051</v>
+        <v>-0.5274022909740934</v>
       </c>
       <c r="E210" t="n">
         <v>-0.8149581777519206</v>
@@ -26643,7 +26687,7 @@
         <v>-2.341082750772228</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.7428076756622399</v>
+        <v>-0.7426844507150528</v>
       </c>
       <c r="E211" t="n">
         <v>-0.06212757037941991</v>
@@ -26661,7 +26705,7 @@
         <v>95.1804107015612</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.7790162218593958</v>
+        <v>-0.7785648106718794</v>
       </c>
       <c r="E212" t="n">
         <v>1.645214688935305</v>
@@ -26679,7 +26723,7 @@
         <v>-34.64151516301665</v>
       </c>
       <c r="D213" t="n">
-        <v>-1.141101683830954</v>
+        <v>-1.137368410240145</v>
       </c>
       <c r="E213" t="n">
         <v>-0.6276223274764197</v>
@@ -26697,7 +26741,7 @@
         <v>-33.21845646697446</v>
       </c>
       <c r="D214" t="n">
-        <v>-1.421717916858911</v>
+        <v>-1.415441199905551</v>
       </c>
       <c r="E214" t="n">
         <v>-0.6027083504317008</v>
@@ -26715,7 +26759,7 @@
         <v>93.68067182921725</v>
       </c>
       <c r="D215" t="n">
-        <v>-1.349300824464599</v>
+        <v>-1.343680479991898</v>
       </c>
       <c r="E215" t="n">
         <v>1.618958245724236</v>
@@ -26733,7 +26777,7 @@
         <v>-65.71523623526801</v>
       </c>
       <c r="D216" t="n">
-        <v>-1.385509370661755</v>
+        <v>-1.379560839948725</v>
       </c>
       <c r="E216" t="n">
         <v>-1.171640628085656</v>
@@ -26751,7 +26795,7 @@
         <v>-65.13108106334673</v>
       </c>
       <c r="D217" t="n">
-        <v>-1.448874326506778</v>
+        <v>-1.442351469873171</v>
       </c>
       <c r="E217" t="n">
         <v>-1.161413622984407</v>
@@ -26769,7 +26813,7 @@
         <v>-17.22612564272645</v>
       </c>
       <c r="D218" t="n">
-        <v>-1.249727322422421</v>
+        <v>-1.245009490110625</v>
       </c>
       <c r="E218" t="n">
         <v>-0.3227251254565219</v>
@@ -26787,7 +26831,7 @@
         <v>-38.68628278652732</v>
       </c>
       <c r="D219" t="n">
-        <v>-1.059632454887353</v>
+        <v>-1.056637600337285</v>
       </c>
       <c r="E219" t="n">
         <v>-0.6984354625941994</v>
@@ -26805,7 +26849,7 @@
         <v>-40.87741073133473</v>
       </c>
       <c r="D220" t="n">
-        <v>-1.213518776225265</v>
+        <v>-1.209129130153798</v>
       </c>
       <c r="E220" t="n">
         <v>-0.7367962916104578</v>
@@ -26823,7 +26867,7 @@
         <v>-46.89106500451042</v>
       </c>
       <c r="D221" t="n">
-        <v>-1.385509370661755</v>
+        <v>-1.379560839948725</v>
       </c>
       <c r="E221" t="n">
         <v>-0.8420794011079544</v>
@@ -26841,7 +26885,7 @@
         <v>-80.90692838228034</v>
       </c>
       <c r="D222" t="n">
-        <v>-1.620864920943268</v>
+        <v>-1.612783179668097</v>
       </c>
       <c r="E222" t="n">
         <v>-1.437606796925877</v>
@@ -26859,7 +26903,7 @@
         <v>-7.641033978214917</v>
       </c>
       <c r="D223" t="n">
-        <v>-1.240675185873132</v>
+        <v>-1.236039400121418</v>
       </c>
       <c r="E223" t="n">
         <v>-0.1549156356826111</v>
@@ -26877,7 +26921,7 @@
         <v>-35.30694651378722</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.5165042619300163</v>
+        <v>-0.5184322009848867</v>
       </c>
       <c r="E224" t="n">
         <v>-0.6392722625381585</v>
@@ -26895,7 +26939,7 @@
         <v>24.39746460697616</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.01863675171912433</v>
+        <v>-0.02507725157852124</v>
       </c>
       <c r="E225" t="n">
         <v>0.4059933559975495</v>
@@ -26913,7 +26957,7 @@
         <v>59.60704619735723</v>
       </c>
       <c r="D226" t="n">
-        <v>0.5154393046889234</v>
+        <v>0.5041580577846708</v>
       </c>
       <c r="E226" t="n">
         <v>1.022419586297543</v>
@@ -26931,7 +26975,7 @@
         <v>106.3363331938049</v>
       </c>
       <c r="D227" t="n">
-        <v>0.08998888687234299</v>
+        <v>0.0825638282919585</v>
       </c>
       <c r="E227" t="n">
         <v>1.840525253184991</v>
@@ -26949,7 +26993,7 @@
         <v>-33.07540183714583</v>
       </c>
       <c r="D228" t="n">
-        <v>0.1352495696187877</v>
+        <v>0.1274142782379917</v>
       </c>
       <c r="E228" t="n">
         <v>-0.6002038439249745</v>
@@ -26967,7 +27011,7 @@
         <v>-43.59555378632452</v>
       </c>
       <c r="D229" t="n">
-        <v>0.3615529833510114</v>
+        <v>0.3516665279681578</v>
       </c>
       <c r="E229" t="n">
         <v>-0.7843837550542495</v>
@@ -26985,7 +27029,7 @@
         <v>-8.163523978925745</v>
       </c>
       <c r="D230" t="n">
-        <v>0.03567606757660934</v>
+        <v>0.02874328835671863</v>
       </c>
       <c r="E230" t="n">
         <v>-0.1640630474654198</v>
@@ -27003,7 +27047,7 @@
         <v>-53.07451020348752</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E231" t="n">
         <v>-0.9503350986227851</v>
@@ -27021,7 +27065,7 @@
         <v>-19.23333969830055</v>
       </c>
       <c r="D232" t="n">
-        <v>0.5244914412382123</v>
+        <v>0.5131281477738775</v>
       </c>
       <c r="E232" t="n">
         <v>-0.3578661108870538</v>
@@ -27039,7 +27083,7 @@
         <v>26.25395341760046</v>
       </c>
       <c r="D233" t="n">
-        <v>1.013306814899815</v>
+        <v>0.9975130071910363</v>
       </c>
       <c r="E233" t="n">
         <v>0.4384955428295536</v>
@@ -27057,7 +27101,7 @@
         <v>14.31606349396328</v>
       </c>
       <c r="D234" t="n">
-        <v>1.40254868651924</v>
+        <v>1.383226876726922</v>
       </c>
       <c r="E234" t="n">
         <v>0.2294948063546191</v>
@@ -27075,7 +27119,7 @@
         <v>253.0970573890424</v>
       </c>
       <c r="D235" t="n">
-        <v>1.094776043843416</v>
+        <v>1.078243817093896</v>
       </c>
       <c r="E235" t="n">
         <v>4.409915626073774</v>
@@ -27093,7 +27137,7 @@
         <v>-6.911964759992227</v>
       </c>
       <c r="D236" t="n">
-        <v>0.4701786219424787</v>
+        <v>0.4593076078386377</v>
       </c>
       <c r="E236" t="n">
         <v>-0.1421515706322172</v>
@@ -27111,7 +27155,7 @@
         <v>25.79231031996054</v>
       </c>
       <c r="D237" t="n">
-        <v>0.09904102342163196</v>
+        <v>0.09153391828116515</v>
       </c>
       <c r="E237" t="n">
         <v>0.4304133986640027</v>
@@ -27129,7 +27173,7 @@
         <v>7.069609762036325</v>
       </c>
       <c r="D238" t="n">
-        <v>0.2348230716609661</v>
+        <v>0.2260852681192649</v>
       </c>
       <c r="E238" t="n">
         <v>0.1026286535845628</v>
@@ -27147,7 +27191,7 @@
         <v>-33.71965257429887</v>
       </c>
       <c r="D239" t="n">
-        <v>0.7598469915197249</v>
+        <v>0.7463504874932502</v>
       </c>
       <c r="E239" t="n">
         <v>-0.611482962714041</v>
@@ -27165,7 +27209,7 @@
         <v>0.2482796010276136</v>
       </c>
       <c r="D240" t="n">
-        <v>0.7326905818718581</v>
+        <v>0.7194402175256303</v>
       </c>
       <c r="E240" t="n">
         <v>-0.01679471490928406</v>
@@ -27183,7 +27227,7 @@
         <v>9.895493856053619</v>
       </c>
       <c r="D241" t="n">
-        <v>0.750794854970436</v>
+        <v>0.7373803975040435</v>
       </c>
       <c r="E241" t="n">
         <v>0.1521023763798282</v>
@@ -27201,7 +27245,7 @@
         <v>6.621825448799489</v>
       </c>
       <c r="D242" t="n">
-        <v>0.5697521239846571</v>
+        <v>0.5579785977199107</v>
       </c>
       <c r="E242" t="n">
         <v>0.09478913991446958</v>
@@ -27219,7 +27263,7 @@
         <v>-13.76342755669412</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E243" t="n">
         <v>-0.2621024815219222</v>
@@ -27237,7 +27281,7 @@
         <v>-44.56272675195723</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.9147982700987299</v>
+        <v>-0.913116160509979</v>
       </c>
       <c r="E244" t="n">
         <v>-0.8013163841376894</v>
@@ -27255,7 +27299,7 @@
         <v>-6.623265115369143</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.6703905832679283</v>
+        <v>-0.6709237308013997</v>
       </c>
       <c r="E245" t="n">
         <v>-0.1370972068600395</v>
@@ -27273,7 +27317,7 @@
         <v>70.48218907556738</v>
       </c>
       <c r="D246" t="n">
-        <v>-1.403613643760333</v>
+        <v>-1.397501019927138</v>
       </c>
       <c r="E246" t="n">
         <v>1.212814445469067</v>
@@ -27291,7 +27335,7 @@
         <v>43.37506096569664</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.593708511295401</v>
+        <v>-1.585872909700477</v>
       </c>
       <c r="E247" t="n">
         <v>0.7382406493524017</v>
@@ -27309,7 +27353,7 @@
         <v>-44.48403187147762</v>
       </c>
       <c r="D248" t="n">
-        <v>-2.055367475309137</v>
+        <v>-2.043347499150016</v>
       </c>
       <c r="E248" t="n">
         <v>-0.7999386458537671</v>
@@ -27327,7 +27371,7 @@
         <v>-43.32371807036854</v>
       </c>
       <c r="D249" t="n">
-        <v>-1.457926463056067</v>
+        <v>-1.451321559862378</v>
       </c>
       <c r="E249" t="n">
         <v>-0.7796246338696505</v>
@@ -27345,7 +27389,7 @@
         <v>7.659602363716401</v>
       </c>
       <c r="D250" t="n">
-        <v>-1.077736727985931</v>
+        <v>-1.074577780315699</v>
       </c>
       <c r="E250" t="n">
         <v>0.1129578565722487</v>
@@ -27363,7 +27407,7 @@
         <v>27.89085391377147</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.8152247680565514</v>
+        <v>-0.8144451706287059</v>
       </c>
       <c r="E251" t="n">
         <v>0.4671533216685541</v>
@@ -27381,7 +27425,7 @@
         <v>3.186973638004633</v>
       </c>
       <c r="D252" t="n">
-        <v>-0.8423811777044182</v>
+        <v>-0.8413554405963258</v>
       </c>
       <c r="E252" t="n">
         <v>0.03465401027845558</v>
@@ -27399,7 +27443,7 @@
         <v>-26.86319712684657</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.8242769046058404</v>
+        <v>-0.8234152606179125</v>
       </c>
       <c r="E253" t="n">
         <v>-0.4914446437739626</v>
@@ -27417,7 +27461,7 @@
         <v>4.232594101070203</v>
       </c>
       <c r="D254" t="n">
-        <v>-1.08678886453522</v>
+        <v>-1.083547870304905</v>
       </c>
       <c r="E254" t="n">
         <v>0.05296004662590614</v>
@@ -27435,7 +27479,7 @@
         <v>-2.355462723064836</v>
       </c>
       <c r="D255" t="n">
-        <v>-1.304040141718154</v>
+        <v>-1.298830030045865</v>
       </c>
       <c r="E255" t="n">
         <v>-0.06237932549015295</v>
@@ -27453,7 +27497,7 @@
         <v>65.23773152568265</v>
       </c>
       <c r="D256" t="n">
-        <v>-1.095841001084509</v>
+        <v>-1.092517960294112</v>
       </c>
       <c r="E256" t="n">
         <v>1.120997927026628</v>
@@ -27471,7 +27515,7 @@
         <v>-36.79966090273778</v>
       </c>
       <c r="D257" t="n">
-        <v>-0.3807222136906822</v>
+        <v>-0.383880851146787</v>
       </c>
       <c r="E257" t="n">
         <v>-0.6654057257073638</v>
@@ -27489,7 +27533,7 @@
         <v>-51.2574617375563</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.9057461335494408</v>
+        <v>-0.9041460705207724</v>
       </c>
       <c r="E258" t="n">
         <v>-0.9185234074428944</v>
@@ -27507,7 +27551,7 @@
         <v>31.19817915786052</v>
       </c>
       <c r="D259" t="n">
-        <v>-1.177310230028109</v>
+        <v>-1.173248770196972</v>
       </c>
       <c r="E259" t="n">
         <v>0.525055799928812</v>
@@ -27525,7 +27569,7 @@
         <v>-36.47297618276435</v>
       </c>
       <c r="D260" t="n">
-        <v>-0.7156512660143731</v>
+        <v>-0.7157741807474329</v>
       </c>
       <c r="E260" t="n">
         <v>-0.6596863441829652</v>
@@ -27543,7 +27587,7 @@
         <v>-32.19341860553382</v>
       </c>
       <c r="D261" t="n">
-        <v>-0.896693997000152</v>
+        <v>-0.8951759805315658</v>
       </c>
       <c r="E261" t="n">
         <v>-0.5847626607557054</v>
@@ -27561,7 +27605,7 @@
         <v>72.30593457637595</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.887641860450863</v>
+        <v>-0.8862058905423591</v>
       </c>
       <c r="E262" t="n">
         <v>1.244743383937257</v>
@@ -27579,7 +27623,7 @@
         <v>17.68784010046044</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.9510068162958858</v>
+        <v>-0.9489965204668057</v>
       </c>
       <c r="E263" t="n">
         <v>0.288525656738952</v>
@@ -27597,10 +27641,10 @@
         <v>-31.3750254132346</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.4712435791835716</v>
+        <v>-0.4735817510388535</v>
       </c>
       <c r="E264" t="n">
-        <v>-0.5704347702314395</v>
+        <v>-0.5704347702314396</v>
       </c>
       <c r="F264" t="inlineStr"/>
     </row>
@@ -27615,7 +27659,7 @@
         <v>-33.6348802925647</v>
       </c>
       <c r="D265" t="n">
-        <v>-0.6794427198172173</v>
+        <v>-0.6798938207906062</v>
       </c>
       <c r="E265" t="n">
         <v>-0.6099988252803376</v>
@@ -27633,7 +27677,7 @@
         <v>24.77871619480581</v>
       </c>
       <c r="D266" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E266" t="n">
         <v>0.4126680584071323</v>
@@ -27651,7 +27695,7 @@
         <v>-3.976594567843735</v>
       </c>
       <c r="D267" t="n">
-        <v>0.6240649432803909</v>
+        <v>0.6117991376551506</v>
       </c>
       <c r="E267" t="n">
         <v>-0.0907610371367728</v>
@@ -27669,7 +27713,7 @@
         <v>90.53370250143212</v>
       </c>
       <c r="D268" t="n">
-        <v>0.741742718421147</v>
+        <v>0.7284103075148369</v>
       </c>
       <c r="E268" t="n">
         <v>1.56386317353155</v>
@@ -27687,7 +27731,7 @@
         <v>6.29394950493973</v>
       </c>
       <c r="D269" t="n">
-        <v>0.7960555377168808</v>
+        <v>0.7822308474500768</v>
       </c>
       <c r="E269" t="n">
         <v>0.08904890322461531</v>
@@ -27705,7 +27749,7 @@
         <v>-18.152032435182</v>
       </c>
       <c r="D270" s="4" t="n">
-        <v>0.8594204935619033</v>
+        <v>0.8450214773745234</v>
       </c>
       <c r="E270" s="4" t="n">
         <v>-0.3389352934818772</v>
@@ -27727,7 +27771,7 @@
         <v>384.295236546903</v>
       </c>
       <c r="D271" s="4" t="n">
-        <v>1.827999104335821</v>
+        <v>1.804821106219634</v>
       </c>
       <c r="E271" s="4" t="n">
         <v>6.70684718127854</v>
@@ -27749,7 +27793,7 @@
         <v>50.91446956446632</v>
       </c>
       <c r="D272" s="4" t="n">
-        <v>2.054302518068044</v>
+        <v>2.0290733559498</v>
       </c>
       <c r="E272" s="4" t="n">
         <v>0.8702356635306048</v>
@@ -27771,7 +27815,7 @@
         <v>138.8032793107375</v>
       </c>
       <c r="D273" s="4" t="n">
-        <v>2.362075160743868</v>
+        <v>2.334056415582827</v>
       </c>
       <c r="E273" s="4" t="n">
         <v>2.408935222864416</v>
@@ -27793,7 +27837,7 @@
         <v>35.72639327221137</v>
       </c>
       <c r="D274" s="4" t="n">
-        <v>1.330131594124928</v>
+        <v>1.311466156813269</v>
       </c>
       <c r="E274" s="4" t="n">
         <v>0.6043327987007336</v>
@@ -27815,7 +27859,7 @@
         <v>-25.69458978652156</v>
       </c>
       <c r="D275" s="4" t="n">
-        <v>1.474965778913552</v>
+        <v>1.454987596640575</v>
       </c>
       <c r="E275" s="4" t="n">
         <v>-0.4709854339521043</v>
@@ -27837,7 +27881,7 @@
         <v>15.01567919564801</v>
       </c>
       <c r="D276" s="4" t="n">
-        <v>1.465913642364262</v>
+        <v>1.446017506651369</v>
       </c>
       <c r="E276" s="4" t="n">
         <v>0.2417432185813074</v>
@@ -27859,7 +27903,7 @@
         <v>33.87197669281145</v>
       </c>
       <c r="D277" s="4" t="n">
-        <v>2.036198244969466</v>
+        <v>2.011133175971387</v>
       </c>
       <c r="E277" s="4" t="n">
         <v>0.5718668911320511</v>
@@ -27881,7 +27925,7 @@
         <v>76.32780845589326</v>
       </c>
       <c r="D278" s="4" t="n">
-        <v>1.357288003772795</v>
+        <v>1.338376426780889</v>
       </c>
       <c r="E278" s="4" t="n">
         <v>1.315155710420857</v>
@@ -27903,7 +27947,7 @@
         <v>14.45081657011441</v>
       </c>
       <c r="D279" s="4" t="n">
-        <v>0.3615529833510114</v>
+        <v>0.3516665279681578</v>
       </c>
       <c r="E279" s="4" t="n">
         <v>0.2318539747116741</v>
@@ -27925,7 +27969,7 @@
         <v>-8.081917128126779</v>
       </c>
       <c r="D280" s="4" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E280" s="4" t="n">
         <v>-0.1626343283176069</v>
@@ -27947,7 +27991,7 @@
         <v>14.33120672977643</v>
       </c>
       <c r="D281" t="n">
-        <v>-0.7880683584086847</v>
+        <v>-0.7875349006610861</v>
       </c>
       <c r="E281" t="n">
         <v>0.2297599241817902</v>
@@ -27965,7 +28009,7 @@
         <v>28.75031791864275</v>
       </c>
       <c r="D282" t="n">
-        <v>-1.023423908690197</v>
+        <v>-1.020757240380459</v>
       </c>
       <c r="E282" t="n">
         <v>0.4822002530057351</v>
@@ -27983,7 +28027,7 @@
         <v>1.820842139489521</v>
       </c>
       <c r="D283" t="n">
-        <v>-1.240675185873132</v>
+        <v>-1.236039400121418</v>
       </c>
       <c r="E283" t="n">
         <v>0.01073667722063219</v>
@@ -28001,7 +28045,7 @@
         <v>12.41389734620285</v>
       </c>
       <c r="D284" t="n">
-        <v>-0.896693997000152</v>
+        <v>-0.8951759805315658</v>
       </c>
       <c r="E284" t="n">
         <v>0.1961929307030054</v>
@@ -28019,7 +28063,7 @@
         <v>57.47523437203479</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.249727322422421</v>
+        <v>-1.245009490110625</v>
       </c>
       <c r="E285" t="n">
         <v>0.9850972249448744</v>
@@ -28037,7 +28081,7 @@
         <v>106.7221696743803</v>
       </c>
       <c r="D286" t="n">
-        <v>-0.9691110893944637</v>
+        <v>-0.966936700445219</v>
       </c>
       <c r="E286" t="n">
         <v>1.8472802248856</v>
@@ -28055,7 +28099,7 @@
         <v>-16.66884679782336</v>
       </c>
       <c r="D287" t="n">
-        <v>-0.7609119487608178</v>
+        <v>-0.7606246306934662</v>
       </c>
       <c r="E287" t="n">
         <v>-0.3129686534374567</v>
@@ -28073,10 +28117,10 @@
         <v>3.353314809908999</v>
       </c>
       <c r="D288" t="n">
-        <v>-0.7971204949579737</v>
+        <v>-0.7965049906502928</v>
       </c>
       <c r="E288" t="n">
-        <v>0.03756620227021455</v>
+        <v>0.03756620227021454</v>
       </c>
       <c r="F288" t="inlineStr"/>
     </row>
@@ -28091,7 +28135,7 @@
         <v>-21.67944741665536</v>
       </c>
       <c r="D289" t="n">
-        <v>-0.8152247680565514</v>
+        <v>-0.8144451706287059</v>
       </c>
       <c r="E289" t="n">
         <v>-0.4006909583185013</v>
@@ -28109,7 +28153,7 @@
         <v>-35.04079226995989</v>
       </c>
       <c r="D290" t="n">
-        <v>-1.005319635591619</v>
+        <v>-1.002817060402046</v>
       </c>
       <c r="E290" t="n">
         <v>-0.6346126088362343</v>
@@ -28127,7 +28171,7 @@
         <v>-17.95544525632441</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.032476045239486</v>
+        <v>-1.029727330369665</v>
       </c>
       <c r="E291" t="n">
         <v>-0.3354935742646968</v>
@@ -28145,7 +28189,7 @@
         <v>-35.44013748329196</v>
       </c>
       <c r="D292" t="n">
-        <v>-0.5436606715778831</v>
+        <v>-0.5453424709525067</v>
       </c>
       <c r="E292" t="n">
         <v>-0.641604082557975</v>
@@ -28163,7 +28207,7 @@
         <v>-33.41955678248868</v>
       </c>
       <c r="D293" t="n">
-        <v>-0.1363145268598806</v>
+        <v>-0.1416884214382076</v>
       </c>
       <c r="E293" t="n">
         <v>-0.6062290826814255</v>
@@ -28181,7 +28225,7 @@
         <v>-29.63300967968762</v>
       </c>
       <c r="D294" t="n">
-        <v>0.03567606757660934</v>
+        <v>0.02874328835671863</v>
       </c>
       <c r="E294" t="n">
         <v>-0.5399367028517635</v>
@@ -28199,7 +28243,7 @@
         <v>14.42041944399284</v>
       </c>
       <c r="D295" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E295" t="n">
         <v>0.231321801791102</v>
@@ -28217,10 +28261,10 @@
         <v>1.034311502666751</v>
       </c>
       <c r="D296" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E296" t="n">
-        <v>-0.00303338460834922</v>
+        <v>-0.003033384608349224</v>
       </c>
       <c r="F296" t="inlineStr"/>
     </row>
@@ -28235,7 +28279,7 @@
         <v>-54.34015257904126</v>
       </c>
       <c r="D297" t="n">
-        <v>-0.1996794827049032</v>
+        <v>-0.2044790513626542</v>
       </c>
       <c r="E297" t="n">
         <v>-0.9724931341128648</v>
@@ -28253,7 +28297,7 @@
         <v>234.3291409520421</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.3535658040428153</v>
+        <v>-0.3569705811791671</v>
       </c>
       <c r="E298" t="n">
         <v>4.081339271079371</v>
@@ -28271,7 +28315,7 @@
         <v>32.08978652155712</v>
       </c>
       <c r="D299" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E299" t="n">
         <v>0.5406654760818896</v>
@@ -28289,7 +28333,7 @@
         <v>36.19645508480318</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.6884948563665062</v>
+        <v>-0.6888639107798129</v>
       </c>
       <c r="E300" t="n">
         <v>0.6125623321986015</v>
@@ -28307,7 +28351,7 @@
         <v>-1.233163749622684</v>
       </c>
       <c r="D301" t="n">
-        <v>-1.104893137633798</v>
+        <v>-1.101488050283319</v>
       </c>
       <c r="E301" t="n">
         <v>-0.04273085214227611</v>
@@ -28325,7 +28369,7 @@
         <v>12.98465906450292</v>
       </c>
       <c r="D302" t="n">
-        <v>-0.8242769046058404</v>
+        <v>-0.8234152606179125</v>
       </c>
       <c r="E302" t="n">
         <v>0.2061854520145162</v>
@@ -28343,7 +28387,7 @@
         <v>61.55097377077816</v>
       </c>
       <c r="D303" t="n">
-        <v>-0.8514333142537072</v>
+        <v>-0.8503255305855325</v>
       </c>
       <c r="E303" t="n">
         <v>1.056452593562458</v>
@@ -28361,7 +28405,7 @@
         <v>45.37903379797596</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.08200170756414694</v>
+        <v>-0.08786788150296776</v>
       </c>
       <c r="E304" t="n">
         <v>0.7733248895741888</v>
@@ -28379,7 +28423,7 @@
         <v>-16.51360193024596</v>
       </c>
       <c r="D305" t="n">
-        <v>0.2167187985623882</v>
+        <v>0.2081450881408516</v>
       </c>
       <c r="E305" t="n">
         <v>-0.3102507282542644</v>
@@ -28397,7 +28441,7 @@
         <v>-35.54854056641881</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.6522863101693505</v>
+        <v>-0.6529835508229863</v>
       </c>
       <c r="E306" t="n">
         <v>-0.643501932542737</v>
@@ -28415,7 +28459,7 @@
         <v>50.96732238660381</v>
       </c>
       <c r="D307" t="n">
-        <v>-1.077736727985931</v>
+        <v>-1.074577780315699</v>
       </c>
       <c r="E307" t="n">
         <v>0.8711609760290592</v>
@@ -28433,7 +28477,7 @@
         <v>212.3447992917449</v>
       </c>
       <c r="D308" t="n">
-        <v>-0.6251299005214837</v>
+        <v>-0.6260732808553665</v>
       </c>
       <c r="E308" t="n">
         <v>3.696451855689401</v>
@@ -28451,7 +28495,7 @@
         <v>140.7959160435724</v>
       </c>
       <c r="D309" t="n">
-        <v>-0.6432341736200615</v>
+        <v>-0.6440134608337796</v>
       </c>
       <c r="E309" t="n">
         <v>2.443820998102207</v>
@@ -28469,7 +28513,7 @@
         <v>29.85456214120491</v>
       </c>
       <c r="D310" t="n">
-        <v>-1.204466639675976</v>
+        <v>-1.200159040164592</v>
       </c>
       <c r="E310" t="n">
         <v>0.5015326356328123</v>
@@ -28487,7 +28531,7 @@
         <v>171.6356215989954</v>
       </c>
       <c r="D311" t="n">
-        <v>-1.566552101647534</v>
+        <v>-1.558962639732858</v>
       </c>
       <c r="E311" t="n">
         <v>2.983742308734442</v>
@@ -28505,7 +28549,7 @@
         <v>-14.29733176438698</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.820011925027624</v>
+        <v>-1.810125159430644</v>
       </c>
       <c r="E312" t="n">
         <v>-0.2714497257441973</v>
@@ -28523,7 +28567,7 @@
         <v>-30.55087730042563</v>
       </c>
       <c r="D313" t="n">
-        <v>-1.485082872703933</v>
+        <v>-1.478231829829998</v>
       </c>
       <c r="E313" t="n">
         <v>-0.5560061263384807</v>
@@ -28541,7 +28585,7 @@
         <v>56.21263525246425</v>
       </c>
       <c r="D314" t="n">
-        <v>-0.7971204949579737</v>
+        <v>-0.7965049906502928</v>
       </c>
       <c r="E314" t="n">
         <v>0.9629924687818651</v>
@@ -28559,7 +28603,7 @@
         <v>6.26328200052401</v>
       </c>
       <c r="D315" t="n">
-        <v>-0.3626179405921042</v>
+        <v>-0.3659406711683738</v>
       </c>
       <c r="E315" t="n">
         <v>0.08851199669844245</v>
@@ -28577,7 +28621,7 @@
         <v>11.21825472598816</v>
       </c>
       <c r="D316" t="n">
-        <v>-0.2630444385499259</v>
+        <v>-0.2672696812871007</v>
       </c>
       <c r="E316" t="n">
         <v>0.1752604049564825</v>
@@ -28595,10 +28639,10 @@
         <v>3.229031942527365</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3706051199003003</v>
+        <v>0.3606366179573645</v>
       </c>
       <c r="E317" t="n">
-        <v>0.03539033945189966</v>
+        <v>0.03539033945189965</v>
       </c>
       <c r="F317" t="inlineStr"/>
     </row>
@@ -28613,7 +28657,7 @@
         <v>38.31031851707785</v>
       </c>
       <c r="D318" t="n">
-        <v>0.8503683570126144</v>
+        <v>0.8360513873853167</v>
       </c>
       <c r="E318" t="n">
         <v>0.6495704648735452</v>
@@ -28631,7 +28675,7 @@
         <v>-2.292310193464472</v>
       </c>
       <c r="D319" t="n">
-        <v>1.456861505814974</v>
+        <v>1.437047416662162</v>
       </c>
       <c r="E319" t="n">
         <v>-0.06127369247785677</v>
@@ -28649,7 +28693,7 @@
         <v>37.24601066701216</v>
       </c>
       <c r="D320" t="n">
-        <v>1.674112782997909</v>
+        <v>1.652329576403122</v>
       </c>
       <c r="E320" t="n">
         <v>0.6309372620275929</v>
@@ -28667,7 +28711,7 @@
         <v>-10.01821839298591</v>
       </c>
       <c r="D321" t="n">
-        <v>1.348235867223506</v>
+        <v>1.329406336791682</v>
       </c>
       <c r="E321" t="n">
         <v>-0.1965338191808637</v>
@@ -28685,7 +28729,7 @@
         <v>-16.22105056142946</v>
       </c>
       <c r="D322" t="n">
-        <v>0.9680461321533707</v>
+        <v>0.952662557245003</v>
       </c>
       <c r="E322" t="n">
         <v>-0.3051289310245602</v>
@@ -28703,7 +28747,7 @@
         <v>-42.60804730012558</v>
       </c>
       <c r="D323" t="n">
-        <v>0.6783777625761245</v>
+        <v>0.6656196775903905</v>
       </c>
       <c r="E323" t="n">
         <v>-0.767095140046944</v>
@@ -28721,7 +28765,7 @@
         <v>-11.37712007984376</v>
       </c>
       <c r="D324" t="n">
-        <v>0.6602734894775465</v>
+        <v>0.6476794976119772</v>
       </c>
       <c r="E324" t="n">
         <v>-0.2203245774444306</v>
@@ -28739,7 +28783,7 @@
         <v>-6.495653961740855</v>
       </c>
       <c r="D325" t="n">
-        <v>0.5697521239846571</v>
+        <v>0.5579785977199107</v>
       </c>
       <c r="E325" t="n">
         <v>-0.1348630745919978</v>
@@ -28757,7 +28801,7 @@
         <v>-33.27897180664759</v>
       </c>
       <c r="D326" t="n">
-        <v>0.4249179391960339</v>
+        <v>0.4144571578926044</v>
       </c>
       <c r="E326" t="n">
         <v>-0.6037678132547474</v>
@@ -28775,7 +28819,7 @@
         <v>-26.13752146953509</v>
       </c>
       <c r="D327" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E327" t="n">
         <v>-0.478739990959253</v>
@@ -28793,7 +28837,7 @@
         <v>-12.48806568646171</v>
       </c>
       <c r="D328" t="n">
-        <v>-0.1996794827049032</v>
+        <v>-0.2044790513626542</v>
       </c>
       <c r="E328" t="n">
         <v>-0.239774283502367</v>
@@ -28811,7 +28855,7 @@
         <v>-26.31155647817061</v>
       </c>
       <c r="D329" t="n">
-        <v>-0.3173572578456595</v>
+        <v>-0.3210902212223405</v>
       </c>
       <c r="E329" t="n">
         <v>-0.48178688159151</v>
@@ -28829,7 +28873,7 @@
         <v>-72.87293726904146</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.6160777639721947</v>
+        <v>-0.6171031908661599</v>
       </c>
       <c r="E330" t="n">
         <v>-1.29695295690551</v>
@@ -28847,7 +28891,7 @@
         <v>21.10225979515526</v>
       </c>
       <c r="D331" t="n">
-        <v>-0.3354615309442374</v>
+        <v>-0.3390304012007538</v>
       </c>
       <c r="E331" t="n">
         <v>0.3483030743052481</v>
@@ -28865,7 +28909,7 @@
         <v>-14.4695644663255</v>
       </c>
       <c r="D332" t="n">
-        <v>-0.235888028902059</v>
+        <v>-0.2403594113194807</v>
       </c>
       <c r="E332" t="n">
         <v>-0.274465062774483</v>
@@ -28883,7 +28927,7 @@
         <v>-21.00618666261812</v>
       </c>
       <c r="D333" t="n">
-        <v>-0.5979734908736168</v>
+        <v>-0.5991630108877466</v>
       </c>
       <c r="E333" t="n">
         <v>-0.3889039512063951</v>
@@ -28901,7 +28945,7 @@
         <v>206.3185398151357</v>
       </c>
       <c r="D334" t="n">
-        <v>-0.7880683584086847</v>
+        <v>-0.7875349006610861</v>
       </c>
       <c r="E334" t="n">
         <v>3.590948062568762</v>
@@ -28919,7 +28963,7 @@
         <v>-21.5348995395563</v>
       </c>
       <c r="D335" t="n">
-        <v>-0.2087316192541921</v>
+        <v>-0.2134491413518607</v>
       </c>
       <c r="E335" t="n">
         <v>-0.3981603090192666</v>
@@ -28937,7 +28981,7 @@
         <v>-69.24536555012722</v>
       </c>
       <c r="D336" t="n">
-        <v>-0.2087316192541921</v>
+        <v>-0.2134491413518607</v>
       </c>
       <c r="E336" t="n">
         <v>-1.233443813688539</v>
@@ -28955,7 +28999,7 @@
         <v>-32.80810502233167</v>
       </c>
       <c r="D337" t="n">
-        <v>-0.2811487116485037</v>
+        <v>-0.285209861265514</v>
       </c>
       <c r="E337" t="n">
         <v>-0.5955241868406056</v>
@@ -28973,7 +29017,7 @@
         <v>-46.70176224296222</v>
       </c>
       <c r="D338" t="n">
-        <v>-0.1544187999584585</v>
+        <v>-0.1596286014166209</v>
       </c>
       <c r="E338" t="n">
         <v>-0.8387652126849254</v>
@@ -28991,7 +29035,7 @@
         <v>-31.27929317923786</v>
       </c>
       <c r="D339" t="n">
-        <v>-0.1453666634091696</v>
+        <v>-0.1506585114274143</v>
       </c>
       <c r="E339" t="n">
         <v>-0.5687587531515624</v>
@@ -29009,7 +29053,7 @@
         <v>-23.87340080198586</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.8785897239015741</v>
+        <v>-0.8772358005531524</v>
       </c>
       <c r="E340" t="n">
         <v>-0.4391012532918064</v>
@@ -29027,7 +29071,7 @@
         <v>-29.2949602756252</v>
       </c>
       <c r="D341" t="n">
-        <v>-0.4802957157328605</v>
+        <v>-0.4825518410280601</v>
       </c>
       <c r="E341" t="n">
         <v>-0.5340183559021854</v>
@@ -29045,7 +29089,7 @@
         <v>-27.69407998085008</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.9147982700987299</v>
+        <v>-0.913116160509979</v>
       </c>
       <c r="E342" t="n">
         <v>-0.5059911950926586</v>
@@ -29063,7 +29107,7 @@
         <v>-50.57714192814176</v>
       </c>
       <c r="D343" t="n">
-        <v>-0.8514333142537072</v>
+        <v>-0.8503255305855325</v>
       </c>
       <c r="E343" t="n">
         <v>-0.9066128150253354</v>
@@ -29081,7 +29125,7 @@
         <v>-3.413875753060835</v>
       </c>
       <c r="D344" t="n">
-        <v>-0.6341820370707725</v>
+        <v>-0.635043370844573</v>
       </c>
       <c r="E344" t="n">
         <v>-0.08090932569779714</v>
@@ -29099,7 +29143,7 @@
         <v>-57.7276350248605</v>
       </c>
       <c r="D345" t="n">
-        <v>-1.023423908690197</v>
+        <v>-1.020757240380459</v>
       </c>
       <c r="E345" t="n">
         <v>-1.031798952017108</v>
@@ -29117,7 +29161,7 @@
         <v>25.86508835841583</v>
       </c>
       <c r="D346" t="n">
-        <v>-0.5798692177750389</v>
+        <v>-0.5812228309093332</v>
       </c>
       <c r="E346" t="n">
         <v>0.4316875487636982</v>
@@ -29135,10 +29179,10 @@
         <v>-62.85710548346589</v>
       </c>
       <c r="D347" t="n">
-        <v>-0.6522863101693505</v>
+        <v>-0.6529835508229863</v>
       </c>
       <c r="E347" t="n">
-        <v>-1.121602351984153</v>
+        <v>-1.121602351984154</v>
       </c>
       <c r="F347" t="inlineStr"/>
     </row>
@@ -29153,10 +29197,10 @@
         <v>-65.30862448172402</v>
       </c>
       <c r="D348" t="n">
-        <v>0.1805102523652325</v>
+        <v>0.172264728184025</v>
       </c>
       <c r="E348" t="n">
-        <v>-1.164521936550245</v>
+        <v>-1.164521936550246</v>
       </c>
       <c r="F348" t="inlineStr"/>
     </row>
@@ -29171,7 +29215,7 @@
         <v>-9.094090525330376</v>
       </c>
       <c r="D349" t="n">
-        <v>0.2981880275059887</v>
+        <v>0.2888758980437114</v>
       </c>
       <c r="E349" t="n">
         <v>-0.1803547954025836</v>
@@ -29189,7 +29233,7 @@
         <v>-44.38224321572371</v>
       </c>
       <c r="D350" t="n">
-        <v>0.3615529833510114</v>
+        <v>0.3516665279681578</v>
       </c>
       <c r="E350" t="n">
         <v>-0.7981565969193706</v>
@@ -29207,7 +29251,7 @@
         <v>-49.61391225874065</v>
       </c>
       <c r="D351" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E351" t="n">
         <v>-0.889749222582526</v>
@@ -29225,7 +29269,7 @@
         <v>-34.02711476035898</v>
       </c>
       <c r="D352" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E352" t="n">
         <v>-0.6168658087392437</v>
@@ -29243,7 +29287,7 @@
         <v>-27.62121096849221</v>
       </c>
       <c r="D353" t="n">
-        <v>0.3525008468017224</v>
+        <v>0.3426964379789512</v>
       </c>
       <c r="E353" t="n">
         <v>-0.5047154522816244</v>
@@ -29261,7 +29305,7 @@
         <v>-27.18241797699017</v>
       </c>
       <c r="D354" t="n">
-        <v>0.09904102342163196</v>
+        <v>0.09153391828116515</v>
       </c>
       <c r="E354" t="n">
         <v>-0.497033352767339</v>
@@ -29279,7 +29323,7 @@
         <v>-56.78751422532922</v>
       </c>
       <c r="D355" t="n">
-        <v>0.3615529833510114</v>
+        <v>0.3516665279681578</v>
       </c>
       <c r="E355" t="n">
         <v>-1.015339934491038</v>
@@ -29297,7 +29341,7 @@
         <v>-51.93366586772041</v>
       </c>
       <c r="D356" t="n">
-        <v>-0.01863675171912433</v>
+        <v>-0.02507725157852124</v>
       </c>
       <c r="E356" t="n">
         <v>-0.9303619452511434</v>
@@ -29315,7 +29359,7 @@
         <v>-3.186321023266397</v>
       </c>
       <c r="D357" t="n">
-        <v>0.1533538427173656</v>
+        <v>0.145354458216405</v>
       </c>
       <c r="E357" t="n">
         <v>-0.07692544693701008</v>
@@ -29333,7 +29377,7 @@
         <v>28.81505136681621</v>
       </c>
       <c r="D358" t="n">
-        <v>0.6059606701818129</v>
+        <v>0.5938589576767372</v>
       </c>
       <c r="E358" t="n">
         <v>0.4833335637021277</v>
@@ -29351,7 +29395,7 @@
         <v>-58.16764336542486</v>
       </c>
       <c r="D359" t="n">
-        <v>0.6240649432803909</v>
+        <v>0.6117991376551506</v>
       </c>
       <c r="E359" t="n">
         <v>-1.039502329064586</v>
@@ -29369,7 +29413,7 @@
         <v>-60.26294226729178</v>
       </c>
       <c r="D360" t="n">
-        <v>0.3434487102524335</v>
+        <v>0.3337263479897446</v>
       </c>
       <c r="E360" t="n">
         <v>-1.07618544613356</v>
@@ -29387,7 +29431,7 @@
         <v>-73.3463400977257</v>
       </c>
       <c r="D361" t="n">
-        <v>0.1443017061680767</v>
+        <v>0.1363843682271984</v>
       </c>
       <c r="E361" t="n">
         <v>-1.305240982718885</v>
@@ -29405,7 +29449,7 @@
         <v>-19.36185764321656</v>
       </c>
       <c r="D362" t="n">
-        <v>-0.00958461516983538</v>
+        <v>-0.01610716158931459</v>
       </c>
       <c r="E362" t="n">
         <v>-0.3601161186614183</v>
@@ -29423,7 +29467,7 @@
         <v>-25.82639515589067</v>
       </c>
       <c r="D363" t="n">
-        <v>-0.1634709365077474</v>
+        <v>-0.1685986914058275</v>
       </c>
       <c r="E363" t="n">
         <v>-0.4732929957947504</v>
@@ -29441,7 +29485,7 @@
         <v>-37.31621157151041</v>
       </c>
       <c r="D364" t="n">
-        <v>0.2076666620130993</v>
+        <v>0.1991749981516449</v>
       </c>
       <c r="E364" t="n">
         <v>-0.674449155567304</v>
@@ -29459,7 +29503,7 @@
         <v>41.31226293080026</v>
       </c>
       <c r="D365" t="n">
-        <v>0.2167187985623882</v>
+        <v>0.2081450881408516</v>
       </c>
       <c r="E365" t="n">
         <v>0.7021265361171343</v>
@@ -29477,10 +29521,10 @@
         <v>-31.45524453553957</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.1725230730570364</v>
+        <v>-0.1775687813950342</v>
       </c>
       <c r="E366" t="n">
-        <v>-0.5718391939401817</v>
+        <v>-0.5718391939401819</v>
       </c>
       <c r="F366" t="inlineStr"/>
     </row>
@@ -29495,7 +29539,7 @@
         <v>-36.74199317184198</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.1091581172120138</v>
+        <v>-0.1147781514705877</v>
       </c>
       <c r="E367" t="n">
         <v>-0.6643961169486002</v>
@@ -29513,7 +29557,7 @@
         <v>-68.25808123340028</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.5436606715778831</v>
+        <v>-0.5453424709525067</v>
       </c>
       <c r="E368" t="n">
         <v>-1.216159088278437</v>
@@ -29531,7 +29575,7 @@
         <v>-49.27316202983261</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.2177837558034811</v>
+        <v>-0.2224192313410674</v>
       </c>
       <c r="E369" t="n">
         <v>-0.8837835913653398</v>
@@ -29549,7 +29593,7 @@
         <v>-48.02446128056489</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.05484529791628009</v>
+        <v>-0.0609576115353478</v>
       </c>
       <c r="E370" t="n">
         <v>-0.8619221587417224</v>
@@ -29567,7 +29611,7 @@
         <v>7.2886144830473</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.235888028902059</v>
+        <v>-0.2403594113194807</v>
       </c>
       <c r="E371" t="n">
         <v>0.1064628444068581</v>
@@ -29585,7 +29629,7 @@
         <v>22.51951428377804</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.1544187999584585</v>
+        <v>-0.1596286014166209</v>
       </c>
       <c r="E372" t="n">
         <v>0.3731154350984293</v>
@@ -29603,7 +29647,7 @@
         <v>-23.25425745519446</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.1453666634091696</v>
+        <v>-0.1506585114274143</v>
       </c>
       <c r="E373" t="n">
         <v>-0.4282616982037047</v>
@@ -29621,10 +29665,10 @@
         <v>-31.86571294578916</v>
       </c>
       <c r="D374" t="n">
-        <v>-1.141101683830954</v>
+        <v>-1.137368410240145</v>
       </c>
       <c r="E374" t="n">
-        <v>-0.5790254052883027</v>
+        <v>-0.5790254052883028</v>
       </c>
       <c r="F374" t="inlineStr"/>
     </row>
@@ -29639,7 +29683,7 @@
         <v>-23.23913423190009</v>
       </c>
       <c r="D375" t="n">
-        <v>-0.8423811777044182</v>
+        <v>-0.8413554405963258</v>
       </c>
       <c r="E375" t="n">
         <v>-0.427996930742569</v>
@@ -29657,10 +29701,10 @@
         <v>-3.069505442046963</v>
       </c>
       <c r="D376" t="n">
-        <v>-0.2811487116485037</v>
+        <v>-0.285209861265514</v>
       </c>
       <c r="E376" t="n">
-        <v>-0.07488031646062095</v>
+        <v>-0.07488031646062096</v>
       </c>
       <c r="F376" t="inlineStr"/>
     </row>
@@ -29675,7 +29719,7 @@
         <v>-41.47311676031693</v>
       </c>
       <c r="D377" t="n">
-        <v>-0.4440871695357047</v>
+        <v>-0.4466714810712336</v>
       </c>
       <c r="E377" t="n">
         <v>-0.7472255215310084</v>
@@ -29693,7 +29737,7 @@
         <v>-55.76367798207686</v>
       </c>
       <c r="D378" t="n">
-        <v>-0.4802957157328605</v>
+        <v>-0.4825518410280601</v>
       </c>
       <c r="E378" t="n">
         <v>-0.9974152819571107</v>
@@ -29711,7 +29755,7 @@
         <v>-56.52739391968785</v>
       </c>
       <c r="D379" t="n">
-        <v>-0.3535658040428153</v>
+        <v>-0.3569705811791671</v>
       </c>
       <c r="E379" t="n">
         <v>-1.010785919016035</v>
@@ -29729,7 +29773,7 @@
         <v>11.67973051758761</v>
       </c>
       <c r="D380" t="n">
-        <v>-0.5889213543243279</v>
+        <v>-0.5901929208985399</v>
       </c>
       <c r="E380" t="n">
         <v>0.1833396200377565</v>
@@ -29747,7 +29791,7 @@
         <v>-1.734542832200986</v>
       </c>
       <c r="D381" t="n">
-        <v>-0.8061726315072624</v>
+        <v>-0.8054750806394992</v>
       </c>
       <c r="E381" t="n">
         <v>-0.05150866783519092</v>
@@ -29765,7 +29809,7 @@
         <v>-34.03320815500884</v>
       </c>
       <c r="D382" t="n">
-        <v>-0.4983999888314384</v>
+        <v>-0.5004920210064734</v>
       </c>
       <c r="E382" t="n">
         <v>-0.616972487890886</v>
@@ -29783,7 +29827,7 @@
         <v>-17.33596693177061</v>
       </c>
       <c r="D383" t="n">
-        <v>-0.2992529847470816</v>
+        <v>-0.3031500412439272</v>
       </c>
       <c r="E383" t="n">
         <v>-0.3246481546059305</v>
@@ -29801,7 +29845,7 @@
         <v>33.8122316208407</v>
       </c>
       <c r="D384" t="n">
-        <v>-0.1996794827049032</v>
+        <v>-0.2044790513626542</v>
       </c>
       <c r="E384" t="n">
         <v>0.5708209136500582</v>
@@ -29819,7 +29863,7 @@
         <v>12.52017725361879</v>
       </c>
       <c r="D385" t="n">
-        <v>0.05378034067518724</v>
+        <v>0.04668346833513194</v>
       </c>
       <c r="E385" t="n">
         <v>0.1980536095218339</v>
@@ -29837,7 +29881,7 @@
         <v>-12.40963804518202</v>
       </c>
       <c r="D386" t="n">
-        <v>-0.01863675171912433</v>
+        <v>-0.02507725157852124</v>
       </c>
       <c r="E386" t="n">
         <v>-0.2384012238668452</v>
@@ -29855,7 +29899,7 @@
         <v>-43.40230269861139</v>
       </c>
       <c r="D387" t="n">
-        <v>-0.4983999888314384</v>
+        <v>-0.5004920210064734</v>
       </c>
       <c r="E387" t="n">
         <v>-0.7810004419298209</v>
@@ -29873,7 +29917,7 @@
         <v>-53.47527210234867</v>
       </c>
       <c r="D388" t="n">
-        <v>-0.9510068162958858</v>
+        <v>-0.9489965204668057</v>
       </c>
       <c r="E388" t="n">
         <v>-0.9573513747443489</v>
@@ -29891,7 +29935,7 @@
         <v>-49.70600702105229</v>
       </c>
       <c r="D389" t="n">
-        <v>-0.5165042619300163</v>
+        <v>-0.5184322009848867</v>
       </c>
       <c r="E389" t="n">
         <v>-0.89136155719708</v>
@@ -29909,7 +29953,7 @@
         <v>-38.1786627967864</v>
       </c>
       <c r="D390" s="4" t="n">
-        <v>-0.06389743446556904</v>
+        <v>-0.06992770152455445</v>
       </c>
       <c r="E390" s="4" t="n">
         <v>-0.689548385197449</v>
@@ -29931,7 +29975,7 @@
         <v>-58.00682815802308</v>
       </c>
       <c r="D391" s="4" t="n">
-        <v>0.3343965737031445</v>
+        <v>0.3247562580005379</v>
       </c>
       <c r="E391" s="4" t="n">
         <v>-1.036686882030116</v>
@@ -29953,7 +29997,7 @@
         <v>-29.49839131091965</v>
       </c>
       <c r="D392" s="4" t="n">
-        <v>0.6421692163789686</v>
+        <v>0.6297393176335639</v>
       </c>
       <c r="E392" s="4" t="n">
         <v>-0.5375798928631028</v>
@@ -29975,10 +30019,10 @@
         <v>-72.50161308687896</v>
       </c>
       <c r="D393" s="4" t="n">
-        <v>0.940889722505504</v>
+        <v>0.9257522872773832</v>
       </c>
       <c r="E393" s="4" t="n">
-        <v>-1.290452056994442</v>
+        <v>-1.290452056994443</v>
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
@@ -29997,7 +30041,7 @@
         <v>-6.35974564763394</v>
       </c>
       <c r="D394" s="4" t="n">
-        <v>1.40254868651924</v>
+        <v>1.383226876726922</v>
       </c>
       <c r="E394" s="4" t="n">
         <v>-0.1324836810875251</v>
@@ -30019,7 +30063,7 @@
         <v>264.8362285475094</v>
       </c>
       <c r="D395" s="4" t="n">
-        <v>1.855155513983687</v>
+        <v>1.831731376187254</v>
       </c>
       <c r="E395" s="4" t="n">
         <v>4.615437324918305</v>
@@ -30041,7 +30085,7 @@
         <v>-10.32362599111615</v>
       </c>
       <c r="D396" s="4" t="n">
-        <v>2.959516172996938</v>
+        <v>2.926082354870465</v>
       </c>
       <c r="E396" s="4" t="n">
         <v>-0.2018806948299579</v>
@@ -30063,7 +30107,7 @@
         <v>182.3371930760852</v>
       </c>
       <c r="D397" s="4" t="n">
-        <v>3.077193948137695</v>
+        <v>3.042693524730152</v>
       </c>
       <c r="E397" s="4" t="n">
         <v>3.171098393809607</v>
@@ -30085,10 +30129,10 @@
         <v>109.523547976864</v>
       </c>
       <c r="D398" s="4" t="n">
-        <v>2.615534984123959</v>
+        <v>2.585218935280612</v>
       </c>
       <c r="E398" s="4" t="n">
-        <v>1.896324916377077</v>
+        <v>1.896324916377076</v>
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
@@ -30107,7 +30151,7 @@
         <v>27.26703734971326</v>
       </c>
       <c r="D399" s="4" t="n">
-        <v>2.054302518068044</v>
+        <v>2.0290733559498</v>
       </c>
       <c r="E399" s="4" t="n">
         <v>0.4562319509617194</v>
@@ -30129,7 +30173,7 @@
         <v>80.34657246515182</v>
       </c>
       <c r="D400" s="4" t="n">
-        <v>2.235345249053823</v>
+        <v>2.208475155733933</v>
       </c>
       <c r="E400" s="4" t="n">
         <v>1.3855135913384</v>
@@ -30151,7 +30195,7 @@
         <v>44.96951385190578</v>
       </c>
       <c r="D401" s="4" t="n">
-        <v>3.222028132926318</v>
+        <v>3.186214964557458</v>
       </c>
       <c r="E401" s="4" t="n">
         <v>0.7661552833140093</v>
@@ -30173,7 +30217,7 @@
         <v>111.9896470729044</v>
       </c>
       <c r="D402" s="4" t="n">
-        <v>3.701791370038632</v>
+        <v>3.66162973398541</v>
       </c>
       <c r="E402" s="4" t="n">
         <v>1.93949975971954</v>
@@ -30195,7 +30239,7 @@
         <v>-41.22906844415542</v>
       </c>
       <c r="D403" s="4" t="n">
-        <v>4.054824695460901</v>
+        <v>4.011463243564469</v>
       </c>
       <c r="E403" s="4" t="n">
         <v>-0.7429528838924062</v>
@@ -30217,7 +30261,7 @@
         <v>-56.29548055537562</v>
       </c>
       <c r="D404" t="n">
-        <v>3.656530687292187</v>
+        <v>3.616779284039376</v>
       </c>
       <c r="E404" t="n">
         <v>-1.00672573214468</v>
@@ -30235,7 +30279,7 @@
         <v>199.8064295745246</v>
       </c>
       <c r="D405" t="n">
-        <v>2.868994807504049</v>
+        <v>2.836381454978399</v>
       </c>
       <c r="E405" t="n">
         <v>3.476938313358492</v>
@@ -30253,7 +30297,7 @@
         <v>-37.85411262303218</v>
       </c>
       <c r="D406" t="n">
-        <v>1.456861505814974</v>
+        <v>1.437047416662162</v>
       </c>
       <c r="E406" t="n">
         <v>-0.6838663739063754</v>
@@ -30271,7 +30315,7 @@
         <v>49.82733361239012</v>
       </c>
       <c r="D407" t="n">
-        <v>1.112880316941994</v>
+        <v>1.09618399707231</v>
       </c>
       <c r="E407" t="n">
         <v>0.8512028012671974</v>
@@ -30289,10 +30333,10 @@
         <v>-0.102885095214933</v>
       </c>
       <c r="D408" t="n">
-        <v>0.5788042605339461</v>
+        <v>0.5669486877091173</v>
       </c>
       <c r="E408" t="n">
-        <v>-0.02294267578077512</v>
+        <v>-0.02294267578077513</v>
       </c>
       <c r="F408" t="inlineStr"/>
     </row>
@@ -30307,7 +30351,7 @@
         <v>92.69113163224689</v>
       </c>
       <c r="D409" t="n">
-        <v>0.4068136660974561</v>
+        <v>0.3965169779141911</v>
       </c>
       <c r="E409" t="n">
         <v>1.601634025844401</v>
@@ -30325,7 +30369,7 @@
         <v>-38.81159506014272</v>
       </c>
       <c r="D410" t="n">
-        <v>-0.1363145268598806</v>
+        <v>-0.1416884214382076</v>
       </c>
       <c r="E410" t="n">
         <v>-0.7006293475807841</v>
@@ -30343,7 +30387,7 @@
         <v>56.58932782160636</v>
       </c>
       <c r="D411" t="n">
-        <v>-0.5798692177750389</v>
+        <v>-0.5812228309093332</v>
       </c>
       <c r="E411" t="n">
         <v>0.9695873548864395</v>
@@ -30361,7 +30405,7 @@
         <v>5.12698109604736</v>
       </c>
       <c r="D412" t="n">
-        <v>-0.5708170812257499</v>
+        <v>-0.5722527409201267</v>
       </c>
       <c r="E412" t="n">
         <v>0.06861838673789783</v>
@@ -30379,7 +30423,7 @@
         <v>-17.84499342455629</v>
       </c>
       <c r="D413" t="n">
-        <v>0.008519657928742501</v>
+        <v>0.001833018389098698</v>
       </c>
       <c r="E413" t="n">
         <v>-0.3335598561342561</v>
@@ -30397,7 +30441,7 @@
         <v>-38.06196795380081</v>
       </c>
       <c r="D414" t="n">
-        <v>-0.7880683584086847</v>
+        <v>-0.7875349006610861</v>
       </c>
       <c r="E414" t="n">
         <v>-0.6875053685267621</v>
@@ -30415,7 +30459,7 @@
         <v>10.0471468053975</v>
       </c>
       <c r="D415" t="n">
-        <v>-0.6432341736200615</v>
+        <v>-0.6440134608337796</v>
       </c>
       <c r="E415" t="n">
         <v>0.1547574166176099</v>
@@ -30433,7 +30477,7 @@
         <v>-34.65915225324437</v>
       </c>
       <c r="D416" t="n">
-        <v>-0.3535658040428153</v>
+        <v>-0.3569705811791671</v>
       </c>
       <c r="E416" t="n">
         <v>-0.6279311060688215</v>
@@ -30451,7 +30495,7 @@
         <v>-21.54704520438759</v>
       </c>
       <c r="D417" t="n">
-        <v>-0.2902008481977927</v>
+        <v>-0.2941799512547206</v>
       </c>
       <c r="E417" t="n">
         <v>-0.3983729473423668</v>
@@ -30469,7 +30513,7 @@
         <v>45.33484421385828</v>
       </c>
       <c r="D418" t="n">
-        <v>0.1533538427173656</v>
+        <v>0.145354458216405</v>
       </c>
       <c r="E418" t="n">
         <v>0.7725512473573319</v>
@@ -30487,7 +30531,7 @@
         <v>-14.2554416073671</v>
       </c>
       <c r="D419" t="n">
-        <v>-0.2449401654513479</v>
+        <v>-0.2493295013086874</v>
       </c>
       <c r="E419" t="n">
         <v>-0.2707163403868008</v>
@@ -30505,7 +30549,7 @@
         <v>-0.4725321438912806</v>
       </c>
       <c r="D420" t="n">
-        <v>0.09904102342163196</v>
+        <v>0.09153391828116515</v>
       </c>
       <c r="E420" t="n">
         <v>-0.02941421354023911</v>
@@ -30523,7 +30567,7 @@
         <v>48.95078281182334</v>
       </c>
       <c r="D421" t="n">
-        <v>-0.1453666634091696</v>
+        <v>-0.1506585114274143</v>
       </c>
       <c r="E421" t="n">
         <v>0.8358567255328742</v>
@@ -30541,7 +30585,7 @@
         <v>-37.97504721425341</v>
       </c>
       <c r="D422" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E422" t="n">
         <v>-0.685983617304682</v>
@@ -30559,7 +30603,7 @@
         <v>-65.85798084480801</v>
       </c>
       <c r="D423" t="n">
-        <v>-1.032476045239486</v>
+        <v>-1.029727330369665</v>
       </c>
       <c r="E423" t="n">
         <v>-1.174139706960778</v>
@@ -30577,7 +30621,7 @@
         <v>-41.307046018713</v>
       </c>
       <c r="D424" t="n">
-        <v>-0.5889213543243279</v>
+        <v>-0.5901929208985399</v>
       </c>
       <c r="E424" t="n">
         <v>-0.7443180640553423</v>
@@ -30595,7 +30639,7 @@
         <v>-63.07969872512472</v>
       </c>
       <c r="D425" t="n">
-        <v>-1.023423908690197</v>
+        <v>-1.020757240380459</v>
       </c>
       <c r="E425" t="n">
         <v>-1.125499368269161</v>
@@ -30613,7 +30657,7 @@
         <v>-9.848745530437904</v>
       </c>
       <c r="D426" t="n">
-        <v>-1.485082872703933</v>
+        <v>-1.478231829829998</v>
       </c>
       <c r="E426" t="n">
         <v>-0.1935667996060798</v>
@@ -30631,7 +30675,7 @@
         <v>-60.67306129084701</v>
       </c>
       <c r="D427" t="n">
-        <v>-0.9329025431973078</v>
+        <v>-0.9310563404883924</v>
       </c>
       <c r="E427" t="n">
         <v>-1.083365540648899</v>
@@ -30649,7 +30693,7 @@
         <v>-59.8583489883613</v>
       </c>
       <c r="D428" t="n">
-        <v>-1.050580318338064</v>
+        <v>-1.047667510348079</v>
       </c>
       <c r="E428" t="n">
         <v>-1.069102092726034</v>
@@ -30667,7 +30711,7 @@
         <v>-9.648157285459437</v>
       </c>
       <c r="D429" t="n">
-        <v>-0.896693997000152</v>
+        <v>-0.8951759805315658</v>
       </c>
       <c r="E429" t="n">
         <v>-0.1900550323509884</v>
@@ -30685,7 +30729,7 @@
         <v>44.80104138376678</v>
       </c>
       <c r="D430" t="n">
-        <v>-0.6794427198172173</v>
+        <v>-0.6798938207906062</v>
       </c>
       <c r="E430" t="n">
         <v>0.7632057779875208</v>
@@ -30703,7 +30747,7 @@
         <v>-45.2569066555044</v>
       </c>
       <c r="D431" t="n">
-        <v>-0.6160777639721947</v>
+        <v>-0.6171031908661599</v>
       </c>
       <c r="E431" t="n">
         <v>-0.8134696299805907</v>
@@ -30721,7 +30765,7 @@
         <v>-48.00914260367061</v>
       </c>
       <c r="D432" t="n">
-        <v>-0.4983999888314384</v>
+        <v>-0.5004920210064734</v>
       </c>
       <c r="E432" t="n">
         <v>-0.8616539694073252</v>
@@ -30739,7 +30783,7 @@
         <v>18.29448072826217</v>
       </c>
       <c r="D433" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E433" t="n">
         <v>0.2991463224342467</v>
@@ -30757,7 +30801,7 @@
         <v>51.88413389835523</v>
       </c>
       <c r="D434" t="n">
-        <v>0.2167187985623882</v>
+        <v>0.2081450881408516</v>
       </c>
       <c r="E434" t="n">
         <v>0.8872119098532475</v>
@@ -30775,7 +30819,7 @@
         <v>-23.95963727402404</v>
       </c>
       <c r="D435" t="n">
-        <v>0.1261974330694988</v>
+        <v>0.1184441882487851</v>
       </c>
       <c r="E435" t="n">
         <v>-0.4406110248077334</v>
@@ -30793,7 +30837,7 @@
         <v>-37.36872255107887</v>
       </c>
       <c r="D436" t="n">
-        <v>-0.4440871695357047</v>
+        <v>-0.4466714810712336</v>
       </c>
       <c r="E436" t="n">
         <v>-0.6753684833105678</v>
@@ -30811,7 +30855,7 @@
         <v>-13.47585562281951</v>
       </c>
       <c r="D437" t="n">
-        <v>-0.5527128081271721</v>
+        <v>-0.5543125609417133</v>
       </c>
       <c r="E437" t="n">
         <v>-0.2570678609688953</v>
@@ -30829,7 +30873,7 @@
         <v>-51.79605332056671</v>
       </c>
       <c r="D438" t="n">
-        <v>-0.8514333142537072</v>
+        <v>-0.8503255305855325</v>
       </c>
       <c r="E438" t="n">
         <v>-0.9279527151537567</v>
@@ -30847,10 +30891,10 @@
         <v>-74.1993171841977</v>
       </c>
       <c r="D439" t="n">
-        <v>-0.7609119487608178</v>
+        <v>-0.7606246306934662</v>
       </c>
       <c r="E439" t="n">
-        <v>-1.320174345349068</v>
+        <v>-1.320174345349069</v>
       </c>
       <c r="F439" t="inlineStr"/>
     </row>
@@ -30865,7 +30909,7 @@
         <v>-59.72879013625273</v>
       </c>
       <c r="D440" t="n">
-        <v>-0.22683589235277</v>
+        <v>-0.2313893213302741</v>
       </c>
       <c r="E440" t="n">
         <v>-1.066833861432166</v>
@@ -30883,7 +30927,7 @@
         <v>-41.53034501081716</v>
       </c>
       <c r="D441" t="n">
-        <v>0.1261974330694988</v>
+        <v>0.1184441882487851</v>
       </c>
       <c r="E441" t="n">
         <v>-0.7482274361556389</v>
@@ -30901,7 +30945,7 @@
         <v>-21.615268633933</v>
       </c>
       <c r="D442" t="n">
-        <v>0.3796572564495893</v>
+        <v>0.3696067079465711</v>
       </c>
       <c r="E442" t="n">
         <v>-0.3995673583405454</v>
@@ -30919,7 +30963,7 @@
         <v>55.75293009627458</v>
       </c>
       <c r="D443" t="n">
-        <v>0.4430222122946119</v>
+        <v>0.4323973378710177</v>
       </c>
       <c r="E443" t="n">
         <v>0.9549442528224659</v>
@@ -30937,7 +30981,7 @@
         <v>-34.99756649026288</v>
       </c>
       <c r="D444" t="n">
-        <v>0.5425957143367902</v>
+        <v>0.5310683277522907</v>
       </c>
       <c r="E444" t="n">
         <v>-0.633855840274188</v>
@@ -30955,7 +30999,7 @@
         <v>-22.74244419266925</v>
       </c>
       <c r="D445" t="n">
-        <v>0.7598469915197249</v>
+        <v>0.7463504874932502</v>
       </c>
       <c r="E445" t="n">
         <v>-0.4193012077410136</v>
@@ -30973,7 +31017,7 @@
         <v>41.37658595529119</v>
       </c>
       <c r="D446" t="n">
-        <v>1.112880316941994</v>
+        <v>1.09618399707231</v>
       </c>
       <c r="E446" t="n">
         <v>0.7032526613852423</v>
@@ -30991,7 +31035,7 @@
         <v>41.43147215510466</v>
       </c>
       <c r="D447" t="n">
-        <v>1.094776043843416</v>
+        <v>1.078243817093896</v>
       </c>
       <c r="E447" t="n">
         <v>0.7042135729246102</v>
@@ -31009,7 +31053,7 @@
         <v>54.92171090318885</v>
       </c>
       <c r="D448" t="n">
-        <v>1.520226461659996</v>
+        <v>1.499838046586608</v>
       </c>
       <c r="E448" t="n">
         <v>0.9403918131000121</v>
@@ -31027,7 +31071,7 @@
         <v>37.62784075470877</v>
       </c>
       <c r="D449" t="n">
-        <v>1.628852100251464</v>
+        <v>1.607479126457088</v>
       </c>
       <c r="E449" t="n">
         <v>0.6376220924329118</v>
@@ -31045,7 +31089,7 @@
         <v>12.03602579255247</v>
       </c>
       <c r="D450" t="n">
-        <v>1.592643554054308</v>
+        <v>1.571598766500262</v>
       </c>
       <c r="E450" t="n">
         <v>0.1895774037119678</v>
@@ -31063,7 +31107,7 @@
         <v>-66.46073809136726</v>
       </c>
       <c r="D451" t="n">
-        <v>1.103828180392705</v>
+        <v>1.087213907083103</v>
       </c>
       <c r="E451" t="n">
         <v>-1.184692384967722</v>
@@ -31081,7 +31125,7 @@
         <v>-21.4225561961521</v>
       </c>
       <c r="D452" t="n">
-        <v>1.14908886313915</v>
+        <v>1.132064357029136</v>
       </c>
       <c r="E452" t="n">
         <v>-0.3961934755453674</v>
@@ -31099,7 +31143,7 @@
         <v>194.6825065472351</v>
       </c>
       <c r="D453" t="n">
-        <v>0.9589939956040816</v>
+        <v>0.9436924672557964</v>
       </c>
       <c r="E453" t="n">
         <v>3.387232034175603</v>
@@ -31117,7 +31161,7 @@
         <v>-13.58013129676627</v>
       </c>
       <c r="D454" t="n">
-        <v>1.212453818984172</v>
+        <v>1.194854986953583</v>
       </c>
       <c r="E454" t="n">
         <v>-0.2588934509844425</v>
@@ -31135,7 +31179,7 @@
         <v>-9.369767685223948</v>
       </c>
       <c r="D455" t="n">
-        <v>1.529278598209285</v>
+        <v>1.508808136575815</v>
       </c>
       <c r="E455" t="n">
         <v>-0.1851811700647417</v>
@@ -31153,7 +31197,7 @@
         <v>-21.50544921357591</v>
       </c>
       <c r="D456" t="n">
-        <v>1.248662365181328</v>
+        <v>1.230735346910409</v>
       </c>
       <c r="E456" t="n">
         <v>-0.3976447120537477</v>
@@ -31171,7 +31215,7 @@
         <v>-49.50109143084615</v>
       </c>
       <c r="D457" t="n">
-        <v>0.8232119473647476</v>
+        <v>0.8091411174176968</v>
       </c>
       <c r="E457" t="n">
         <v>-0.8877740296237625</v>
@@ -31189,7 +31233,7 @@
         <v>12.87692184192628</v>
       </c>
       <c r="D458" t="n">
-        <v>0.2348230716609661</v>
+        <v>0.2260852681192649</v>
       </c>
       <c r="E458" t="n">
         <v>0.2042992594789577</v>
@@ -31207,7 +31251,7 @@
         <v>-13.86713632790893</v>
       </c>
       <c r="D459" t="n">
-        <v>-0.06389743446556904</v>
+        <v>-0.06992770152455445</v>
       </c>
       <c r="E459" t="n">
         <v>-0.2639181465767564</v>
@@ -31225,7 +31269,7 @@
         <v>-74.87110941378651</v>
       </c>
       <c r="D460" t="n">
-        <v>-0.5165042619300163</v>
+        <v>-0.5184322009848867</v>
       </c>
       <c r="E460" t="n">
         <v>-1.331935642499597</v>
@@ -31243,7 +31287,7 @@
         <v>-1.900900998815328</v>
       </c>
       <c r="D461" t="n">
-        <v>-0.5346085350285942</v>
+        <v>-0.5363723809633</v>
       </c>
       <c r="E461" t="n">
         <v>-0.05442115735917073</v>
@@ -31261,10 +31305,10 @@
         <v>0.3306353884591719</v>
       </c>
       <c r="D462" t="n">
-        <v>-0.9238504066480187</v>
+        <v>-0.9220862504991857</v>
       </c>
       <c r="E462" t="n">
-        <v>-0.01535288387077799</v>
+        <v>-0.015352883870778</v>
       </c>
       <c r="F462" t="inlineStr"/>
     </row>
@@ -31279,7 +31323,7 @@
         <v>-12.12810925052837</v>
       </c>
       <c r="D463" t="n">
-        <v>-1.285935868619576</v>
+        <v>-1.280889850067451</v>
       </c>
       <c r="E463" t="n">
         <v>-0.2334724026264174</v>
@@ -31297,7 +31341,7 @@
         <v>-2.139880373993219</v>
       </c>
       <c r="D464" t="n">
-        <v>-1.023423908690197</v>
+        <v>-1.020757240380459</v>
       </c>
       <c r="E464" t="n">
         <v>-0.05860505130810079</v>
@@ -31315,7 +31359,7 @@
         <v>7.346187421717862</v>
       </c>
       <c r="D465" t="n">
-        <v>-1.104893137633798</v>
+        <v>-1.101488050283319</v>
       </c>
       <c r="E465" t="n">
         <v>0.1074707936055979</v>
@@ -31333,7 +31377,7 @@
         <v>82.42009346232011</v>
       </c>
       <c r="D466" t="n">
-        <v>-0.9510068162958858</v>
+        <v>-0.9489965204668057</v>
       </c>
       <c r="E466" t="n">
         <v>1.42181543515473</v>
@@ -31351,7 +31395,7 @@
         <v>-36.62358727501047</v>
       </c>
       <c r="D467" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E467" t="n">
         <v>-0.6623231442709278</v>
@@ -31369,7 +31413,7 @@
         <v>-6.36840257027916</v>
       </c>
       <c r="D468" t="n">
-        <v>-0.6522863101693505</v>
+        <v>-0.6529835508229863</v>
       </c>
       <c r="E468" t="n">
         <v>-0.132635240803692</v>
@@ -31387,10 +31431,10 @@
         <v>-31.98132975209865</v>
       </c>
       <c r="D469" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E469" t="n">
-        <v>-0.5810495484008739</v>
+        <v>-0.581049548400874</v>
       </c>
       <c r="F469" t="inlineStr"/>
     </row>
@@ -31405,7 +31449,7 @@
         <v>84.07221351405022</v>
       </c>
       <c r="D470" t="n">
-        <v>-0.05484529791628009</v>
+        <v>-0.0609576115353478</v>
       </c>
       <c r="E470" t="n">
         <v>1.45073966797689</v>
@@ -31423,7 +31467,7 @@
         <v>46.15295042356846</v>
       </c>
       <c r="D471" t="n">
-        <v>0.1624059792666546</v>
+        <v>0.1543245482056117</v>
       </c>
       <c r="E471" t="n">
         <v>0.7868741135789069</v>
@@ -31441,7 +31485,7 @@
         <v>11.55718923047547</v>
       </c>
       <c r="D472" t="n">
-        <v>0.08093675032305407</v>
+        <v>0.07359373830275187</v>
       </c>
       <c r="E472" t="n">
         <v>0.1811942476630026</v>
@@ -31459,7 +31503,7 @@
         <v>-29.0449847297547</v>
       </c>
       <c r="D473" t="n">
-        <v>0.1352495696187877</v>
+        <v>0.1274142782379917</v>
       </c>
       <c r="E473" t="n">
         <v>-0.5296419482185953</v>
@@ -31477,7 +31521,7 @@
         <v>-50.02767762301581</v>
       </c>
       <c r="D474" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E474" t="n">
         <v>-0.8969931548364247</v>
@@ -31495,7 +31539,7 @@
         <v>27.91416029913837</v>
       </c>
       <c r="D475" t="n">
-        <v>-0.7609119487608178</v>
+        <v>-0.7606246306934662</v>
       </c>
       <c r="E475" t="n">
         <v>0.4675613545568961</v>
@@ -31513,7 +31557,7 @@
         <v>-18.42110945563689</v>
       </c>
       <c r="D476" t="n">
-        <v>-0.4983999888314384</v>
+        <v>-0.5004920210064734</v>
       </c>
       <c r="E476" t="n">
         <v>-0.343646117237439</v>
@@ -31531,7 +31575,7 @@
         <v>-56.4181880289976</v>
       </c>
       <c r="D477" t="n">
-        <v>-0.05484529791628009</v>
+        <v>-0.0609576115353478</v>
       </c>
       <c r="E477" t="n">
         <v>-1.008874014003703</v>
@@ -31549,7 +31593,7 @@
         <v>13.75619258107717</v>
       </c>
       <c r="D478" t="n">
-        <v>-0.3716700771413932</v>
+        <v>-0.3749107611575804</v>
       </c>
       <c r="E478" t="n">
         <v>0.2196929541116694</v>
@@ -31567,7 +31611,7 @@
         <v>7.092402678945161</v>
       </c>
       <c r="D479" t="n">
-        <v>-0.2177837558034811</v>
+        <v>-0.2224192313410674</v>
       </c>
       <c r="E479" t="n">
         <v>0.1030276970043657</v>
@@ -31585,7 +31629,7 @@
         <v>-45.14437797642884</v>
       </c>
       <c r="D480" t="n">
-        <v>-0.0005324786205464267</v>
+        <v>-0.00713707160010793</v>
       </c>
       <c r="E480" t="n">
         <v>-0.811499551771478</v>
@@ -31603,7 +31647,7 @@
         <v>-65.09171081238325</v>
       </c>
       <c r="D481" t="n">
-        <v>-0.1453666634091696</v>
+        <v>-0.1506585114274143</v>
       </c>
       <c r="E481" t="n">
         <v>-1.160724354487277</v>
@@ -31621,7 +31665,7 @@
         <v>-44.90825436124501</v>
       </c>
       <c r="D482" t="n">
-        <v>-0.2177837558034811</v>
+        <v>-0.2224192313410674</v>
       </c>
       <c r="E482" t="n">
         <v>-0.8073656545929798</v>
@@ -31639,7 +31683,7 @@
         <v>-3.419842217111582</v>
       </c>
       <c r="D483" t="n">
-        <v>0.07188461377376512</v>
+        <v>0.06462364831354522</v>
       </c>
       <c r="E483" t="n">
         <v>-0.08101378263187295</v>
@@ -31657,7 +31701,7 @@
         <v>-53.35115524155051</v>
       </c>
       <c r="D484" t="n">
-        <v>-0.1815752096063253</v>
+        <v>-0.1865388713842409</v>
       </c>
       <c r="E484" t="n">
         <v>-0.9551784182602713</v>
@@ -31675,7 +31719,7 @@
         <v>-35.10960884261323</v>
       </c>
       <c r="D485" t="n">
-        <v>-0.2539923020006369</v>
+        <v>-0.258299591297894</v>
       </c>
       <c r="E485" t="n">
         <v>-0.6358174041943947</v>
@@ -31693,7 +31737,7 @@
         <v>-49.75838183151061</v>
       </c>
       <c r="D486" t="n">
-        <v>-0.0005324786205464267</v>
+        <v>-0.00713707160010793</v>
       </c>
       <c r="E486" t="n">
         <v>-0.8922785009809937</v>
@@ -31711,7 +31755,7 @@
         <v>33.89692732888962</v>
       </c>
       <c r="D487" t="n">
-        <v>-0.05484529791628009</v>
+        <v>-0.0609576115353478</v>
       </c>
       <c r="E487" t="n">
         <v>0.5723037104819707</v>
@@ -31729,10 +31773,10 @@
         <v>-31.26902895640345</v>
       </c>
       <c r="D488" t="n">
-        <v>-0.3807222136906822</v>
+        <v>-0.383880851146787</v>
       </c>
       <c r="E488" t="n">
-        <v>-0.5685790538792909</v>
+        <v>-0.568579053879291</v>
       </c>
       <c r="F488" t="inlineStr"/>
     </row>
@@ -31747,7 +31791,7 @@
         <v>-53.6000303639883</v>
       </c>
       <c r="D489" t="n">
-        <v>-0.1815752096063253</v>
+        <v>-0.1865388713842409</v>
       </c>
       <c r="E489" t="n">
         <v>-0.9595355604531138</v>
@@ -31765,7 +31809,7 @@
         <v>114.167314409867</v>
       </c>
       <c r="D490" t="n">
-        <v>-0.22683589235277</v>
+        <v>-0.2313893213302741</v>
       </c>
       <c r="E490" t="n">
         <v>1.977624929254017</v>
@@ -31783,7 +31827,7 @@
         <v>90.81597948932608</v>
       </c>
       <c r="D491" t="n">
-        <v>-0.4169307598878378</v>
+        <v>-0.4197612111036136</v>
       </c>
       <c r="E491" t="n">
         <v>1.568805093647847</v>
@@ -31801,7 +31845,7 @@
         <v>-40.96736632638602</v>
       </c>
       <c r="D492" t="n">
-        <v>-0.3716700771413932</v>
+        <v>-0.3749107611575804</v>
       </c>
       <c r="E492" t="n">
         <v>-0.7383711750895334</v>
@@ -31819,7 +31863,7 @@
         <v>-21.81068158653362</v>
       </c>
       <c r="D493" t="n">
-        <v>-0.235888028902059</v>
+        <v>-0.2403594113194807</v>
       </c>
       <c r="E493" t="n">
         <v>-0.4029885199756015</v>
@@ -31837,7 +31881,7 @@
         <v>-37.13216188468314</v>
       </c>
       <c r="D494" t="n">
-        <v>-0.2720965750992148</v>
+        <v>-0.2762397712763073</v>
       </c>
       <c r="E494" t="n">
         <v>-0.6712269345264886</v>
@@ -31855,7 +31899,7 @@
         <v>-5.090099269308026</v>
       </c>
       <c r="D495" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E495" t="n">
         <v>-0.1102555461465722</v>
@@ -31873,7 +31917,7 @@
         <v>-25.40099293488638</v>
       </c>
       <c r="D496" t="n">
-        <v>0.02662393102732041</v>
+        <v>0.01977319836751201</v>
       </c>
       <c r="E496" t="n">
         <v>-0.4658453330958401</v>
@@ -31891,7 +31935,7 @@
         <v>-52.66767381451815</v>
       </c>
       <c r="D497" t="n">
-        <v>-0.05484529791628009</v>
+        <v>-0.0609576115353478</v>
       </c>
       <c r="E497" t="n">
         <v>-0.9432124743178782</v>
@@ -31909,7 +31953,7 @@
         <v>-18.30463338370162</v>
       </c>
       <c r="D498" t="n">
-        <v>-0.08200170756414694</v>
+        <v>-0.08786788150296776</v>
       </c>
       <c r="E498" t="n">
         <v>-0.3416069306666215</v>
@@ -31927,7 +31971,7 @@
         <v>-39.63583157210209</v>
       </c>
       <c r="D499" t="n">
-        <v>0.4068136660974561</v>
+        <v>0.3965169779141911</v>
       </c>
       <c r="E499" t="n">
         <v>-0.7150595391080112</v>
@@ -31945,7 +31989,7 @@
         <v>-42.62702165792145</v>
       </c>
       <c r="D500" t="n">
-        <v>0.7598469915197249</v>
+        <v>0.7463504874932502</v>
       </c>
       <c r="E500" t="n">
         <v>-0.7674273306416675</v>
@@ -31963,7 +32007,7 @@
         <v>-48.33377614149618</v>
       </c>
       <c r="D501" t="n">
-        <v>0.5516478508860791</v>
+        <v>0.5400384177414974</v>
       </c>
       <c r="E501" t="n">
         <v>-0.8673374401818099</v>
@@ -31981,7 +32025,7 @@
         <v>-35.213193358369</v>
       </c>
       <c r="D502" t="n">
-        <v>0.6331170798296798</v>
+        <v>0.6207692276443573</v>
       </c>
       <c r="E502" t="n">
         <v>-0.6376308938662578</v>
@@ -31999,7 +32043,7 @@
         <v>-57.36317496860611</v>
       </c>
       <c r="D503" t="n">
-        <v>0.8051076742661697</v>
+        <v>0.7912009374392834</v>
       </c>
       <c r="E503" t="n">
         <v>-1.025418224714368</v>
@@ -32017,7 +32061,7 @@
         <v>10.80170284073756</v>
       </c>
       <c r="D504" t="n">
-        <v>0.8684726301111922</v>
+        <v>0.8539915673637301</v>
       </c>
       <c r="E504" t="n">
         <v>0.1679676881234166</v>
@@ -32035,7 +32079,7 @@
         <v>-9.356558865086898</v>
       </c>
       <c r="D505" t="n">
-        <v>0.9680461321533707</v>
+        <v>0.952662557245003</v>
       </c>
       <c r="E505" t="n">
         <v>-0.1849499187167843</v>
@@ -32053,7 +32097,7 @@
         <v>-7.257263812545668</v>
       </c>
       <c r="D506" t="n">
-        <v>0.6421692163789686</v>
+        <v>0.6297393176335639</v>
       </c>
       <c r="E506" t="n">
         <v>-0.1481968396663095</v>
@@ -32071,7 +32115,7 @@
         <v>-12.37154667986376</v>
       </c>
       <c r="D507" t="n">
-        <v>0.7688991280690138</v>
+        <v>0.7553205774824568</v>
       </c>
       <c r="E507" t="n">
         <v>-0.2377343452596729</v>
@@ -32089,7 +32133,7 @@
         <v>50.16230666412069</v>
       </c>
       <c r="D508" t="n">
-        <v>1.339183730674217</v>
+        <v>1.320436246802476</v>
       </c>
       <c r="E508" t="n">
         <v>0.8570672894605695</v>
@@ -32107,7 +32151,7 @@
         <v>73.32543555521742</v>
       </c>
       <c r="D509" t="n">
-        <v>2.199136702856667</v>
+        <v>2.172594795777107</v>
       </c>
       <c r="E509" t="n">
         <v>1.2625921375091</v>
@@ -32125,7 +32169,7 @@
         <v>86.28985203692345</v>
       </c>
       <c r="D510" t="n">
-        <v>2.226293112504534</v>
+        <v>2.199505065744727</v>
       </c>
       <c r="E510" t="n">
         <v>1.489564626782883</v>
@@ -32143,7 +32187,7 @@
         <v>84.5716143716469</v>
       </c>
       <c r="D511" t="n">
-        <v>0.9861504052519485</v>
+        <v>0.9706027372234163</v>
       </c>
       <c r="E511" t="n">
         <v>1.459482850206042</v>
@@ -32161,7 +32205,7 @@
         <v>166.696897065492</v>
       </c>
       <c r="D512" t="n">
-        <v>0.1533538427173656</v>
+        <v>0.145354458216405</v>
       </c>
       <c r="E512" t="n">
         <v>2.897278363150117</v>
@@ -32179,7 +32223,7 @@
         <v>-59.66333927961437</v>
       </c>
       <c r="D513" t="n">
-        <v>0.08998888687234299</v>
+        <v>0.0825638282919585</v>
       </c>
       <c r="E513" t="n">
         <v>-1.065687990819534</v>
@@ -32197,7 +32241,7 @@
         <v>16.50949138891751</v>
       </c>
       <c r="D514" t="n">
-        <v>0.2438752082102551</v>
+        <v>0.2350553581084714</v>
       </c>
       <c r="E514" t="n">
         <v>0.2678959013875366</v>
@@ -32215,7 +32259,7 @@
         <v>-61.11082042695688</v>
       </c>
       <c r="D515" t="n">
-        <v>0.2257709351116772</v>
+        <v>0.2171151781300582</v>
       </c>
       <c r="E515" t="n">
         <v>-1.091029540101972</v>
@@ -32233,7 +32277,7 @@
         <v>-43.5364133146867</v>
       </c>
       <c r="D516" t="n">
-        <v>0.1533538427173656</v>
+        <v>0.145354458216405</v>
       </c>
       <c r="E516" t="n">
         <v>-0.7833483625178091</v>
@@ -32251,7 +32295,7 @@
         <v>-52.61134125696088</v>
       </c>
       <c r="D517" t="n">
-        <v>0.1261974330694988</v>
+        <v>0.1184441882487851</v>
       </c>
       <c r="E517" t="n">
         <v>-0.9422262408970393</v>
@@ -32269,7 +32313,7 @@
         <v>-13.72149716714479</v>
       </c>
       <c r="D518" t="n">
-        <v>0.2076666620130993</v>
+        <v>0.1991749981516449</v>
       </c>
       <c r="E518" t="n">
         <v>-0.2613683917998232</v>
@@ -32287,7 +32331,7 @@
         <v>33.4349800588047</v>
       </c>
       <c r="D519" t="n">
-        <v>0.4882828950410565</v>
+        <v>0.4772477878170509</v>
       </c>
       <c r="E519" t="n">
         <v>0.5642162410650207</v>
@@ -32305,7 +32349,7 @@
         <v>32.77162497613138</v>
       </c>
       <c r="D520" t="n">
-        <v>0.7598469915197249</v>
+        <v>0.7463504874932502</v>
       </c>
       <c r="E520" t="n">
         <v>0.552602655941522</v>
@@ -32323,7 +32367,7 @@
         <v>40.61124455216337</v>
       </c>
       <c r="D521" t="n">
-        <v>1.348235867223506</v>
+        <v>1.329406336791682</v>
       </c>
       <c r="E521" t="n">
         <v>0.6898535667435873</v>
@@ -32341,7 +32385,7 @@
         <v>-19.41772265525651</v>
       </c>
       <c r="D522" t="n">
-        <v>1.257714501730617</v>
+        <v>1.239705436899616</v>
       </c>
       <c r="E522" t="n">
         <v>-0.3610941666024042</v>
@@ -32359,7 +32403,7 @@
         <v>-28.71077873516501</v>
       </c>
       <c r="D523" t="n">
-        <v>1.158140999688438</v>
+        <v>1.141034447018343</v>
       </c>
       <c r="E523" t="n">
         <v>-0.5237908891578746</v>
@@ -32377,7 +32421,7 @@
         <v>-50.702856772689</v>
       </c>
       <c r="D524" t="n">
-        <v>0.8503683570126144</v>
+        <v>0.8360513873853167</v>
       </c>
       <c r="E524" t="n">
         <v>-0.908813747959403</v>
@@ -32395,7 +32439,7 @@
         <v>-58.41082476183246</v>
       </c>
       <c r="D525" t="n">
-        <v>0.7236384453225692</v>
+        <v>0.7104701275364238</v>
       </c>
       <c r="E525" t="n">
         <v>-1.043759789241494</v>
@@ -32413,7 +32457,7 @@
         <v>-19.36767777038986</v>
       </c>
       <c r="D526" t="n">
-        <v>0.5606999874353681</v>
+        <v>0.549008507730704</v>
       </c>
       <c r="E526" t="n">
         <v>-0.3602180136255517</v>
@@ -32431,7 +32475,7 @@
         <v>-7.270301381331105</v>
       </c>
       <c r="D527" t="n">
-        <v>0.7145863087732802</v>
+        <v>0.7015000375472171</v>
       </c>
       <c r="E527" t="n">
         <v>-0.1484250928580736</v>
@@ -32449,7 +32493,7 @@
         <v>-49.93130725678765</v>
       </c>
       <c r="D528" t="n">
-        <v>0.4973350315903455</v>
+        <v>0.4862178778062575</v>
       </c>
       <c r="E528" t="n">
         <v>-0.8953059657565384</v>
@@ -32467,7 +32511,7 @@
         <v>21.31286663546211</v>
       </c>
       <c r="D529" t="n">
-        <v>0.2348230716609661</v>
+        <v>0.2260852681192649</v>
       </c>
       <c r="E529" t="n">
         <v>0.3519902405475533</v>
@@ -32485,7 +32529,7 @@
         <v>31.17323722891415</v>
       </c>
       <c r="D530" t="n">
-        <v>0.1352495696187877</v>
+        <v>0.1274142782379917</v>
       </c>
       <c r="E530" t="n">
         <v>0.5246191330176374</v>
@@ -32503,7 +32547,7 @@
         <v>-23.83955343367005</v>
       </c>
       <c r="D531" t="n">
-        <v>-0.08200170756414694</v>
+        <v>-0.08786788150296776</v>
       </c>
       <c r="E531" t="n">
         <v>-0.4385086757968726</v>
@@ -32521,7 +32565,7 @@
         <v>34.96753866717588</v>
       </c>
       <c r="D532" t="n">
-        <v>-0.6975469929157951</v>
+        <v>-0.6978340007690196</v>
       </c>
       <c r="E532" t="n">
         <v>0.5910472706598209</v>
@@ -32539,7 +32583,7 @@
         <v>-12.64984947124737</v>
       </c>
       <c r="D533" t="n">
-        <v>-0.9329025431973078</v>
+        <v>-0.9310563404883924</v>
       </c>
       <c r="E533" t="n">
         <v>-0.2426066877535534</v>
@@ -32557,7 +32601,7 @@
         <v>11.3268802082554</v>
       </c>
       <c r="D534" t="n">
-        <v>-0.7428076756622399</v>
+        <v>-0.7426844507150528</v>
       </c>
       <c r="E534" t="n">
         <v>0.177162148559332</v>
@@ -32575,7 +32619,7 @@
         <v>-22.82555682002926</v>
       </c>
       <c r="D535" t="n">
-        <v>-0.6070256274229058</v>
+        <v>-0.6081331008769533</v>
       </c>
       <c r="E535" t="n">
         <v>-0.4207562890359261</v>
@@ -32593,7 +32637,7 @@
         <v>-43.08047764030144</v>
       </c>
       <c r="D536" t="n">
-        <v>-0.5708170812257499</v>
+        <v>-0.5722527409201267</v>
       </c>
       <c r="E536" t="n">
         <v>-0.7753661401702033</v>
@@ -32611,7 +32655,7 @@
         <v>-34.75538011917864</v>
       </c>
       <c r="D537" t="n">
-        <v>-0.7156512660143731</v>
+        <v>-0.7157741807474329</v>
       </c>
       <c r="E537" t="n">
         <v>-0.6296158003471506</v>
@@ -32629,7 +32673,7 @@
         <v>-44.82164430001592</v>
       </c>
       <c r="D538" t="n">
-        <v>0.08093675032305407</v>
+        <v>0.07359373830275187</v>
       </c>
       <c r="E538" t="n">
         <v>-0.8058493425228562</v>
@@ -32647,7 +32691,7 @@
         <v>4.561270406027624</v>
       </c>
       <c r="D539" t="n">
-        <v>0.940889722505504</v>
+        <v>0.9257522872773832</v>
       </c>
       <c r="E539" t="n">
         <v>0.05871429551221453</v>
@@ -32665,7 +32709,7 @@
         <v>-34.64640179402035</v>
       </c>
       <c r="D540" t="n">
-        <v>0.7598469915197249</v>
+        <v>0.7463504874932502</v>
       </c>
       <c r="E540" t="n">
         <v>-0.6277078794026971</v>
@@ -32683,7 +32727,7 @@
         <v>69.50205381475861</v>
       </c>
       <c r="D541" t="n">
-        <v>0.9952025418012375</v>
+        <v>0.979572827212623</v>
       </c>
       <c r="E541" t="n">
         <v>1.19565488103478</v>
@@ -32701,7 +32745,7 @@
         <v>-7.650187800766401</v>
       </c>
       <c r="D542" t="n">
-        <v>0.8775247666604812</v>
+        <v>0.8629616573529367</v>
       </c>
       <c r="E542" t="n">
         <v>-0.1550758947959937</v>
@@ -32719,7 +32763,7 @@
         <v>-20.73920700998515</v>
       </c>
       <c r="D543" t="n">
-        <v>0.3072401640552777</v>
+        <v>0.297845988032918</v>
       </c>
       <c r="E543" t="n">
         <v>-0.3842298467891956</v>
@@ -32737,7 +32781,7 @@
         <v>-41.67462287569219</v>
       </c>
       <c r="D544" t="n">
-        <v>-0.22683589235277</v>
+        <v>-0.2313893213302741</v>
       </c>
       <c r="E544" t="n">
         <v>-0.7507533582581878</v>
@@ -32755,7 +32799,7 @@
         <v>-27.38210392461608</v>
       </c>
       <c r="D545" t="n">
-        <v>-1.186362366577398</v>
+        <v>-1.182218860186178</v>
       </c>
       <c r="E545" t="n">
         <v>-0.5005293231929729</v>
@@ -32773,7 +32817,7 @@
         <v>-38.932691013001</v>
       </c>
       <c r="D546" t="n">
-        <v>-1.059632454887353</v>
+        <v>-1.056637600337285</v>
       </c>
       <c r="E546" t="n">
         <v>-0.7027494159926566</v>
@@ -32791,7 +32835,7 @@
         <v>-29.06844415542188</v>
       </c>
       <c r="D547" t="n">
-        <v>-0.6251299005214837</v>
+        <v>-0.6260732808553665</v>
       </c>
       <c r="E547" t="n">
         <v>-0.5300526604360041</v>
@@ -32809,7 +32853,7 @@
         <v>44.95476236747208</v>
       </c>
       <c r="D548" t="n">
-        <v>-0.3354615309442374</v>
+        <v>-0.3390304012007538</v>
       </c>
       <c r="E548" t="n">
         <v>0.7658970240127037</v>
@@ -32827,7 +32871,7 @@
         <v>-19.21281360306676</v>
       </c>
       <c r="D549" t="n">
-        <v>-0.1544187999584585</v>
+        <v>-0.1596286014166209</v>
       </c>
       <c r="E549" t="n">
         <v>-0.3575067534923836</v>
@@ -32845,7 +32889,7 @@
         <v>-51.59251177643962</v>
       </c>
       <c r="D550" t="n">
-        <v>-0.03674102481770224</v>
+        <v>-0.04301743155693454</v>
       </c>
       <c r="E550" t="n">
         <v>-0.9243892434767749</v>
@@ -32863,7 +32907,7 @@
         <v>-55.10673922143157</v>
       </c>
       <c r="D551" t="n">
-        <v>-0.2811487116485037</v>
+        <v>-0.285209861265514</v>
       </c>
       <c r="E551" t="n">
         <v>-0.9859140295857062</v>
@@ -32881,7 +32925,7 @@
         <v>33.22079634295852</v>
       </c>
       <c r="D552" t="n">
-        <v>-0.03674102481770224</v>
+        <v>-0.04301743155693454</v>
       </c>
       <c r="E552" t="n">
         <v>0.5604664532349154</v>
@@ -32899,7 +32943,7 @@
         <v>-36.08895926928813</v>
       </c>
       <c r="D553" t="n">
-        <v>-0.5527128081271721</v>
+        <v>-0.5543125609417133</v>
       </c>
       <c r="E553" t="n">
         <v>-0.6529632282681128</v>
@@ -32917,7 +32961,7 @@
         <v>-20.3695175484923</v>
       </c>
       <c r="D554" t="n">
-        <v>-0.3716700771413932</v>
+        <v>-0.3749107611575804</v>
       </c>
       <c r="E554" t="n">
         <v>-0.3777575664939953</v>
@@ -32935,7 +32979,7 @@
         <v>-2.824881371721344</v>
       </c>
       <c r="D555" t="n">
-        <v>-0.1815752096063253</v>
+        <v>-0.1865388713842409</v>
       </c>
       <c r="E555" t="n">
         <v>-0.07059759889624474</v>
@@ -32953,10 +32997,10 @@
         <v>-0.4200878365476396</v>
       </c>
       <c r="D556" t="n">
-        <v>-0.08200170756414694</v>
+        <v>-0.08786788150296776</v>
       </c>
       <c r="E556" t="n">
-        <v>-0.02849605305049996</v>
+        <v>-0.02849605305049997</v>
       </c>
       <c r="F556" t="inlineStr"/>
     </row>
@@ -32971,7 +33015,7 @@
         <v>-26.42567574911151</v>
       </c>
       <c r="D557" t="n">
-        <v>-1.521291418901089</v>
+        <v>-1.514112189786824</v>
       </c>
       <c r="E557" t="n">
         <v>-0.4837848068383667</v>
@@ -32989,7 +33033,7 @@
         <v>-65.29674900136145</v>
       </c>
       <c r="D558" t="n">
-        <v>-1.08678886453522</v>
+        <v>-1.083547870304905</v>
       </c>
       <c r="E558" t="n">
         <v>-1.164314028439378</v>
@@ -33007,7 +33051,7 @@
         <v>-43.79775646236384</v>
       </c>
       <c r="D559" t="n">
-        <v>-1.494135009253222</v>
+        <v>-1.487201919819204</v>
       </c>
       <c r="E559" t="n">
         <v>-0.7879237867080633</v>
@@ -33025,7 +33069,7 @@
         <v>5.137008486104809</v>
       </c>
       <c r="D560" t="n">
-        <v>-0.9238504066480187</v>
+        <v>-0.9220862504991857</v>
       </c>
       <c r="E560" t="n">
         <v>0.06879393969745215</v>
@@ -33043,7 +33087,7 @@
         <v>-41.04641894712869</v>
       </c>
       <c r="D561" t="n">
-        <v>-0.5708170812257499</v>
+        <v>-0.5722527409201267</v>
       </c>
       <c r="E561" t="n">
         <v>-0.7397551764550325</v>
@@ -33061,7 +33105,7 @@
         <v>-13.07442335246906</v>
       </c>
       <c r="D562" t="n">
-        <v>-0.3716700771413932</v>
+        <v>-0.3749107611575804</v>
       </c>
       <c r="E562" t="n">
         <v>-0.2500398484235689</v>
@@ -33079,7 +33123,7 @@
         <v>-11.76355169526999</v>
       </c>
       <c r="D563" t="n">
-        <v>-0.4169307598878378</v>
+        <v>-0.4197612111036136</v>
       </c>
       <c r="E563" t="n">
         <v>-0.2270899683751482</v>
@@ -33097,7 +33141,7 @@
         <v>-47.19591909658261</v>
       </c>
       <c r="D564" t="n">
-        <v>-0.7790162218593958</v>
+        <v>-0.7785648106718794</v>
       </c>
       <c r="E564" t="n">
         <v>-0.8474165863365037</v>
@@ -33115,7 +33159,7 @@
         <v>-53.52998044610868</v>
       </c>
       <c r="D565" t="n">
-        <v>-0.8061726315072624</v>
+        <v>-0.8054750806394992</v>
       </c>
       <c r="E565" t="n">
         <v>-0.9583091724967413</v>
@@ -33133,7 +33177,7 @@
         <v>-19.64704440886064</v>
       </c>
       <c r="D566" t="n">
-        <v>-0.5979734908736168</v>
+        <v>-0.5991630108877466</v>
       </c>
       <c r="E566" t="n">
         <v>-0.3651089812555438</v>
@@ -33151,7 +33195,7 @@
         <v>-19.44011819161014</v>
       </c>
       <c r="D567" t="n">
-        <v>0.01757179447803145</v>
+        <v>0.01080310837830535</v>
       </c>
       <c r="E567" t="n">
         <v>-0.3614862529444295</v>
@@ -33169,7 +33213,7 @@
         <v>-5.403857170135571</v>
       </c>
       <c r="D568" t="n">
-        <v>0.7055341722239913</v>
+        <v>0.6925299475580105</v>
       </c>
       <c r="E568" t="n">
         <v>-0.1157486134111602</v>
@@ -33187,7 +33231,7 @@
         <v>18.31994696171026</v>
       </c>
       <c r="D569" t="n">
-        <v>1.040463224547682</v>
+        <v>1.024423277158656</v>
       </c>
       <c r="E569" t="n">
         <v>0.2995921685242962</v>
@@ -33205,10 +33249,10 @@
         <v>1.76687960982032</v>
       </c>
       <c r="D570" s="4" t="n">
-        <v>2.135771747011645</v>
+        <v>2.109804165852661</v>
       </c>
       <c r="E570" s="4" t="n">
-        <v>0.009791936691522231</v>
+        <v>0.009791936691522228</v>
       </c>
       <c r="F570" s="4" t="inlineStr">
         <is>
@@ -33227,7 +33271,7 @@
         <v>211.3802633718095</v>
       </c>
       <c r="D571" s="4" t="n">
-        <v>2.932359763349071</v>
+        <v>2.899172084902845</v>
       </c>
       <c r="E571" s="4" t="n">
         <v>3.679565394270128</v>
@@ -33249,7 +33293,7 @@
         <v>-13.17397594523979</v>
       </c>
       <c r="D572" s="4" t="n">
-        <v>3.502644365954275</v>
+        <v>3.464287754222864</v>
       </c>
       <c r="E572" s="4" t="n">
         <v>-0.2517827498358088</v>
@@ -33271,7 +33315,7 @@
         <v>278.3163168482181</v>
       </c>
       <c r="D573" s="4" t="n">
-        <v>3.80136487208081</v>
+        <v>3.760300723866683</v>
       </c>
       <c r="E573" s="4" t="n">
         <v>4.851437857727446</v>
@@ -33293,7 +33337,7 @@
         <v>10.5533756005282</v>
       </c>
       <c r="D574" s="4" t="n">
-        <v>3.80136487208081</v>
+        <v>3.760300723866683</v>
       </c>
       <c r="E574" s="4" t="n">
         <v>0.1636201378928032</v>
@@ -33315,7 +33359,7 @@
         <v>40.80159062369193</v>
       </c>
       <c r="D575" s="4" t="n">
-        <v>3.538852912151431</v>
+        <v>3.500168114179691</v>
       </c>
       <c r="E575" s="4" t="n">
         <v>0.69318602075255</v>
@@ -33337,7 +33381,7 @@
         <v>99.8311945144378</v>
       </c>
       <c r="D576" s="4" t="n">
-        <v>4.263023836094546</v>
+        <v>4.217775313316221</v>
       </c>
       <c r="E576" s="4" t="n">
         <v>1.72663755749035</v>
@@ -33359,7 +33403,7 @@
         <v>13.12385443505879</v>
       </c>
       <c r="D577" s="4" t="n">
-        <v>4.063876832010189</v>
+        <v>4.020433333553675</v>
       </c>
       <c r="E577" s="4" t="n">
         <v>0.2086223931444955</v>
@@ -33381,7 +33425,7 @@
         <v>-36.23223920198405</v>
       </c>
       <c r="D578" s="4" t="n">
-        <v>3.430227273559963</v>
+        <v>3.39252703430921</v>
       </c>
       <c r="E578" s="4" t="n">
         <v>-0.6554716792294702</v>
@@ -33403,7 +33447,7 @@
         <v>91.06430671596171</v>
       </c>
       <c r="D579" s="4" t="n">
-        <v>2.60648284757467</v>
+        <v>2.576248845291406</v>
       </c>
       <c r="E579" s="4" t="n">
         <v>1.573152643640821</v>
@@ -33425,7 +33469,7 @@
         <v>59.88161160970022</v>
       </c>
       <c r="D580" s="4" t="n">
-        <v>2.697004213067559</v>
+        <v>2.665949745183473</v>
       </c>
       <c r="E580" s="4" t="n">
         <v>1.027226497213735</v>
@@ -33447,7 +33491,7 @@
         <v>12.50529839472226</v>
       </c>
       <c r="D581" s="4" t="n">
-        <v>2.642691393771825</v>
+        <v>2.612129205248233</v>
       </c>
       <c r="E581" s="4" t="n">
         <v>0.1977931202320873</v>
@@ -33469,7 +33513,7 @@
         <v>111.5677503328795</v>
       </c>
       <c r="D582" t="n">
-        <v>2.678899939968981</v>
+        <v>2.648009565205059</v>
       </c>
       <c r="E582" t="n">
         <v>1.932113468679364</v>
@@ -33487,7 +33531,7 @@
         <v>365.5015444643148</v>
       </c>
       <c r="D583" t="n">
-        <v>2.244397385603112</v>
+        <v>2.21744524572314</v>
       </c>
       <c r="E583" t="n">
         <v>6.377819563209556</v>
@@ -33505,7 +33549,7 @@
         <v>167.8413335924511</v>
       </c>
       <c r="D584" t="n">
-        <v>1.502122188561418</v>
+        <v>1.481897866608195</v>
       </c>
       <c r="E584" t="n">
         <v>2.917314406245946</v>
@@ -33523,7 +33567,7 @@
         <v>-32.47808099593881</v>
       </c>
       <c r="D585" t="n">
-        <v>1.085723907294127</v>
+        <v>1.069273727104689</v>
       </c>
       <c r="E585" t="n">
         <v>-0.5897463429325328</v>
@@ -33541,7 +33585,7 @@
         <v>-8.916380254914252</v>
       </c>
       <c r="D586" t="n">
-        <v>0.415865802646745</v>
+        <v>0.4054870679033978</v>
       </c>
       <c r="E586" t="n">
         <v>-0.1772435607008304</v>
@@ -33559,7 +33603,7 @@
         <v>-17.29672457095019</v>
       </c>
       <c r="D587" t="n">
-        <v>0.5154393046889234</v>
+        <v>0.5041580577846708</v>
       </c>
       <c r="E587" t="n">
         <v>-0.3239611251254322</v>
@@ -33577,7 +33621,7 @@
         <v>91.23690063271252</v>
       </c>
       <c r="D588" t="n">
-        <v>0.08998888687234299</v>
+        <v>0.0825638282919585</v>
       </c>
       <c r="E588" t="n">
         <v>1.576174304582809</v>
@@ -33595,7 +33639,7 @@
         <v>-62.25705274301286</v>
       </c>
       <c r="D589" t="n">
-        <v>0.05378034067518724</v>
+        <v>0.04668346833513194</v>
       </c>
       <c r="E589" t="n">
         <v>-1.11109702269391</v>
@@ -33613,7 +33657,7 @@
         <v>-11.52239032984488</v>
       </c>
       <c r="D590" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E590" t="n">
         <v>-0.22286787357401</v>
@@ -33631,7 +33675,7 @@
         <v>78.20987744170476</v>
       </c>
       <c r="D591" t="n">
-        <v>-0.2720965750992148</v>
+        <v>-0.2762397712763073</v>
       </c>
       <c r="E591" t="n">
         <v>1.348105738160047</v>
@@ -33649,7 +33693,7 @@
         <v>39.84628604162689</v>
       </c>
       <c r="D592" t="n">
-        <v>0.1805102523652325</v>
+        <v>0.172264728184025</v>
       </c>
       <c r="E592" t="n">
         <v>0.6764611755339536</v>
@@ -33667,7 +33711,7 @@
         <v>17.96128639589605</v>
       </c>
       <c r="D593" t="n">
-        <v>-0.5979734908736168</v>
+        <v>-0.5991630108877466</v>
       </c>
       <c r="E593" t="n">
         <v>0.2933129748913189</v>
@@ -33685,7 +33729,7 @@
         <v>30.95854340898548</v>
       </c>
       <c r="D594" t="n">
-        <v>-0.4078786233385489</v>
+        <v>-0.4107911211144069</v>
       </c>
       <c r="E594" t="n">
         <v>0.5208604146202712</v>
@@ -33703,7 +33747,7 @@
         <v>-32.85644610632418</v>
       </c>
       <c r="D595" t="n">
-        <v>-0.4712435791835716</v>
+        <v>-0.4735817510388535</v>
       </c>
       <c r="E595" t="n">
         <v>-0.5963705107907391</v>
@@ -33721,7 +33765,7 @@
         <v>-29.36883245881108</v>
       </c>
       <c r="D596" t="n">
-        <v>0.008519657928742501</v>
+        <v>0.001833018389098698</v>
       </c>
       <c r="E596" t="n">
         <v>-0.5353116615692355</v>
@@ -33739,7 +33783,7 @@
         <v>-10.70140812995785</v>
       </c>
       <c r="D597" t="n">
-        <v>0.1171452965202099</v>
+        <v>0.1094740982595784</v>
       </c>
       <c r="E597" t="n">
         <v>-0.208494656405249</v>
@@ -33757,7 +33801,7 @@
         <v>130.5747277137318</v>
       </c>
       <c r="D598" t="n">
-        <v>-0.733755539112951</v>
+        <v>-0.7337143607258462</v>
       </c>
       <c r="E598" t="n">
         <v>2.264875145673471</v>
@@ -33775,7 +33819,7 @@
         <v>-34.3475303474257</v>
       </c>
       <c r="D599" t="n">
-        <v>-0.561764944676461</v>
+        <v>-0.56328265093092</v>
       </c>
       <c r="E599" t="n">
         <v>-0.6224754344020164</v>
@@ -33793,7 +33837,7 @@
         <v>-40.5237898679744</v>
       </c>
       <c r="D600" t="n">
-        <v>-0.896693997000152</v>
+        <v>-0.8951759805315658</v>
       </c>
       <c r="E600" t="n">
         <v>-0.7306053297781766</v>
@@ -33811,7 +33855,7 @@
         <v>57.29727601608058</v>
       </c>
       <c r="D601" t="n">
-        <v>-0.3626179405921042</v>
+        <v>-0.3659406711683738</v>
       </c>
       <c r="E601" t="n">
         <v>0.9819816469244526</v>
@@ -33829,7 +33873,7 @@
         <v>-4.018809651565141</v>
       </c>
       <c r="D602" t="n">
-        <v>-0.4712435791835716</v>
+        <v>-0.4735817510388535</v>
       </c>
       <c r="E602" t="n">
         <v>-0.09150011109746123</v>
@@ -33847,7 +33891,7 @@
         <v>-19.62570230852086</v>
       </c>
       <c r="D603" t="n">
-        <v>-0.3445136674935264</v>
+        <v>-0.3480004911899605</v>
       </c>
       <c r="E603" t="n">
         <v>-0.3647353377793962</v>
@@ -33865,7 +33909,7 @@
         <v>-10.50696963910636</v>
       </c>
       <c r="D604" t="n">
-        <v>-0.2087316192541921</v>
+        <v>-0.2134491413518607</v>
       </c>
       <c r="E604" t="n">
         <v>-0.2050905550065106</v>
@@ -33883,7 +33927,7 @@
         <v>63.70681129019987</v>
       </c>
       <c r="D605" t="n">
-        <v>0.1805102523652325</v>
+        <v>0.172264728184025</v>
       </c>
       <c r="E605" t="n">
         <v>1.094195580988343</v>
@@ -33901,7 +33945,7 @@
         <v>107.824538830957</v>
       </c>
       <c r="D606" t="n">
-        <v>-0.1453666634091696</v>
+        <v>-0.1506585114274143</v>
       </c>
       <c r="E606" t="n">
         <v>1.866579780088869</v>
@@ -33919,7 +33963,7 @@
         <v>11.83547390668185</v>
       </c>
       <c r="D607" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E607" t="n">
         <v>0.1860662730082575</v>
@@ -33937,7 +33981,7 @@
         <v>-63.68033512556413</v>
       </c>
       <c r="D608" t="n">
-        <v>-0.03674102481770224</v>
+        <v>-0.04301743155693454</v>
       </c>
       <c r="E608" t="n">
         <v>-1.136014915895122</v>
@@ -33955,7 +33999,7 @@
         <v>-35.23930618286711</v>
       </c>
       <c r="D609" t="n">
-        <v>-0.2992529847470816</v>
+        <v>-0.3031500412439272</v>
       </c>
       <c r="E609" t="n">
         <v>-0.638088060047757</v>
@@ -33973,7 +34017,7 @@
         <v>26.7360298180388</v>
       </c>
       <c r="D610" t="n">
-        <v>0.008519657928742501</v>
+        <v>0.001833018389098698</v>
       </c>
       <c r="E610" t="n">
         <v>0.4469354198407584</v>
@@ -33991,7 +34035,7 @@
         <v>-64.64263290079532</v>
       </c>
       <c r="D611" t="n">
-        <v>-0.02768888826841329</v>
+        <v>-0.03404734156772789</v>
       </c>
       <c r="E611" t="n">
         <v>-1.152862193346834</v>
@@ -34009,7 +34053,7 @@
         <v>45.75183129308697</v>
       </c>
       <c r="D612" t="n">
-        <v>-0.8604854508029961</v>
+        <v>-0.8592956205747392</v>
       </c>
       <c r="E612" t="n">
         <v>0.7798515832807491</v>
@@ -34027,7 +34071,7 @@
         <v>-2.860467456113101</v>
       </c>
       <c r="D613" t="n">
-        <v>-0.6522863101693505</v>
+        <v>-0.6529835508229863</v>
       </c>
       <c r="E613" t="n">
         <v>-0.0712206166903199</v>
@@ -34045,7 +34089,7 @@
         <v>76.30879600485029</v>
       </c>
       <c r="D614" t="n">
-        <v>-0.3535658040428153</v>
+        <v>-0.3569705811791671</v>
       </c>
       <c r="E614" t="n">
         <v>1.314822852914582</v>
@@ -34063,10 +34107,10 @@
         <v>-31.54129428546476</v>
       </c>
       <c r="D615" t="n">
-        <v>-0.2177837558034811</v>
+        <v>-0.2224192313410674</v>
       </c>
       <c r="E615" t="n">
-        <v>-0.5733456964479859</v>
+        <v>-0.5733456964479861</v>
       </c>
       <c r="F615" t="inlineStr"/>
     </row>
@@ -34081,7 +34125,7 @@
         <v>-37.18732098529692</v>
       </c>
       <c r="D616" t="n">
-        <v>0.3706051199003003</v>
+        <v>0.3606366179573645</v>
       </c>
       <c r="E616" t="n">
         <v>-0.6721926238338385</v>
@@ -34099,7 +34143,7 @@
         <v>46.0183242943625</v>
       </c>
       <c r="D617" t="n">
-        <v>0.3796572564495893</v>
+        <v>0.3696067079465711</v>
       </c>
       <c r="E617" t="n">
         <v>0.7845171677255948</v>
@@ -34117,10 +34161,10 @@
         <v>1.686090872368753</v>
       </c>
       <c r="D618" t="n">
-        <v>-0.4259828964371268</v>
+        <v>-0.4287313010928202</v>
       </c>
       <c r="E618" t="n">
-        <v>0.008377540534892798</v>
+        <v>0.008377540534892793</v>
       </c>
       <c r="F618" t="inlineStr"/>
     </row>
@@ -34135,7 +34179,7 @@
         <v>-38.20516989107463</v>
       </c>
       <c r="D619" t="n">
-        <v>-0.5527128081271721</v>
+        <v>-0.5543125609417133</v>
       </c>
       <c r="E619" t="n">
         <v>-0.6900124539954936</v>
@@ -34153,7 +34197,7 @@
         <v>-24.85586577702922</v>
       </c>
       <c r="D620" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E620" t="n">
         <v>-0.456301604832854</v>
@@ -34171,7 +34215,7 @@
         <v>-52.17671841196341</v>
       </c>
       <c r="D621" t="n">
-        <v>-0.5436606715778831</v>
+        <v>-0.5453424709525067</v>
       </c>
       <c r="E621" t="n">
         <v>-0.9346171495689777</v>
@@ -34189,7 +34233,7 @@
         <v>-42.04025060638129</v>
       </c>
       <c r="D622" t="n">
-        <v>-0.8061726315072624</v>
+        <v>-0.8054750806394992</v>
       </c>
       <c r="E622" t="n">
         <v>-0.7571545284380514</v>
@@ -34207,7 +34251,7 @@
         <v>-62.60203013813312</v>
       </c>
       <c r="D623" t="n">
-        <v>-0.8061726315072624</v>
+        <v>-0.8054750806394992</v>
       </c>
       <c r="E623" t="n">
         <v>-1.117136660360914</v>
@@ -34225,7 +34269,7 @@
         <v>-16.62610817104802</v>
       </c>
       <c r="D624" t="n">
-        <v>-0.5889213543243279</v>
+        <v>-0.5901929208985399</v>
       </c>
       <c r="E624" t="n">
         <v>-0.3122204136288212</v>
@@ -34243,7 +34287,7 @@
         <v>-12.89988145179986</v>
       </c>
       <c r="D625" t="n">
-        <v>-0.7065991294650842</v>
+        <v>-0.7068040907582263</v>
       </c>
       <c r="E625" t="n">
         <v>-0.2469840834584918</v>
@@ -34261,7 +34305,7 @@
         <v>-43.7358198802638</v>
       </c>
       <c r="D626" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E626" t="n">
         <v>-0.7868394417060192</v>
@@ -34279,7 +34323,7 @@
         <v>-3.987511280603179</v>
       </c>
       <c r="D627" t="n">
-        <v>0.1533538427173656</v>
+        <v>0.145354458216405</v>
       </c>
       <c r="E627" t="n">
         <v>-0.0909521597741236</v>
@@ -34297,7 +34341,7 @@
         <v>54.5016230666412</v>
       </c>
       <c r="D628" t="n">
-        <v>0.9137333128576369</v>
+        <v>0.8988420173097633</v>
       </c>
       <c r="E628" t="n">
         <v>0.9330371911539027</v>
@@ -34315,7 +34359,7 @@
         <v>43.45335782369117</v>
       </c>
       <c r="D629" t="n">
-        <v>0.9589939956040816</v>
+        <v>0.9436924672557964</v>
       </c>
       <c r="E629" t="n">
         <v>0.7396114193200598</v>
@@ -34333,7 +34377,7 @@
         <v>-2.335392947442444</v>
       </c>
       <c r="D630" t="n">
-        <v>0.7870034011675917</v>
+        <v>0.7732607574608702</v>
       </c>
       <c r="E630" t="n">
         <v>-0.06202795703954752</v>
@@ -34351,7 +34395,7 @@
         <v>-44.9357827995448</v>
       </c>
       <c r="D631" t="n">
-        <v>0.5606999874353681</v>
+        <v>0.549008507730704</v>
       </c>
       <c r="E631" t="n">
         <v>-0.8078476044112028</v>
@@ -34369,7 +34413,7 @@
         <v>-29.95184729329965</v>
       </c>
       <c r="D632" t="n">
-        <v>0.008519657928742501</v>
+        <v>0.001833018389098698</v>
       </c>
       <c r="E632" t="n">
         <v>-0.5455187023916389</v>
@@ -34387,7 +34431,7 @@
         <v>-70.65130754924658</v>
       </c>
       <c r="D633" t="n">
-        <v>-0.01863675171912433</v>
+        <v>-0.02507725157852124</v>
       </c>
       <c r="E633" t="n">
         <v>-1.258058122845065</v>
@@ -34405,7 +34449,7 @@
         <v>-52.15440949232541</v>
       </c>
       <c r="D634" t="n">
-        <v>0.3977615295481671</v>
+        <v>0.3875468879249845</v>
       </c>
       <c r="E634" t="n">
         <v>-0.9342265796555234</v>
@@ -34423,7 +34467,7 @@
         <v>-8.506435747174546</v>
       </c>
       <c r="D635" t="n">
-        <v>0.5516478508860791</v>
+        <v>0.5400384177414974</v>
       </c>
       <c r="E635" t="n">
         <v>-0.1700665214937752</v>
@@ -34441,7 +34485,7 @@
         <v>136.3892876285293</v>
       </c>
       <c r="D636" t="n">
-        <v>1.094776043843416</v>
+        <v>1.078243817093896</v>
       </c>
       <c r="E636" t="n">
         <v>2.366672641901351</v>
@@ -34459,7 +34503,7 @@
         <v>12.38894308374054</v>
       </c>
       <c r="D637" t="n">
-        <v>1.212453818984172</v>
+        <v>1.194854986953583</v>
       </c>
       <c r="E637" t="n">
         <v>0.1957560478647337</v>
@@ -34477,7 +34521,7 @@
         <v>8.523070553093346</v>
       </c>
       <c r="D638" t="n">
-        <v>0.3343965737031445</v>
+        <v>0.3247562580005379</v>
       </c>
       <c r="E638" t="n">
         <v>0.1280748905419736</v>
@@ -34495,7 +34539,7 @@
         <v>-14.17280428517364</v>
       </c>
       <c r="D639" t="n">
-        <v>0.1080931599709209</v>
+        <v>0.1005040082703718</v>
       </c>
       <c r="E639" t="n">
         <v>-0.2692695804225838</v>
@@ -34513,7 +34557,7 @@
         <v>-11.14664884475845</v>
       </c>
       <c r="D640" t="n">
-        <v>0.1533538427173656</v>
+        <v>0.145354458216405</v>
       </c>
       <c r="E640" t="n">
         <v>-0.2162896384244498</v>
@@ -34531,7 +34575,7 @@
         <v>-14.0627547305155</v>
       </c>
       <c r="D641" t="n">
-        <v>-0.2902008481977927</v>
+        <v>-0.2941799512547206</v>
       </c>
       <c r="E641" t="n">
         <v>-0.2673429050955857</v>
@@ -34549,10 +34593,10 @@
         <v>-2.326416421058932</v>
       </c>
       <c r="D642" t="n">
-        <v>-1.276883732070288</v>
+        <v>-1.271919760078245</v>
       </c>
       <c r="E642" t="n">
-        <v>-0.06187080191103305</v>
+        <v>-0.06187080191103306</v>
       </c>
       <c r="F642" t="inlineStr"/>
     </row>
@@ -34567,7 +34611,7 @@
         <v>-8.844090391806207</v>
       </c>
       <c r="D643" t="n">
-        <v>-1.005319635591619</v>
+        <v>-1.002817060402046</v>
       </c>
       <c r="E643" t="n">
         <v>-0.1759779572545012</v>
@@ -34585,7 +34629,7 @@
         <v>-31.4633672345663</v>
       </c>
       <c r="D644" t="n">
-        <v>-0.6975469929157951</v>
+        <v>-0.6978340007690196</v>
       </c>
       <c r="E644" t="n">
         <v>-0.571981400820092</v>
@@ -34603,7 +34647,7 @@
         <v>-34.41378525069267</v>
       </c>
       <c r="D645" t="n">
-        <v>0.2257709351116772</v>
+        <v>0.2171151781300582</v>
       </c>
       <c r="E645" t="n">
         <v>-0.623635381734958</v>
@@ -34621,7 +34665,7 @@
         <v>-50.44062145887377</v>
       </c>
       <c r="D646" t="n">
-        <v>-0.1906273461556143</v>
+        <v>-0.1955089613734475</v>
       </c>
       <c r="E646" t="n">
         <v>-0.9042227043103407</v>
@@ -34639,7 +34683,7 @@
         <v>133.45280452072</v>
       </c>
       <c r="D647" t="n">
-        <v>0.4249179391960339</v>
+        <v>0.4144571578926044</v>
       </c>
       <c r="E647" t="n">
         <v>2.315262624209433</v>
@@ -34657,7 +34701,7 @@
         <v>51.77707818651157</v>
       </c>
       <c r="D648" t="n">
-        <v>0.4701786219424787</v>
+        <v>0.4593076078386377</v>
       </c>
       <c r="E648" t="n">
         <v>0.8853376487600143</v>
@@ -34675,7 +34719,7 @@
         <v>38.08459354590354</v>
       </c>
       <c r="D649" t="n">
-        <v>0.415865802646745</v>
+        <v>0.4054870679033978</v>
       </c>
       <c r="E649" t="n">
         <v>0.6456186203249702</v>
@@ -34693,7 +34737,7 @@
         <v>-36.16252688149327</v>
       </c>
       <c r="D650" t="n">
-        <v>0.02662393102732041</v>
+        <v>0.01977319836751201</v>
       </c>
       <c r="E650" t="n">
         <v>-0.6542512017064617</v>
@@ -34711,7 +34755,7 @@
         <v>-39.43953596692963</v>
       </c>
       <c r="D651" t="n">
-        <v>0.1533538427173656</v>
+        <v>0.145354458216405</v>
       </c>
       <c r="E651" t="n">
         <v>-0.7116229245714166</v>
@@ -34729,7 +34773,7 @@
         <v>-11.34714531220164</v>
       </c>
       <c r="D652" t="n">
-        <v>-0.4531393060849936</v>
+        <v>-0.4556415710604401</v>
       </c>
       <c r="E652" t="n">
         <v>-0.2197997988987292</v>
@@ -34747,7 +34791,7 @@
         <v>-8.231803410535923</v>
       </c>
       <c r="D653" t="n">
-        <v>-0.2992529847470816</v>
+        <v>-0.3031500412439272</v>
       </c>
       <c r="E653" t="n">
         <v>-0.1652584389109684</v>
@@ -34765,7 +34809,7 @@
         <v>13.42738738199608</v>
       </c>
       <c r="D654" t="n">
-        <v>-1.222570912774554</v>
+        <v>-1.218099220143005</v>
       </c>
       <c r="E654" t="n">
         <v>0.213936448631696</v>
@@ -34783,7 +34827,7 @@
         <v>-22.90684441554218</v>
       </c>
       <c r="D655" t="n">
-        <v>-0.7518598122115289</v>
+        <v>-0.7516545407042595</v>
       </c>
       <c r="E655" t="n">
         <v>-0.4221794188718645</v>
@@ -34801,7 +34845,7 @@
         <v>-12.31025026451599</v>
       </c>
       <c r="D656" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E656" t="n">
         <v>-0.2366612078766928</v>
@@ -34819,7 +34863,7 @@
         <v>-62.79462557406915</v>
       </c>
       <c r="D657" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E657" t="n">
         <v>-1.120508494764634</v>
@@ -34837,7 +34881,7 @@
         <v>54.97139004129949</v>
       </c>
       <c r="D658" t="n">
-        <v>-0.02768888826841329</v>
+        <v>-0.03404734156772789</v>
       </c>
       <c r="E658" t="n">
         <v>0.9412615628228677</v>
@@ -34855,7 +34899,7 @@
         <v>25.63441816659691</v>
       </c>
       <c r="D659" t="n">
-        <v>0.3525008468017224</v>
+        <v>0.3426964379789512</v>
       </c>
       <c r="E659" t="n">
         <v>0.427649126539892</v>
@@ -34873,7 +34917,7 @@
         <v>-29.54527252228665</v>
       </c>
       <c r="D660" t="n">
-        <v>0.8684726301111922</v>
+        <v>0.8539915673637301</v>
       </c>
       <c r="E660" t="n">
         <v>-0.5384006583220923</v>
@@ -34891,7 +34935,7 @@
         <v>-45.34096824570536</v>
       </c>
       <c r="D661" t="n">
-        <v>0.5425957143367902</v>
+        <v>0.5310683277522907</v>
       </c>
       <c r="E661" t="n">
         <v>-0.8149413250936833</v>
@@ -34909,7 +34953,7 @@
         <v>-41.17547647314807</v>
       </c>
       <c r="D662" t="n">
-        <v>0.1986145254638104</v>
+        <v>0.1902049081624383</v>
       </c>
       <c r="E662" t="n">
         <v>-0.7420146308609805</v>
@@ -34927,7 +34971,7 @@
         <v>-40.30741463130622</v>
       </c>
       <c r="D663" t="n">
-        <v>-0.6341820370707725</v>
+        <v>-0.635043370844573</v>
       </c>
       <c r="E663" t="n">
         <v>-0.7268171742408194</v>
@@ -34945,7 +34989,7 @@
         <v>-30.96715676914263</v>
       </c>
       <c r="D664" t="n">
-        <v>-1.104893137633798</v>
+        <v>-1.101488050283319</v>
       </c>
       <c r="E664" t="n">
         <v>-0.5632940738817882</v>
@@ -34963,7 +35007,7 @@
         <v>4.495212424871475</v>
       </c>
       <c r="D665" t="n">
-        <v>-0.1634709365077474</v>
+        <v>-0.1685986914058275</v>
       </c>
       <c r="E665" t="n">
         <v>0.05755779576225904</v>
@@ -34981,7 +35025,7 @@
         <v>-77.48687183016413</v>
       </c>
       <c r="D666" t="n">
-        <v>-0.1272623903105917</v>
+        <v>-0.132718331449001</v>
       </c>
       <c r="E666" t="n">
         <v>-1.3777306929619</v>
@@ -34999,7 +35043,7 @@
         <v>-32.97024874004227</v>
       </c>
       <c r="D667" t="n">
-        <v>-0.4802957157328605</v>
+        <v>-0.4825518410280601</v>
       </c>
       <c r="E667" t="n">
         <v>-0.598362892561053</v>
@@ -35017,7 +35061,7 @@
         <v>-41.28824685279955</v>
       </c>
       <c r="D668" t="n">
-        <v>-0.1001059806627248</v>
+        <v>-0.105808061481381</v>
       </c>
       <c r="E668" t="n">
         <v>-0.7439889406050374</v>
@@ -35035,7 +35079,7 @@
         <v>-70.22431396363912</v>
       </c>
       <c r="D669" t="n">
-        <v>-0.1453666634091696</v>
+        <v>-0.1506585114274143</v>
       </c>
       <c r="E669" t="n">
         <v>-1.250582599579824</v>
@@ -35053,7 +35097,7 @@
         <v>-50.30014702990232</v>
       </c>
       <c r="D670" t="n">
-        <v>-0.4531393060849936</v>
+        <v>-0.4556415710604401</v>
       </c>
       <c r="E670" t="n">
         <v>-0.9017633702656536</v>
@@ -35071,7 +35115,7 @@
         <v>-36.89828380075346</v>
       </c>
       <c r="D671" t="n">
-        <v>-0.9329025431973078</v>
+        <v>-0.9310563404883924</v>
       </c>
       <c r="E671" t="n">
         <v>-0.667132350634417</v>
@@ -35089,7 +35133,7 @@
         <v>-47.41770732578844</v>
       </c>
       <c r="D672" t="n">
-        <v>-1.077736727985931</v>
+        <v>-1.074577780315699</v>
       </c>
       <c r="E672" t="n">
         <v>-0.8512995089921827</v>
@@ -35107,7 +35151,7 @@
         <v>-27.20440596853004</v>
       </c>
       <c r="D673" t="n">
-        <v>-0.6160777639721947</v>
+        <v>-0.6171031908661599</v>
       </c>
       <c r="E673" t="n">
         <v>-0.4974183040824234</v>
@@ -35125,7 +35169,7 @@
         <v>-12.37795062677713</v>
       </c>
       <c r="D674" t="n">
-        <v>-0.1182102537613027</v>
+        <v>-0.1237482414597943</v>
       </c>
       <c r="E674" t="n">
         <v>-0.237846461356387</v>
@@ -35143,7 +35187,7 @@
         <v>16.24661581904457</v>
       </c>
       <c r="D675" t="n">
-        <v>0.415865802646745</v>
+        <v>0.4054870679033978</v>
       </c>
       <c r="E675" t="n">
         <v>0.2632936485559095</v>
@@ -35161,7 +35205,7 @@
         <v>12.34008019858699</v>
       </c>
       <c r="D676" t="n">
-        <v>-0.04579316136699114</v>
+        <v>-0.05198752154614115</v>
       </c>
       <c r="E676" t="n">
         <v>0.19490058856257</v>
@@ -35179,7 +35223,7 @@
         <v>-53.17305915725635</v>
       </c>
       <c r="D677" t="n">
-        <v>-1.141101683830954</v>
+        <v>-1.137368410240145</v>
       </c>
       <c r="E677" t="n">
         <v>-0.9520604289825281</v>
@@ -35197,7 +35241,7 @@
         <v>-67.38827964871861</v>
       </c>
       <c r="D678" t="n">
-        <v>-0.2902008481977927</v>
+        <v>-0.2941799512547206</v>
       </c>
       <c r="E678" t="n">
         <v>-1.200931173383227</v>
@@ -35215,7 +35259,7 @@
         <v>-7.706064054625256</v>
       </c>
       <c r="D679" t="n">
-        <v>0.02662393102732041</v>
+        <v>0.01977319836751201</v>
       </c>
       <c r="E679" t="n">
         <v>-0.1560541395513619</v>
@@ -35233,7 +35277,7 @@
         <v>-11.77042171406361</v>
       </c>
       <c r="D680" t="n">
-        <v>0.3977615295481671</v>
+        <v>0.3875468879249845</v>
       </c>
       <c r="E680" t="n">
         <v>-0.2272102441522452</v>
@@ -35251,7 +35295,7 @@
         <v>-32.36421603977681</v>
       </c>
       <c r="D681" t="n">
-        <v>0.8503683570126144</v>
+        <v>0.8360513873853167</v>
       </c>
       <c r="E681" t="n">
         <v>-0.5877528700618019</v>
@@ -35269,7 +35313,7 @@
         <v>4.372500725784554</v>
       </c>
       <c r="D682" t="n">
-        <v>1.094776043843416</v>
+        <v>1.078243817093896</v>
       </c>
       <c r="E682" t="n">
         <v>0.05540943992657019</v>
@@ -35287,7 +35331,7 @@
         <v>-50.41727710339055</v>
       </c>
       <c r="D683" t="n">
-        <v>1.167193136237727</v>
+        <v>1.150004537007549</v>
       </c>
       <c r="E683" t="n">
         <v>-0.9038140066661394</v>
@@ -35305,7 +35349,7 @@
         <v>31.29863168984148</v>
       </c>
       <c r="D684" t="n">
-        <v>0.9318375859562148</v>
+        <v>0.9167821972881766</v>
       </c>
       <c r="E684" t="n">
         <v>0.5268144568857021</v>
@@ -35323,7 +35367,7 @@
         <v>-25.89206426974745</v>
       </c>
       <c r="D685" t="n">
-        <v>0.8594204935619033</v>
+        <v>0.8450214773745234</v>
       </c>
       <c r="E685" t="n">
         <v>-0.4744426875114204</v>
@@ -35341,7 +35385,7 @@
         <v>-27.15696257082137</v>
       </c>
       <c r="D686" t="n">
-        <v>0.8141598108154586</v>
+        <v>0.8001710274284901</v>
       </c>
       <c r="E686" t="n">
         <v>-0.4965876962341845</v>
@@ -35359,7 +35403,7 @@
         <v>-49.45561992372857</v>
       </c>
       <c r="D687" t="n">
-        <v>0.3162923006045666</v>
+        <v>0.3068160780221246</v>
       </c>
       <c r="E687" t="n">
         <v>-0.8869779443409369</v>
@@ -35377,7 +35421,7 @@
         <v>-26.12659919801413</v>
       </c>
       <c r="D688" t="n">
-        <v>-0.3626179405921042</v>
+        <v>-0.3659406711683738</v>
       </c>
       <c r="E688" t="n">
         <v>-0.4785487710027563</v>
@@ -35395,7 +35439,7 @@
         <v>-1.743307719896966</v>
       </c>
       <c r="D689" t="n">
-        <v>-0.887641860450863</v>
+        <v>-0.8862058905423591</v>
       </c>
       <c r="E689" t="n">
         <v>-0.05166211773255953</v>
@@ -35413,7 +35457,7 @@
         <v>-22.90959141844078</v>
       </c>
       <c r="D690" t="n">
-        <v>-1.403613643760333</v>
+        <v>-1.397501019927138</v>
       </c>
       <c r="E690" t="n">
         <v>-0.4222275115944963</v>
@@ -35431,7 +35475,7 @@
         <v>16.24126158348236</v>
       </c>
       <c r="D691" t="n">
-        <v>-1.240675185873132</v>
+        <v>-1.236039400121418</v>
       </c>
       <c r="E691" t="n">
         <v>0.2631999101161249</v>
@@ -35449,7 +35493,7 @@
         <v>104.2927166331973</v>
       </c>
       <c r="D692" t="n">
-        <v>-0.6703905832679283</v>
+        <v>-0.6709237308013997</v>
       </c>
       <c r="E692" t="n">
         <v>1.804746956603979</v>
@@ -35467,7 +35511,7 @@
         <v>16.17072152427224</v>
       </c>
       <c r="D693" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E693" t="n">
         <v>0.2619649410872423</v>
@@ -35485,7 +35529,7 @@
         <v>-33.19036158118017</v>
       </c>
       <c r="D694" t="n">
-        <v>-0.6613384467186394</v>
+        <v>-0.661953640812193</v>
       </c>
       <c r="E694" t="n">
         <v>-0.6022164836227634</v>
@@ -35503,7 +35547,7 @@
         <v>-57.65749267475931</v>
       </c>
       <c r="D695" t="n">
-        <v>-1.159205956929531</v>
+        <v>-1.155308590218558</v>
       </c>
       <c r="E695" t="n">
         <v>-1.030570945818106</v>
@@ -35521,7 +35565,7 @@
         <v>30.54085524005493</v>
       </c>
       <c r="D696" t="n">
-        <v>-1.349300824464599</v>
+        <v>-1.343680479991898</v>
       </c>
       <c r="E696" t="n">
         <v>0.5135478044788003</v>
@@ -35539,7 +35583,7 @@
         <v>-47.36197446183053</v>
       </c>
       <c r="D697" t="n">
-        <v>-1.285935868619576</v>
+        <v>-1.280889850067451</v>
       </c>
       <c r="E697" t="n">
         <v>-0.8503237746130277</v>
@@ -35557,7 +35601,7 @@
         <v>22.17401040192323</v>
       </c>
       <c r="D698" t="n">
-        <v>-0.2177837558034811</v>
+        <v>-0.2224192313410674</v>
       </c>
       <c r="E698" t="n">
         <v>0.367066580047452</v>
@@ -35575,7 +35619,7 @@
         <v>53.40164769584585</v>
       </c>
       <c r="D699" t="n">
-        <v>0.415865802646745</v>
+        <v>0.4054870679033978</v>
       </c>
       <c r="E699" t="n">
         <v>0.913779544779955</v>
@@ -35593,7 +35637,7 @@
         <v>49.94271529501625</v>
       </c>
       <c r="D700" t="n">
-        <v>0.5697521239846571</v>
+        <v>0.5579785977199107</v>
       </c>
       <c r="E700" t="n">
         <v>0.8532228279887397</v>
@@ -35611,7 +35655,7 @@
         <v>26.24851916660326</v>
       </c>
       <c r="D701" t="n">
-        <v>0.587856397083235</v>
+        <v>0.575918777698324</v>
       </c>
       <c r="E701" t="n">
         <v>0.438400403532084</v>
@@ -35629,7 +35673,7 @@
         <v>-15.53986325758142</v>
       </c>
       <c r="D702" t="n">
-        <v>0.7055341722239913</v>
+        <v>0.6925299475580105</v>
       </c>
       <c r="E702" t="n">
         <v>-0.2932031510841939</v>
@@ -35647,7 +35691,7 @@
         <v>-39.76589172492278</v>
       </c>
       <c r="D703" t="n">
-        <v>0.7145863087732802</v>
+        <v>0.7015000375472171</v>
       </c>
       <c r="E703" t="n">
         <v>-0.717336546845513</v>
@@ -35665,7 +35709,7 @@
         <v>107.5316879359116</v>
       </c>
       <c r="D704" t="n">
-        <v>1.112880316941994</v>
+        <v>1.09618399707231</v>
       </c>
       <c r="E704" t="n">
         <v>1.861452738950665</v>
@@ -35683,7 +35727,7 @@
         <v>272.7654002353209</v>
       </c>
       <c r="D705" t="n">
-        <v>1.48401791546284</v>
+        <v>1.463957686629782</v>
       </c>
       <c r="E705" t="n">
         <v>4.754256055279313</v>
@@ -35701,7 +35745,7 @@
         <v>4.934398441670347</v>
       </c>
       <c r="D706" t="n">
-        <v>1.140036726589861</v>
+        <v>1.123094267039929</v>
       </c>
       <c r="E706" t="n">
         <v>0.06524677610531877</v>
@@ -35719,7 +35763,7 @@
         <v>19.78730640435328</v>
       </c>
       <c r="D707" t="n">
-        <v>0.5335435777875013</v>
+        <v>0.5220982377630841</v>
       </c>
       <c r="E707" t="n">
         <v>0.3252817339456201</v>
@@ -35737,7 +35781,7 @@
         <v>-20.43347277241449</v>
       </c>
       <c r="D708" t="n">
-        <v>-0.03674102481770224</v>
+        <v>-0.04301743155693454</v>
       </c>
       <c r="E708" t="n">
         <v>-0.3788772525513018</v>
@@ -35755,7 +35799,7 @@
         <v>-49.40922751193137</v>
       </c>
       <c r="D709" t="n">
-        <v>-0.1906273461556143</v>
+        <v>-0.1955089613734475</v>
       </c>
       <c r="E709" t="n">
         <v>-0.8861657364637923</v>
@@ -35773,7 +35817,7 @@
         <v>56.54852188755617</v>
       </c>
       <c r="D710" t="n">
-        <v>0.06283247722447617</v>
+        <v>0.05565355832433857</v>
       </c>
       <c r="E710" t="n">
         <v>0.9688729513927241</v>
@@ -35791,7 +35835,7 @@
         <v>-20.13332945183546</v>
       </c>
       <c r="D711" t="n">
-        <v>-0.39882648678926</v>
+        <v>-0.4018210311252003</v>
       </c>
       <c r="E711" t="n">
         <v>-0.3736225404162166</v>
@@ -35809,7 +35853,7 @@
         <v>-20.68932594997136</v>
       </c>
       <c r="D712" t="n">
-        <v>-0.5165042619300163</v>
+        <v>-0.5184322009848867</v>
       </c>
       <c r="E712" t="n">
         <v>-0.3833565619502736</v>
@@ -35827,7 +35871,7 @@
         <v>-51.194991794281</v>
       </c>
       <c r="D713" t="n">
-        <v>0.587856397083235</v>
+        <v>0.575918777698324</v>
       </c>
       <c r="E713" t="n">
         <v>-0.9174297247036832</v>
@@ -35845,7 +35889,7 @@
         <v>65.41045166888587</v>
       </c>
       <c r="D714" t="n">
-        <v>0.5244914412382123</v>
+        <v>0.5131281477738775</v>
       </c>
       <c r="E714" t="n">
         <v>1.124021797858445</v>
@@ -35863,7 +35907,7 @@
         <v>-11.33149081450171</v>
       </c>
       <c r="D715" t="n">
-        <v>0.8051076742661697</v>
+        <v>0.7912009374392834</v>
       </c>
       <c r="E715" t="n">
         <v>-0.2195257302342199</v>
@@ -35881,7 +35925,7 @@
         <v>-48.24123858262616</v>
       </c>
       <c r="D716" t="n">
-        <v>0.8956290397590591</v>
+        <v>0.88090183733135</v>
       </c>
       <c r="E716" t="n">
         <v>-0.865717353375922</v>
@@ -35899,7 +35943,7 @@
         <v>-11.98238888678026</v>
       </c>
       <c r="D717" t="n">
-        <v>0.9770982687026596</v>
+        <v>0.9616326472342097</v>
       </c>
       <c r="E717" t="n">
         <v>-0.2309212262009716</v>
@@ -35917,7 +35961,7 @@
         <v>-45.69258575963889</v>
       </c>
       <c r="D718" t="n">
-        <v>0.6783777625761245</v>
+        <v>0.6656196775903905</v>
       </c>
       <c r="E718" t="n">
         <v>-0.8210972135999164</v>
@@ -35935,7 +35979,7 @@
         <v>-34.09245500209292</v>
       </c>
       <c r="D719" t="n">
-        <v>0.5063871681396345</v>
+        <v>0.4951879677954642</v>
       </c>
       <c r="E719" t="n">
         <v>-0.6180097427787763</v>
@@ -35953,7 +35997,7 @@
         <v>-40.63468398257732</v>
       </c>
       <c r="D720" t="n">
-        <v>0.5154393046889234</v>
+        <v>0.5041580577846708</v>
       </c>
       <c r="E720" t="n">
         <v>-0.7325467911060161</v>
@@ -35971,7 +36015,7 @@
         <v>8.911237581966681</v>
       </c>
       <c r="D721" t="n">
-        <v>0.7598469915197249</v>
+        <v>0.7463504874932502</v>
       </c>
       <c r="E721" t="n">
         <v>0.134870663951576</v>
@@ -35989,7 +36033,7 @@
         <v>-10.33094339782073</v>
       </c>
       <c r="D722" t="n">
-        <v>0.4701786219424787</v>
+        <v>0.4593076078386377</v>
       </c>
       <c r="E722" t="n">
         <v>-0.2020088031807742</v>
@@ -36007,7 +36051,7 @@
         <v>32.91643620273063</v>
       </c>
       <c r="D723" t="n">
-        <v>0.3253444371538556</v>
+        <v>0.3157861680113313</v>
       </c>
       <c r="E723" t="n">
         <v>0.555137915790849</v>
@@ -36025,10 +36069,10 @@
         <v>-2.05270192858506</v>
       </c>
       <c r="D724" t="n">
-        <v>0.2800837544074108</v>
+        <v>0.2709357180652981</v>
       </c>
       <c r="E724" t="n">
-        <v>-0.05707878834106098</v>
+        <v>-0.05707878834106099</v>
       </c>
       <c r="F724" t="inlineStr"/>
     </row>
@@ -36043,7 +36087,7 @@
         <v>69.92359443097958</v>
       </c>
       <c r="D725" t="n">
-        <v>0.1171452965202099</v>
+        <v>0.1094740982595784</v>
       </c>
       <c r="E725" t="n">
         <v>1.203034937293284</v>
@@ -36061,7 +36105,7 @@
         <v>68.75869600993401</v>
       </c>
       <c r="D726" t="n">
-        <v>0.4339700757453229</v>
+        <v>0.423427247881811</v>
       </c>
       <c r="E726" t="n">
         <v>1.182640660794307</v>
@@ -36079,7 +36123,7 @@
         <v>11.39652089091204</v>
       </c>
       <c r="D727" t="n">
-        <v>0.2257709351116772</v>
+        <v>0.2171151781300582</v>
       </c>
       <c r="E727" t="n">
         <v>0.1783813718941892</v>
@@ -36097,7 +36141,7 @@
         <v>147.6733389475503</v>
       </c>
       <c r="D728" t="n">
-        <v>-0.7156512660143731</v>
+        <v>-0.7157741807474329</v>
       </c>
       <c r="E728" t="n">
         <v>2.564226401500585</v>
@@ -36115,7 +36159,7 @@
         <v>-37.65893650130944</v>
       </c>
       <c r="D729" t="n">
-        <v>-0.9691110893944637</v>
+        <v>-0.966936700445219</v>
       </c>
       <c r="E729" t="n">
         <v>-0.6804493585507886</v>
@@ -36133,7 +36177,7 @@
         <v>11.11527331641397</v>
       </c>
       <c r="D730" t="n">
-        <v>-0.887641860450863</v>
+        <v>-0.8862058905423591</v>
       </c>
       <c r="E730" t="n">
         <v>0.1734574740715514</v>
@@ -36151,7 +36195,7 @@
         <v>-10.64514441188782</v>
       </c>
       <c r="D731" t="n">
-        <v>-0.9419546797465966</v>
+        <v>-0.940026430477599</v>
       </c>
       <c r="E731" t="n">
         <v>-0.2075096281809418</v>
@@ -36169,7 +36213,7 @@
         <v>13.72191452528077</v>
       </c>
       <c r="D732" t="n">
-        <v>-0.9691110893944637</v>
+        <v>-0.966936700445219</v>
       </c>
       <c r="E732" t="n">
         <v>0.2190928364231831</v>
@@ -36187,7 +36231,7 @@
         <v>40.52554910563914</v>
       </c>
       <c r="D733" t="n">
-        <v>-0.5979734908736168</v>
+        <v>-0.5991630108877466</v>
       </c>
       <c r="E733" t="n">
         <v>0.6883532671470356</v>
@@ -36205,7 +36249,7 @@
         <v>-9.627482709232016</v>
       </c>
       <c r="D734" t="n">
-        <v>-0.2177837558034811</v>
+        <v>-0.2224192313410674</v>
       </c>
       <c r="E734" t="n">
         <v>-0.1896930754485979</v>
@@ -36223,7 +36267,7 @@
         <v>16.14836540420948</v>
       </c>
       <c r="D735" t="n">
-        <v>0.07188461377376512</v>
+        <v>0.06462364831354522</v>
       </c>
       <c r="E735" t="n">
         <v>0.2615735448197506</v>
@@ -36241,7 +36285,7 @@
         <v>-57.19400420087837</v>
       </c>
       <c r="D736" t="n">
-        <v>-0.5798692177750389</v>
+        <v>-0.5812228309093332</v>
       </c>
       <c r="E736" t="n">
         <v>-1.022456494017294</v>
@@ -36259,7 +36303,7 @@
         <v>43.19251377582628</v>
       </c>
       <c r="D737" t="n">
-        <v>0.04472820412589829</v>
+        <v>0.03771337834592529</v>
       </c>
       <c r="E737" t="n">
         <v>0.7350447330415306</v>
@@ -36277,7 +36321,7 @@
         <v>-13.17903681871905</v>
       </c>
       <c r="D738" t="n">
-        <v>0.3162923006045666</v>
+        <v>0.3068160780221246</v>
       </c>
       <c r="E738" t="n">
         <v>-0.2518713522849131</v>
@@ -36295,10 +36339,10 @@
         <v>99.86993984717932</v>
       </c>
       <c r="D739" t="n">
-        <v>0.4882828950410565</v>
+        <v>0.4772477878170509</v>
       </c>
       <c r="E739" t="n">
-        <v>1.727315885329671</v>
+        <v>1.72731588532967</v>
       </c>
       <c r="F739" t="inlineStr"/>
     </row>
@@ -36313,10 +36357,10 @@
         <v>68.64243916132236</v>
       </c>
       <c r="D740" t="n">
-        <v>0.3072401640552777</v>
+        <v>0.297845988032918</v>
       </c>
       <c r="E740" t="n">
-        <v>1.180605312241463</v>
+        <v>1.180605312241462</v>
       </c>
       <c r="F740" t="inlineStr"/>
     </row>
@@ -36331,7 +36375,7 @@
         <v>-53.25843549550232</v>
       </c>
       <c r="D741" t="n">
-        <v>0.02662393102732041</v>
+        <v>0.01977319836751201</v>
       </c>
       <c r="E741" t="n">
         <v>-0.9535551418409209</v>
@@ -36349,7 +36393,7 @@
         <v>19.29088508255215</v>
       </c>
       <c r="D742" t="n">
-        <v>-0.4531393060849936</v>
+        <v>-0.4556415710604401</v>
       </c>
       <c r="E742" t="n">
         <v>0.3165907154723415</v>
@@ -36367,7 +36411,7 @@
         <v>-15.49157597321055</v>
       </c>
       <c r="D743" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E743" t="n">
         <v>-0.2923577690225026</v>
@@ -36385,7 +36429,7 @@
         <v>25.12552597694634</v>
       </c>
       <c r="D744" t="n">
-        <v>-0.2992529847470816</v>
+        <v>-0.3031500412439272</v>
       </c>
       <c r="E744" t="n">
         <v>0.4187397763026512</v>
@@ -36403,7 +36447,7 @@
         <v>90.85385325395129</v>
       </c>
       <c r="D745" t="n">
-        <v>-0.39882648678926</v>
+        <v>-0.4018210311252003</v>
       </c>
       <c r="E745" t="n">
         <v>1.569468162644997</v>
@@ -36421,7 +36465,7 @@
         <v>113.871061782016</v>
       </c>
       <c r="D746" t="n">
-        <v>0.05378034067518724</v>
+        <v>0.04668346833513194</v>
       </c>
       <c r="E746" t="n">
         <v>1.972438332811969</v>
@@ -36439,10 +36483,10 @@
         <v>85.23478210241333</v>
       </c>
       <c r="D747" t="n">
-        <v>0.5425957143367902</v>
+        <v>0.5310683277522907</v>
       </c>
       <c r="E747" t="n">
-        <v>1.4710931552954</v>
+        <v>1.471093155295399</v>
       </c>
       <c r="F747" t="inlineStr"/>
     </row>
@@ -36457,7 +36501,7 @@
         <v>38.71491311819744</v>
       </c>
       <c r="D748" t="n">
-        <v>0.3615529833510114</v>
+        <v>0.3516665279681578</v>
       </c>
       <c r="E748" t="n">
         <v>0.6566538414290909</v>
@@ -36475,10 +36519,10 @@
         <v>1.707441663315543</v>
       </c>
       <c r="D749" t="n">
-        <v>1.031411087998393</v>
+        <v>1.01545318716945</v>
       </c>
       <c r="E749" t="n">
-        <v>0.008751336160480362</v>
+        <v>0.008751336160480357</v>
       </c>
       <c r="F749" t="inlineStr"/>
     </row>
@@ -36493,7 +36537,7 @@
         <v>57.56496760970062</v>
       </c>
       <c r="D750" t="n">
-        <v>1.004254678350526</v>
+        <v>0.9885429172018296</v>
       </c>
       <c r="E750" t="n">
         <v>0.9866682155368806</v>
@@ -36511,7 +36555,7 @@
         <v>5.186148593724606</v>
       </c>
       <c r="D751" t="n">
-        <v>1.140036726589861</v>
+        <v>1.123094267039929</v>
       </c>
       <c r="E751" t="n">
         <v>0.06965425242848679</v>
@@ -36529,7 +36573,7 @@
         <v>-53.83386236531278</v>
       </c>
       <c r="D752" t="n">
-        <v>0.5788042605339461</v>
+        <v>0.5669486877091173</v>
       </c>
       <c r="E752" t="n">
         <v>-0.9636293375611987</v>
@@ -36547,7 +36591,7 @@
         <v>-51.97745473867992</v>
       </c>
       <c r="D753" t="n">
-        <v>0.2800837544074108</v>
+        <v>0.2709357180652981</v>
       </c>
       <c r="E753" t="n">
         <v>-0.9311285720451985</v>
@@ -36565,7 +36609,7 @@
         <v>-48.33350502430207</v>
       </c>
       <c r="D754" t="n">
-        <v>0.2710316178581219</v>
+        <v>0.2619656280760914</v>
       </c>
       <c r="E754" t="n">
         <v>-0.867332693640034</v>
@@ -36583,7 +36627,7 @@
         <v>-5.602501046462957</v>
       </c>
       <c r="D755" t="n">
-        <v>-0.1182102537613027</v>
+        <v>-0.1237482414597943</v>
       </c>
       <c r="E755" t="n">
         <v>-0.1192263399368887</v>
@@ -36601,7 +36645,7 @@
         <v>28.26752589069537</v>
       </c>
       <c r="D756" t="n">
-        <v>-0.1544187999584585</v>
+        <v>-0.1596286014166209</v>
       </c>
       <c r="E756" t="n">
         <v>0.4737478472580964</v>
@@ -36619,7 +36663,7 @@
         <v>-21.88942208846057</v>
       </c>
       <c r="D757" t="n">
-        <v>-0.5527128081271721</v>
+        <v>-0.5543125609417133</v>
       </c>
       <c r="E757" t="n">
         <v>-0.4043670569698616</v>
@@ -36637,7 +36681,7 @@
         <v>13.13675867284644</v>
       </c>
       <c r="D758" t="n">
-        <v>-0.39882648678926</v>
+        <v>-0.4018210311252003</v>
       </c>
       <c r="E758" t="n">
         <v>0.2088483120647166</v>
@@ -36655,7 +36699,7 @@
         <v>2.218639923146351</v>
       </c>
       <c r="D759" t="n">
-        <v>-0.4440871695357047</v>
+        <v>-0.4466714810712336</v>
       </c>
       <c r="E759" t="n">
         <v>0.01770105955990604</v>
@@ -36673,7 +36717,7 @@
         <v>27.9071987779263</v>
       </c>
       <c r="D760" t="n">
-        <v>-0.3897743502399711</v>
+        <v>-0.3928509411359937</v>
       </c>
       <c r="E760" t="n">
         <v>0.467439476815552</v>
@@ -36691,7 +36735,7 @@
         <v>12.70636568161811</v>
       </c>
       <c r="D761" t="n">
-        <v>-0.896693997000152</v>
+        <v>-0.8951759805315658</v>
       </c>
       <c r="E761" t="n">
         <v>0.2013132742384534</v>
@@ -36709,7 +36753,7 @@
         <v>14.51354707440043</v>
       </c>
       <c r="D762" t="n">
-        <v>-1.213518776225265</v>
+        <v>-1.209129130153798</v>
       </c>
       <c r="E762" t="n">
         <v>0.2329522191819353</v>
@@ -36727,7 +36771,7 @@
         <v>-34.59600065030077</v>
       </c>
       <c r="D763" t="n">
-        <v>-1.5122392823518</v>
+        <v>-1.505142099797617</v>
       </c>
       <c r="E763" t="n">
         <v>-0.6268254892798233</v>
@@ -36745,7 +36789,7 @@
         <v>-14.49115760834358</v>
       </c>
       <c r="D764" t="n">
-        <v>-1.231623049323843</v>
+        <v>-1.227069310132212</v>
       </c>
       <c r="E764" t="n">
         <v>-0.2748431013234608</v>
@@ -36763,7 +36807,7 @@
         <v>-36.43488822256803</v>
       </c>
       <c r="D765" t="n">
-        <v>-0.8333290411551293</v>
+        <v>-0.8323853506071192</v>
       </c>
       <c r="E765" t="n">
         <v>-0.6590195251904314</v>
@@ -36781,10 +36825,10 @@
         <v>2.630617806538627</v>
       </c>
       <c r="D766" t="n">
-        <v>-0.4802957157328605</v>
+        <v>-0.4825518410280601</v>
       </c>
       <c r="E766" t="n">
-        <v>0.02491369777245013</v>
+        <v>0.02491369777245012</v>
       </c>
       <c r="F766" t="inlineStr"/>
     </row>
@@ -36799,7 +36843,7 @@
         <v>90.93370657178735</v>
       </c>
       <c r="D767" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E767" t="n">
         <v>1.570866182089343</v>
@@ -36817,7 +36861,7 @@
         <v>-63.70065981998189</v>
       </c>
       <c r="D768" t="n">
-        <v>-0.2902008481977927</v>
+        <v>-0.2941799512547206</v>
       </c>
       <c r="E768" t="n">
         <v>-1.136370747296577</v>
@@ -36835,7 +36879,7 @@
         <v>-40.90525330382022</v>
       </c>
       <c r="D769" t="n">
-        <v>-0.1815752096063253</v>
+        <v>-0.1865388713842409</v>
       </c>
       <c r="E769" t="n">
         <v>-0.7372837410836935</v>
@@ -36853,7 +36897,7 @@
         <v>-16.46562760100892</v>
       </c>
       <c r="D770" t="n">
-        <v>0.2076666620130993</v>
+        <v>0.1991749981516449</v>
       </c>
       <c r="E770" t="n">
         <v>-0.3094108252055204</v>
@@ -36871,7 +36915,7 @@
         <v>-13.45775959942941</v>
       </c>
       <c r="D771" t="n">
-        <v>-0.3354615309442374</v>
+        <v>-0.3390304012007538</v>
       </c>
       <c r="E771" t="n">
         <v>-0.2567510476760949</v>
@@ -36889,7 +36933,7 @@
         <v>-28.01222073706319</v>
       </c>
       <c r="D772" t="n">
-        <v>-0.06389743446556904</v>
+        <v>-0.06992770152455445</v>
       </c>
       <c r="E772" t="n">
         <v>-0.5115609945108603</v>
@@ -36907,7 +36951,7 @@
         <v>-35.5932571813627</v>
       </c>
       <c r="D773" t="n">
-        <v>0.1895623889145214</v>
+        <v>0.1812348181732316</v>
       </c>
       <c r="E773" t="n">
         <v>-0.6442848016691671</v>
@@ -36925,7 +36969,7 @@
         <v>43.21150192247272</v>
       </c>
       <c r="D774" t="n">
-        <v>1.176245272787016</v>
+        <v>1.158974626996756</v>
       </c>
       <c r="E774" t="n">
         <v>0.7353771650423939</v>
@@ -36943,7 +36987,7 @@
         <v>30.59665095106487</v>
       </c>
       <c r="D775" t="n">
-        <v>1.610747827152886</v>
+        <v>1.589538946478675</v>
       </c>
       <c r="E775" t="n">
         <v>0.5145246391428669</v>
@@ -36961,7 +37005,7 @@
         <v>15.09144695644663</v>
       </c>
       <c r="D776" t="n">
-        <v>1.103828180392705</v>
+        <v>1.087213907083103</v>
       </c>
       <c r="E776" t="n">
         <v>0.243069710776265</v>
@@ -36979,7 +37023,7 @@
         <v>10.90446730178011</v>
       </c>
       <c r="D777" t="n">
-        <v>1.022358951449104</v>
+        <v>1.006483097180243</v>
       </c>
       <c r="E777" t="n">
         <v>0.1697668208159383</v>
@@ -36997,7 +37041,7 @@
         <v>131.7266180312977</v>
       </c>
       <c r="D778" t="n">
-        <v>0.940889722505504</v>
+        <v>0.9257522872773832</v>
       </c>
       <c r="E778" t="n">
         <v>2.285041684839906</v>
@@ -37015,7 +37059,7 @@
         <v>61.73739012138972</v>
       </c>
       <c r="D779" s="4" t="n">
-        <v>0.8413162204633253</v>
+        <v>0.82708129739611</v>
       </c>
       <c r="E779" s="4" t="n">
         <v>1.059716248598483</v>
@@ -37037,7 +37081,7 @@
         <v>-60.17053050512269</v>
       </c>
       <c r="D780" s="4" t="n">
-        <v>0.940889722505504</v>
+        <v>0.9257522872773832</v>
       </c>
       <c r="E780" s="4" t="n">
         <v>-1.074567561693694</v>
@@ -37059,7 +37103,7 @@
         <v>-3.923464232126998</v>
       </c>
       <c r="D781" s="4" t="n">
-        <v>0.587856397083235</v>
+        <v>0.575918777698324</v>
       </c>
       <c r="E781" s="4" t="n">
         <v>-0.08983086611283229</v>
@@ -37081,7 +37125,7 @@
         <v>-8.138174044201833</v>
       </c>
       <c r="D782" s="4" t="n">
-        <v>0.07188461377376512</v>
+        <v>0.06462364831354522</v>
       </c>
       <c r="E782" s="4" t="n">
         <v>-0.1636192374570532</v>
@@ -37103,7 +37147,7 @@
         <v>-24.22709673663067</v>
       </c>
       <c r="D783" s="4" t="n">
-        <v>-0.2630444385499259</v>
+        <v>-0.2672696812871007</v>
       </c>
       <c r="E783" s="4" t="n">
         <v>-0.4452935294228323</v>
@@ -37125,7 +37169,7 @@
         <v>30.11265991980142</v>
       </c>
       <c r="D784" s="4" t="n">
-        <v>0.2981880275059887</v>
+        <v>0.2888758980437114</v>
       </c>
       <c r="E784" s="4" t="n">
         <v>0.5060512420326257</v>
@@ -37147,7 +37191,7 @@
         <v>5.505983110347904</v>
       </c>
       <c r="D785" s="4" t="n">
-        <v>1.121932453491283</v>
+        <v>1.105154087061516</v>
       </c>
       <c r="E785" s="4" t="n">
         <v>0.07525370509155907</v>
@@ -37169,7 +37213,7 @@
         <v>135.9839020960189</v>
       </c>
       <c r="D786" s="4" t="n">
-        <v>1.619799963702175</v>
+        <v>1.598509036467882</v>
       </c>
       <c r="E786" s="4" t="n">
         <v>2.359575418238465</v>
@@ -37191,7 +37235,7 @@
         <v>196.3095431637132</v>
       </c>
       <c r="D787" s="4" t="n">
-        <v>2.199136702856667</v>
+        <v>2.172594795777107</v>
       </c>
       <c r="E787" s="4" t="n">
         <v>3.415717122687126</v>
@@ -37213,7 +37257,7 @@
         <v>148.9473343266179</v>
       </c>
       <c r="D788" s="4" t="n">
-        <v>2.51596148208178</v>
+        <v>2.48654794539934</v>
       </c>
       <c r="E788" s="4" t="n">
         <v>2.586530675890281</v>
@@ -37235,7 +37279,7 @@
         <v>-69.54112422666718</v>
       </c>
       <c r="D789" s="4" t="n">
-        <v>1.710321329195064</v>
+        <v>1.688209936359948</v>
       </c>
       <c r="E789" s="4" t="n">
         <v>-1.238621762355439</v>
@@ -37257,7 +37301,7 @@
         <v>-55.52579578764012</v>
       </c>
       <c r="D790" s="4" t="n">
-        <v>2.280605931800267</v>
+        <v>2.253325605679966</v>
       </c>
       <c r="E790" s="4" t="n">
         <v>-0.9932505967280141</v>
@@ -37279,7 +37323,7 @@
         <v>88.81461908748432</v>
       </c>
       <c r="D791" s="4" t="n">
-        <v>2.135771747011645</v>
+        <v>2.109804165852661</v>
       </c>
       <c r="E791" s="4" t="n">
         <v>1.533766590142426</v>
@@ -37301,7 +37345,7 @@
         <v>20.8376202123006</v>
       </c>
       <c r="D792" s="4" t="n">
-        <v>2.280605931800267</v>
+        <v>2.253325605679966</v>
       </c>
       <c r="E792" s="4" t="n">
         <v>0.3436699382928672</v>
@@ -37323,7 +37367,7 @@
         <v>-19.18599818896845</v>
       </c>
       <c r="D793" s="4" t="n">
-        <v>2.217240975955245</v>
+        <v>2.19053497575552</v>
       </c>
       <c r="E793" s="4" t="n">
         <v>-0.3570372868335958</v>
@@ -37345,7 +37389,7 @@
         <v>11.08341396020907</v>
       </c>
       <c r="D794" s="4" t="n">
-        <v>1.837051240885109</v>
+        <v>1.813791196208841</v>
       </c>
       <c r="E794" s="4" t="n">
         <v>0.1728997013870122</v>
@@ -37367,7 +37411,7 @@
         <v>-8.829073389420975</v>
       </c>
       <c r="D795" s="4" t="n">
-        <v>1.393496549969951</v>
+        <v>1.374256786737716</v>
       </c>
       <c r="E795" s="4" t="n">
         <v>-0.1757150494392813</v>
@@ -37389,7 +37433,7 @@
         <v>30.19381325186177</v>
       </c>
       <c r="D796" s="4" t="n">
-        <v>1.438757232716396</v>
+        <v>1.419107236683749</v>
       </c>
       <c r="E796" s="4" t="n">
         <v>0.5074720212722152</v>
@@ -37411,7 +37455,7 @@
         <v>17.92324663891576</v>
       </c>
       <c r="D797" s="4" t="n">
-        <v>0.6240649432803909</v>
+        <v>0.6117991376551506</v>
       </c>
       <c r="E797" s="4" t="n">
         <v>0.2926469998090334</v>
@@ -37433,7 +37477,7 @@
         <v>-43.30425936176898</v>
       </c>
       <c r="D798" t="n">
-        <v>0.6602734894775465</v>
+        <v>0.6476794976119772</v>
       </c>
       <c r="E798" t="n">
         <v>-0.7792839635791576</v>
@@ -37451,7 +37495,7 @@
         <v>31.6533896927329</v>
       </c>
       <c r="D799" t="n">
-        <v>0.7960555377168808</v>
+        <v>0.7822308474500768</v>
       </c>
       <c r="E799" t="n">
         <v>0.5330253270100678</v>
@@ -37469,7 +37513,7 @@
         <v>-46.42741465310618</v>
       </c>
       <c r="D800" t="n">
-        <v>0.4430222122946119</v>
+        <v>0.4323973378710177</v>
       </c>
       <c r="E800" t="n">
         <v>-0.8339621152617782</v>
@@ -37487,7 +37531,7 @@
         <v>-58.66702091319694</v>
       </c>
       <c r="D801" t="n">
-        <v>0.4339700757453229</v>
+        <v>0.423427247881811</v>
       </c>
       <c r="E801" t="n">
         <v>-1.048245103200639</v>
@@ -37505,7 +37549,7 @@
         <v>115.2630149558442</v>
       </c>
       <c r="D802" t="n">
-        <v>0.7326905818718581</v>
+        <v>0.7194402175256303</v>
       </c>
       <c r="E802" t="n">
         <v>1.996807734802577</v>
@@ -37523,7 +37567,7 @@
         <v>-66.42816031812474</v>
       </c>
       <c r="D803" t="n">
-        <v>0.5244914412382123</v>
+        <v>0.5131281477738775</v>
       </c>
       <c r="E803" t="n">
         <v>-1.184122034709514</v>
@@ -37541,7 +37585,7 @@
         <v>-52.07526013911051</v>
       </c>
       <c r="D804" t="n">
-        <v>0.3253444371538556</v>
+        <v>0.3157861680113313</v>
       </c>
       <c r="E804" t="n">
         <v>-0.9328408847614303</v>
@@ -37559,7 +37603,7 @@
         <v>-14.93401108491288</v>
       </c>
       <c r="D805" t="n">
-        <v>0.6059606701818129</v>
+        <v>0.5938589576767372</v>
       </c>
       <c r="E805" t="n">
         <v>-0.2825962891435465</v>
@@ -37577,7 +37621,7 @@
         <v>38.98735460756191</v>
       </c>
       <c r="D806" t="n">
-        <v>1.05856749764626</v>
+        <v>1.042363457137069</v>
       </c>
       <c r="E806" t="n">
         <v>0.661423568096679</v>
@@ -37595,7 +37639,7 @@
         <v>58.33054350673925</v>
       </c>
       <c r="D807" t="n">
-        <v>1.447809369265685</v>
+        <v>1.428077326672955</v>
       </c>
       <c r="E807" t="n">
         <v>1.00007141554392</v>
@@ -37613,7 +37657,7 @@
         <v>85.45445865953792</v>
       </c>
       <c r="D808" t="n">
-        <v>1.674112782997909</v>
+        <v>1.652329576403122</v>
       </c>
       <c r="E808" t="n">
         <v>1.474939108183138</v>
@@ -37631,7 +37675,7 @@
         <v>77.50437457205273</v>
       </c>
       <c r="D809" t="n">
-        <v>1.167193136237727</v>
+        <v>1.150004537007549</v>
       </c>
       <c r="E809" t="n">
         <v>1.335754257263033</v>
@@ -37649,7 +37693,7 @@
         <v>118.9823611256564</v>
       </c>
       <c r="D810" t="n">
-        <v>0.4068136660974561</v>
+        <v>0.3965169779141911</v>
       </c>
       <c r="E810" t="n">
         <v>2.061923604832238</v>
@@ -37667,7 +37711,7 @@
         <v>27.89790278003577</v>
       </c>
       <c r="D811" t="n">
-        <v>-0.0005324786205464267</v>
+        <v>-0.00713707160010793</v>
       </c>
       <c r="E811" t="n">
         <v>0.4672767285897082</v>
@@ -37685,7 +37729,7 @@
         <v>-50.76763619874328</v>
       </c>
       <c r="D812" t="n">
-        <v>-0.07294957101485799</v>
+        <v>-0.07889779151376111</v>
       </c>
       <c r="E812" t="n">
         <v>-0.9099478636063366</v>
@@ -37703,7 +37747,7 @@
         <v>-46.19880821345884</v>
       </c>
       <c r="D813" t="n">
-        <v>-0.09105384411343591</v>
+        <v>-0.09683797149217441</v>
       </c>
       <c r="E813" t="n">
         <v>-0.8299598238556057</v>
@@ -37721,7 +37765,7 @@
         <v>8.474354051750787</v>
       </c>
       <c r="D814" t="n">
-        <v>-0.5165042619300163</v>
+        <v>-0.5184322009848867</v>
       </c>
       <c r="E814" t="n">
         <v>0.1272219940314339</v>
@@ -37739,7 +37783,7 @@
         <v>39.72242570113016</v>
       </c>
       <c r="D815" t="n">
-        <v>-0.5165042619300163</v>
+        <v>-0.5184322009848867</v>
       </c>
       <c r="E815" t="n">
         <v>0.6742927100388416</v>
@@ -37757,7 +37801,7 @@
         <v>-51.74257779530179</v>
       </c>
       <c r="D816" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E816" t="n">
         <v>-0.9270165007779126</v>
@@ -37775,7 +37819,7 @@
         <v>-27.34876355539612</v>
       </c>
       <c r="D817" t="n">
-        <v>-1.068684591436642</v>
+        <v>-1.065607690326492</v>
       </c>
       <c r="E817" t="n">
         <v>-0.4999456219052336</v>
@@ -37793,7 +37837,7 @@
         <v>-24.68534393523935</v>
       </c>
       <c r="D818" t="n">
-        <v>-0.7971204949579737</v>
+        <v>-0.7965049906502928</v>
       </c>
       <c r="E818" t="n">
         <v>-0.4533162204184292</v>
@@ -37811,7 +37855,7 @@
         <v>-2.273587377368928</v>
       </c>
       <c r="D819" t="n">
-        <v>-0.6613384467186394</v>
+        <v>-0.661953640812193</v>
       </c>
       <c r="E819" t="n">
         <v>-0.06094590571002057</v>
@@ -37829,7 +37873,7 @@
         <v>-44.15696009165552</v>
       </c>
       <c r="D820" t="n">
-        <v>-1.005319635591619</v>
+        <v>-1.002817060402046</v>
       </c>
       <c r="E820" t="n">
         <v>-0.7942124879397426</v>
@@ -37847,7 +37891,7 @@
         <v>-38.97879555260898</v>
       </c>
       <c r="D821" t="n">
-        <v>-0.7156512660143731</v>
+        <v>-0.7157741807474329</v>
       </c>
       <c r="E821" t="n">
         <v>-0.7035565839925747</v>
@@ -37865,7 +37909,7 @@
         <v>-18.63676485989138</v>
       </c>
       <c r="D822" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E822" t="n">
         <v>-0.3474216704216534</v>
@@ -37883,7 +37927,7 @@
         <v>22.95561697284995</v>
       </c>
       <c r="D823" t="n">
-        <v>-0.4350350329864158</v>
+        <v>-0.4377013910820269</v>
       </c>
       <c r="E823" t="n">
         <v>0.3807504345646464</v>
@@ -37901,7 +37945,7 @@
         <v>5.504091900412428</v>
       </c>
       <c r="D824" t="n">
-        <v>-0.1453666634091696</v>
+        <v>-0.1506585114274143</v>
       </c>
       <c r="E824" t="n">
         <v>0.07522059503007654</v>
@@ -37919,7 +37963,7 @@
         <v>-18.4157589099328</v>
       </c>
       <c r="D825" t="n">
-        <v>-0.02768888826841329</v>
+        <v>-0.03404734156772789</v>
       </c>
       <c r="E825" t="n">
         <v>-0.3435524433972671</v>
@@ -37937,7 +37981,7 @@
         <v>-48.92349762598215</v>
       </c>
       <c r="D826" t="n">
-        <v>0.1443017061680767</v>
+        <v>0.1363843682271984</v>
       </c>
       <c r="E826" t="n">
         <v>-0.8776618966277199</v>
@@ -37955,7 +37999,7 @@
         <v>18.53155085809962</v>
       </c>
       <c r="D827" t="n">
-        <v>0.3615529833510114</v>
+        <v>0.3516665279681578</v>
       </c>
       <c r="E827" t="n">
         <v>0.3032967905696691</v>
@@ -37973,7 +38017,7 @@
         <v>-12.46757887343902</v>
       </c>
       <c r="D828" t="n">
-        <v>0.9499418590547927</v>
+        <v>0.9347223772665899</v>
       </c>
       <c r="E828" t="n">
         <v>-0.2394156138348499</v>
@@ -37991,7 +38035,7 @@
         <v>-14.09411239769203</v>
       </c>
       <c r="D829" t="n">
-        <v>1.167193136237727</v>
+        <v>1.150004537007549</v>
       </c>
       <c r="E829" t="n">
         <v>-0.2678918945381046</v>
@@ -38009,7 +38053,7 @@
         <v>66.23219695209288</v>
       </c>
       <c r="D830" t="n">
-        <v>0.9680461321533707</v>
+        <v>0.952662557245003</v>
       </c>
       <c r="E830" t="n">
         <v>1.138408374588811</v>
@@ -38027,7 +38071,7 @@
         <v>17.1636196908387</v>
       </c>
       <c r="D831" t="n">
-        <v>0.6874298991254134</v>
+        <v>0.6745897675795972</v>
       </c>
       <c r="E831" t="n">
         <v>0.2793479500933915</v>
@@ -38045,7 +38089,7 @@
         <v>37.38781745274013</v>
       </c>
       <c r="D832" t="n">
-        <v>0.3253444371538556</v>
+        <v>0.3157861680113313</v>
       </c>
       <c r="E832" t="n">
         <v>0.6334199220993368</v>
@@ -38063,7 +38107,7 @@
         <v>-35.32154463150344</v>
       </c>
       <c r="D833" t="n">
-        <v>0.4882828950410565</v>
+        <v>0.4772477878170509</v>
       </c>
       <c r="E833" t="n">
         <v>-0.6395278367956995</v>
@@ -38081,7 +38125,7 @@
         <v>54.84508011549797</v>
       </c>
       <c r="D834" t="n">
-        <v>0.3977615295481671</v>
+        <v>0.3875468879249845</v>
       </c>
       <c r="E834" t="n">
         <v>0.939050211597025</v>
@@ -38099,7 +38143,7 @@
         <v>-28.36937083401073</v>
       </c>
       <c r="D835" t="n">
-        <v>-0.09105384411343591</v>
+        <v>-0.09683797149217441</v>
       </c>
       <c r="E835" t="n">
         <v>-0.5178137438469329</v>
@@ -38117,7 +38161,7 @@
         <v>26.64377793612748</v>
       </c>
       <c r="D836" t="n">
-        <v>-0.4078786233385489</v>
+        <v>-0.4107911211144069</v>
       </c>
       <c r="E836" t="n">
         <v>0.4453203344794427</v>
@@ -38135,7 +38179,7 @@
         <v>-25.16225756253084</v>
       </c>
       <c r="D837" t="n">
-        <v>-0.4712435791835716</v>
+        <v>-0.4735817510388535</v>
       </c>
       <c r="E837" t="n">
         <v>-0.4616657109880729</v>
@@ -38153,7 +38197,7 @@
         <v>53.59474063737933</v>
       </c>
       <c r="D838" t="n">
-        <v>-0.4259828964371268</v>
+        <v>-0.4287313010928202</v>
       </c>
       <c r="E838" t="n">
         <v>0.9171600891849343</v>
@@ -38171,7 +38215,7 @@
         <v>8.563991209711173</v>
       </c>
       <c r="D839" t="n">
-        <v>-0.4531393060849936</v>
+        <v>-0.4556415710604401</v>
       </c>
       <c r="E839" t="n">
         <v>0.1287913025230582</v>
@@ -38189,7 +38233,7 @@
         <v>103.6940061731057</v>
       </c>
       <c r="D840" t="n">
-        <v>0.1171452965202099</v>
+        <v>0.1094740982595784</v>
       </c>
       <c r="E840" t="n">
         <v>1.79426512707675</v>
@@ -38207,7 +38251,7 @@
         <v>-11.4956758341025</v>
       </c>
       <c r="D841" t="n">
-        <v>0.1805102523652325</v>
+        <v>0.172264728184025</v>
       </c>
       <c r="E841" t="n">
         <v>-0.2224001737275189</v>
@@ -38225,7 +38269,7 @@
         <v>28.124907578363</v>
       </c>
       <c r="D842" t="n">
-        <v>-0.1182102537613027</v>
+        <v>-0.1237482414597943</v>
       </c>
       <c r="E842" t="n">
         <v>0.4712509795115394</v>
@@ -38243,10 +38287,10 @@
         <v>-15.97952024686326</v>
       </c>
       <c r="D843" t="n">
-        <v>0.2348230716609661</v>
+        <v>0.2260852681192649</v>
       </c>
       <c r="E843" t="n">
-        <v>-0.3009003769041702</v>
+        <v>-0.3009003769041703</v>
       </c>
       <c r="F843" t="inlineStr"/>
     </row>
@@ -38261,7 +38305,7 @@
         <v>-39.7842276112278</v>
       </c>
       <c r="D844" t="n">
-        <v>0.1624059792666546</v>
+        <v>0.1543245482056117</v>
       </c>
       <c r="E844" t="n">
         <v>-0.717657559500696</v>
@@ -38279,7 +38323,7 @@
         <v>-16.92660500603202</v>
       </c>
       <c r="D845" t="n">
-        <v>0.4701786219424787</v>
+        <v>0.4593076078386377</v>
       </c>
       <c r="E845" t="n">
         <v>-0.3174813148619353</v>
@@ -38297,7 +38341,7 @@
         <v>18.39140647207551</v>
       </c>
       <c r="D846" t="n">
-        <v>0.08998888687234299</v>
+        <v>0.0825638282919585</v>
       </c>
       <c r="E846" t="n">
         <v>0.3008432347001455</v>
@@ -38315,10 +38359,10 @@
         <v>-15.08697772719883</v>
       </c>
       <c r="D847" t="n">
-        <v>-0.4169307598878378</v>
+        <v>-0.4197612111036136</v>
       </c>
       <c r="E847" t="n">
-        <v>-0.2852743286545794</v>
+        <v>-0.2852743286545795</v>
       </c>
       <c r="F847" t="inlineStr"/>
     </row>
@@ -38333,7 +38377,7 @@
         <v>49.38135648118159</v>
       </c>
       <c r="D848" t="n">
-        <v>-0.9419546797465966</v>
+        <v>-0.940026430477599</v>
       </c>
       <c r="E848" t="n">
         <v>0.8433949265531741</v>
@@ -38351,10 +38395,10 @@
         <v>-0.994420617148044</v>
       </c>
       <c r="D849" t="n">
-        <v>-0.733755539112951</v>
+        <v>-0.7337143607258462</v>
       </c>
       <c r="E849" t="n">
-        <v>-0.03855109417544019</v>
+        <v>-0.0385510941754402</v>
       </c>
       <c r="F849" t="inlineStr"/>
     </row>
@@ -38369,7 +38413,7 @@
         <v>91.57902623125838</v>
       </c>
       <c r="D850" t="n">
-        <v>-0.887641860450863</v>
+        <v>-0.8862058905423591</v>
       </c>
       <c r="E850" t="n">
         <v>1.582164014868329</v>
@@ -38387,7 +38431,7 @@
         <v>-35.46593763080787</v>
       </c>
       <c r="D851" t="n">
-        <v>-0.3264093943949484</v>
+        <v>-0.3300603112115472</v>
       </c>
       <c r="E851" t="n">
         <v>-0.6420557745962229</v>
@@ -38405,7 +38449,7 @@
         <v>-18.51130811929742</v>
       </c>
       <c r="D852" t="n">
-        <v>-0.3083051212963705</v>
+        <v>-0.3121201312331338</v>
       </c>
       <c r="E852" t="n">
         <v>-0.3452252562020881</v>
@@ -38423,7 +38467,7 @@
         <v>-14.99962816985201</v>
       </c>
       <c r="D853" t="n">
-        <v>-0.3264093943949484</v>
+        <v>-0.3300603112115472</v>
       </c>
       <c r="E853" t="n">
         <v>-0.2837450699720966</v>
@@ -38441,7 +38485,7 @@
         <v>-3.898397461626532</v>
       </c>
       <c r="D854" t="n">
-        <v>-0.5798692177750389</v>
+        <v>-0.5812228309093332</v>
       </c>
       <c r="E854" t="n">
         <v>-0.08939201355771932</v>
@@ -38459,7 +38503,7 @@
         <v>-28.79574102646212</v>
       </c>
       <c r="D855" t="n">
-        <v>-0.561764944676461</v>
+        <v>-0.56328265093092</v>
       </c>
       <c r="E855" t="n">
         <v>-0.5252783531542158</v>
@@ -38477,10 +38521,10 @@
         <v>-0.4200878365476396</v>
       </c>
       <c r="D856" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E856" t="n">
-        <v>-0.02849605305049996</v>
+        <v>-0.02849605305049997</v>
       </c>
       <c r="F856" t="inlineStr"/>
     </row>
@@ -38495,7 +38539,7 @@
         <v>-26.99627210381593</v>
       </c>
       <c r="D857" t="n">
-        <v>-0.6341820370707725</v>
+        <v>-0.635043370844573</v>
       </c>
       <c r="E857" t="n">
         <v>-0.4937744330726487</v>
@@ -38513,7 +38557,7 @@
         <v>-5.12709265271316</v>
       </c>
       <c r="D858" t="n">
-        <v>-0.4983999888314384</v>
+        <v>-0.5004920210064734</v>
       </c>
       <c r="E858" t="n">
         <v>-0.1109032020075183</v>
@@ -38531,7 +38575,7 @@
         <v>46.18761177044384</v>
       </c>
       <c r="D859" t="n">
-        <v>-0.1182102537613027</v>
+        <v>-0.1237482414597943</v>
       </c>
       <c r="E859" t="n">
         <v>0.7874809416758745</v>
@@ -38549,7 +38593,7 @@
         <v>-39.51760920731575</v>
       </c>
       <c r="D860" t="n">
-        <v>0.02662393102732041</v>
+        <v>0.01977319836751201</v>
       </c>
       <c r="E860" t="n">
         <v>-0.7129897795888493</v>
@@ -38567,7 +38611,7 @@
         <v>-20.20913196948418</v>
       </c>
       <c r="D861" t="n">
-        <v>-0.04579316136699114</v>
+        <v>-0.05198752154614115</v>
       </c>
       <c r="E861" t="n">
         <v>-0.3749496411112787</v>
@@ -38585,7 +38629,7 @@
         <v>2.377763834390015</v>
       </c>
       <c r="D862" t="n">
-        <v>-0.4169307598878378</v>
+        <v>-0.4197612111036136</v>
       </c>
       <c r="E862" t="n">
         <v>0.02048689649201316</v>
@@ -38603,7 +38647,7 @@
         <v>85.71447258267058</v>
       </c>
       <c r="D863" t="n">
-        <v>-0.5708170812257499</v>
+        <v>-0.5722527409201267</v>
       </c>
       <c r="E863" t="n">
         <v>1.479491261183047</v>
@@ -38621,7 +38665,7 @@
         <v>15.14505566268473</v>
       </c>
       <c r="D864" t="n">
-        <v>-0.7971204949579737</v>
+        <v>-0.7965049906502928</v>
       </c>
       <c r="E864" t="n">
         <v>0.2440082567971198</v>
@@ -38639,10 +38683,10 @@
         <v>2.625120844798111</v>
       </c>
       <c r="D865" t="n">
-        <v>-1.313092278267443</v>
+        <v>-1.307800120035071</v>
       </c>
       <c r="E865" t="n">
-        <v>0.02481746057647233</v>
+        <v>0.02481746057647232</v>
       </c>
       <c r="F865" t="inlineStr"/>
     </row>
@@ -38657,7 +38701,7 @@
         <v>-39.90797973695218</v>
       </c>
       <c r="D866" t="n">
-        <v>-0.7880683584086847</v>
+        <v>-0.7875349006610861</v>
       </c>
       <c r="E866" t="n">
         <v>-0.7198241304426447</v>
@@ -38675,7 +38719,7 @@
         <v>-28.26628045762861</v>
       </c>
       <c r="D867" t="n">
-        <v>-1.213518776225265</v>
+        <v>-1.209129130153798</v>
       </c>
       <c r="E867" t="n">
         <v>-0.5160089052426934</v>
@@ -38693,7 +38737,7 @@
         <v>5.895550887912939</v>
       </c>
       <c r="D868" t="n">
-        <v>-0.4712435791835716</v>
+        <v>-0.4735817510388535</v>
       </c>
       <c r="E868" t="n">
         <v>0.08207400188930246</v>
@@ -38711,7 +38755,7 @@
         <v>-7.867708593724531</v>
       </c>
       <c r="D869" t="n">
-        <v>-1.050580318338064</v>
+        <v>-1.047667510348079</v>
       </c>
       <c r="E869" t="n">
         <v>-0.1588841059805219</v>
@@ -38729,10 +38773,10 @@
         <v>-31.43729148277255</v>
       </c>
       <c r="D870" t="n">
-        <v>-1.285935868619576</v>
+        <v>-1.280889850067451</v>
       </c>
       <c r="E870" t="n">
-        <v>-0.571524883683153</v>
+        <v>-0.5715248836831531</v>
       </c>
       <c r="F870" t="inlineStr"/>
     </row>
@@ -38747,7 +38791,7 @@
         <v>108.031214436677</v>
       </c>
       <c r="D871" t="n">
-        <v>-1.132049547281665</v>
+        <v>-1.128398320250938</v>
       </c>
       <c r="E871" t="n">
         <v>1.870198120857898</v>
@@ -38765,7 +38809,7 @@
         <v>25.62890026127701</v>
       </c>
       <c r="D872" t="n">
-        <v>-0.869537587352285</v>
+        <v>-0.8682657105639457</v>
       </c>
       <c r="E872" t="n">
         <v>0.4275525226774813</v>
@@ -38783,7 +38827,7 @@
         <v>-34.18605533836868</v>
       </c>
       <c r="D873" t="n">
-        <v>-0.3264093943949484</v>
+        <v>-0.3300603112115472</v>
       </c>
       <c r="E873" t="n">
         <v>-0.6196484359934962</v>
@@ -38801,7 +38845,7 @@
         <v>-8.270197881645608</v>
       </c>
       <c r="D874" t="n">
-        <v>-0.7065991294650842</v>
+        <v>-0.7068040907582263</v>
       </c>
       <c r="E874" t="n">
         <v>-0.1659306240952698</v>
@@ -38819,7 +38863,7 @@
         <v>-5.857576391795737</v>
       </c>
       <c r="D875" t="n">
-        <v>-1.394561507211044</v>
+        <v>-1.388530929937931</v>
       </c>
       <c r="E875" t="n">
         <v>-0.1236920315601288</v>
@@ -38837,7 +38881,7 @@
         <v>-34.81274296592471</v>
       </c>
       <c r="D876" t="n">
-        <v>-0.8061726315072624</v>
+        <v>-0.8054750806394992</v>
       </c>
       <c r="E876" t="n">
         <v>-0.6306200713944559</v>
@@ -38855,7 +38899,7 @@
         <v>-19.14662793800497</v>
       </c>
       <c r="D877" t="n">
-        <v>-0.1996794827049032</v>
+        <v>-0.2044790513626542</v>
       </c>
       <c r="E877" t="n">
         <v>-0.3563480183364656</v>
@@ -38873,7 +38917,7 @@
         <v>13.03535893395077</v>
       </c>
       <c r="D878" t="n">
-        <v>-0.2902008481977927</v>
+        <v>-0.2941799512547206</v>
       </c>
       <c r="E878" t="n">
         <v>0.2070730720312497</v>
@@ -38891,7 +38935,7 @@
         <v>-16.08322901807807</v>
       </c>
       <c r="D879" t="n">
-        <v>0.6512213529282576</v>
+        <v>0.6387094076227705</v>
       </c>
       <c r="E879" t="n">
         <v>-0.3027160419590045</v>
@@ -38909,7 +38953,7 @@
         <v>-9.008019858697716</v>
       </c>
       <c r="D880" t="n">
-        <v>1.565487144406441</v>
+        <v>1.544688496532642</v>
       </c>
       <c r="E880" t="n">
         <v>-0.1788479266988023</v>
@@ -38927,7 +38971,7 @@
         <v>6.17439598300166</v>
       </c>
       <c r="D881" t="n">
-        <v>2.588378574476092</v>
+        <v>2.558308665312993</v>
       </c>
       <c r="E881" t="n">
         <v>0.08695583868028954</v>
@@ -38945,7 +38989,7 @@
         <v>-27.42478418934487</v>
       </c>
       <c r="D882" s="4" t="n">
-        <v>2.226293112504534</v>
+        <v>2.199505065744727</v>
       </c>
       <c r="E882" s="4" t="n">
         <v>-0.5012765412372272</v>
@@ -38967,7 +39011,7 @@
         <v>18.38725410502357</v>
       </c>
       <c r="D883" s="4" t="n">
-        <v>2.479752935884624</v>
+        <v>2.450667585442513</v>
       </c>
       <c r="E883" s="4" t="n">
         <v>0.3007705377849015</v>
@@ -38989,7 +39033,7 @@
         <v>-13.69221135367408</v>
       </c>
       <c r="D884" s="4" t="n">
-        <v>2.914255490250494</v>
+        <v>2.881231904924432</v>
       </c>
       <c r="E884" s="4" t="n">
         <v>-0.2608556750112785</v>
@@ -39011,7 +39055,7 @@
         <v>-4.609632975291296</v>
       </c>
       <c r="D885" s="4" t="n">
-        <v>3.194871723278451</v>
+        <v>3.159304694589838</v>
       </c>
       <c r="E885" s="4" t="n">
         <v>-0.1018438578211463</v>
@@ -39033,7 +39077,7 @@
         <v>-13.69251083994343</v>
       </c>
       <c r="D886" s="4" t="n">
-        <v>2.407335843490312</v>
+        <v>2.37890686552886</v>
       </c>
       <c r="E886" s="4" t="n">
         <v>-0.2608609182201923</v>
@@ -39055,7 +39099,7 @@
         <v>9.446944328170783</v>
       </c>
       <c r="D887" s="4" t="n">
-        <v>2.316814477997423</v>
+        <v>2.289205965636793</v>
       </c>
       <c r="E887" s="4" t="n">
         <v>0.1442494658342738</v>
@@ -39077,7 +39121,7 @@
         <v>-3.984179106316655</v>
       </c>
       <c r="D888" s="4" t="n">
-        <v>2.0905110642652</v>
+        <v>2.064953715906627</v>
       </c>
       <c r="E888" s="4" t="n">
         <v>-0.09089382225514821</v>
@@ -39099,7 +39143,7 @@
         <v>-15.53768826635286</v>
       </c>
       <c r="D889" s="4" t="n">
-        <v>1.674112782997909</v>
+        <v>1.652329576403122</v>
       </c>
       <c r="E889" s="4" t="n">
         <v>-0.2931650727662076</v>
@@ -39121,7 +39165,7 @@
         <v>26.30604976192188</v>
       </c>
       <c r="D890" s="4" t="n">
-        <v>1.384444413420662</v>
+        <v>1.365286696748509</v>
       </c>
       <c r="E890" s="4" t="n">
         <v>0.4394076114112274</v>
@@ -39143,7 +39187,7 @@
         <v>24.72890163314023</v>
       </c>
       <c r="D891" s="4" t="n">
-        <v>1.23055809208275</v>
+        <v>1.212795166931996</v>
       </c>
       <c r="E891" s="4" t="n">
         <v>0.4117959377776174</v>
@@ -39165,7 +39209,7 @@
         <v>-50.39621920947107</v>
       </c>
       <c r="D892" s="4" t="n">
-        <v>0.4430222122946119</v>
+        <v>0.4323973378710177</v>
       </c>
       <c r="E892" s="4" t="n">
         <v>-0.9034453388893434</v>
@@ -39187,7 +39231,7 @@
         <v>-5.031029573193932</v>
       </c>
       <c r="D893" s="4" t="n">
-        <v>0.02662393102732041</v>
+        <v>0.01977319836751201</v>
       </c>
       <c r="E893" s="4" t="n">
         <v>-0.1092213927015189</v>
@@ -39209,7 +39253,7 @@
         <v>26.6767403240526</v>
       </c>
       <c r="D894" t="n">
-        <v>-0.8333290411551293</v>
+        <v>-0.8323853506071192</v>
       </c>
       <c r="E894" t="n">
         <v>0.4458974183189143</v>
@@ -39227,10 +39271,10 @@
         <v>-0.2763778247439353</v>
       </c>
       <c r="D895" t="n">
-        <v>-0.6432341736200615</v>
+        <v>-0.6440134608337796</v>
       </c>
       <c r="E895" t="n">
-        <v>-0.0259800725465815</v>
+        <v>-0.02598007254658151</v>
       </c>
       <c r="F895" t="inlineStr"/>
     </row>
@@ -39245,7 +39289,7 @@
         <v>42.23402647319213</v>
       </c>
       <c r="D896" t="n">
-        <v>-0.4893478522821495</v>
+        <v>-0.4915219310172668</v>
       </c>
       <c r="E896" t="n">
         <v>0.7182641668414885</v>
@@ -39263,7 +39307,7 @@
         <v>-51.72125858731543</v>
       </c>
       <c r="D897" t="n">
-        <v>-0.1634709365077474</v>
+        <v>-0.1685986914058275</v>
       </c>
       <c r="E897" t="n">
         <v>-0.926643258086054</v>
@@ -39281,7 +39325,7 @@
         <v>-19.73291128571562</v>
       </c>
       <c r="D898" t="n">
-        <v>-0.4621914426342826</v>
+        <v>-0.4646116610496468</v>
       </c>
       <c r="E898" t="n">
         <v>-0.366612282141738</v>
@@ -39299,7 +39343,7 @@
         <v>-11.41037044788615</v>
       </c>
       <c r="D899" t="n">
-        <v>-0.07294957101485799</v>
+        <v>-0.07889779151376111</v>
       </c>
       <c r="E899" t="n">
         <v>-0.220906703050662</v>
@@ -39317,7 +39361,7 @@
         <v>-77.28518885883796</v>
       </c>
       <c r="D900" t="n">
-        <v>0.2710316178581219</v>
+        <v>0.2619656280760914</v>
       </c>
       <c r="E900" t="n">
         <v>-1.374199759956883</v>
@@ -39335,7 +39379,7 @@
         <v>96.18196055100856</v>
       </c>
       <c r="D901" t="n">
-        <v>0.1895623889145214</v>
+        <v>0.1812348181732316</v>
       </c>
       <c r="E901" t="n">
         <v>1.662749165923268</v>
@@ -39351,7 +39395,7 @@
       </c>
       <c r="C902" t="inlineStr"/>
       <c r="D902" t="n">
-        <v>-0.08200170756414694</v>
+        <v>-0.08786788150296776</v>
       </c>
       <c r="E902" t="inlineStr"/>
       <c r="F902" t="inlineStr"/>
@@ -39365,7 +39409,7 @@
       </c>
       <c r="C903" t="inlineStr"/>
       <c r="D903" t="n">
-        <v>0.741742718421147</v>
+        <v>0.7284103075148369</v>
       </c>
       <c r="E903" t="inlineStr"/>
       <c r="F903" t="inlineStr"/>
@@ -39379,7 +39423,7 @@
       </c>
       <c r="C904" t="inlineStr"/>
       <c r="D904" t="n">
-        <v>1.112880316941994</v>
+        <v>1.09618399707231</v>
       </c>
       <c r="E904" t="inlineStr"/>
       <c r="F904" t="inlineStr"/>
@@ -39393,7 +39437,7 @@
       </c>
       <c r="C905" t="inlineStr"/>
       <c r="D905" t="n">
-        <v>0.5969085336325239</v>
+        <v>0.5848888676875307</v>
       </c>
       <c r="E905" t="inlineStr"/>
       <c r="F905" t="inlineStr"/>
@@ -39407,7 +39451,7 @@
       </c>
       <c r="C906" t="inlineStr"/>
       <c r="D906" t="n">
-        <v>0.1624059792666546</v>
+        <v>0.1543245482056117</v>
       </c>
       <c r="E906" t="inlineStr"/>
       <c r="F906" t="inlineStr"/>
@@ -39421,7 +39465,7 @@
       </c>
       <c r="C907" t="inlineStr"/>
       <c r="D907" t="n">
-        <v>0.2981880275059887</v>
+        <v>0.2888758980437114</v>
       </c>
       <c r="E907" t="inlineStr"/>
       <c r="F907" t="inlineStr"/>
@@ -39435,7 +39479,7 @@
       </c>
       <c r="C908" t="inlineStr"/>
       <c r="D908" t="n">
-        <v>0.4430222122946119</v>
+        <v>0.4323973378710177</v>
       </c>
       <c r="E908" t="inlineStr"/>
       <c r="F908" t="inlineStr"/>
@@ -39449,7 +39493,7 @@
       </c>
       <c r="C909" t="inlineStr"/>
       <c r="D909" t="n">
-        <v>0.2710316178581219</v>
+        <v>0.2619656280760914</v>
       </c>
       <c r="E909" t="inlineStr"/>
       <c r="F909" t="inlineStr"/>
@@ -39463,7 +39507,7 @@
       </c>
       <c r="C910" t="inlineStr"/>
       <c r="D910" t="n">
-        <v>-0.1815752096063253</v>
+        <v>-0.1865388713842409</v>
       </c>
       <c r="E910" t="inlineStr"/>
       <c r="F910" t="inlineStr"/>
@@ -39477,7 +39521,7 @@
       </c>
       <c r="C911" t="inlineStr"/>
       <c r="D911" t="n">
-        <v>-0.1001059806627248</v>
+        <v>-0.105808061481381</v>
       </c>
       <c r="E911" t="inlineStr"/>
       <c r="F911" t="inlineStr"/>
@@ -39491,7 +39535,7 @@
       </c>
       <c r="C912" t="inlineStr"/>
       <c r="D912" t="n">
-        <v>-0.1996794827049032</v>
+        <v>-0.2044790513626542</v>
       </c>
       <c r="E912" t="inlineStr"/>
       <c r="F912" t="inlineStr"/>
@@ -39505,7 +39549,7 @@
       </c>
       <c r="C913" t="inlineStr"/>
       <c r="D913" t="n">
-        <v>-0.3445136674935264</v>
+        <v>-0.3480004911899605</v>
       </c>
       <c r="E913" t="inlineStr"/>
       <c r="F913" t="inlineStr"/>
@@ -39519,7 +39563,7 @@
       </c>
       <c r="C914" t="inlineStr"/>
       <c r="D914" t="n">
-        <v>-0.04579316136699114</v>
+        <v>-0.05198752154614115</v>
       </c>
       <c r="E914" t="inlineStr"/>
       <c r="F914" t="inlineStr"/>
@@ -39533,7 +39577,7 @@
       </c>
       <c r="C915" t="inlineStr"/>
       <c r="D915" t="n">
-        <v>0.8594204935619033</v>
+        <v>0.8450214773745234</v>
       </c>
       <c r="E915" t="inlineStr"/>
       <c r="F915" t="inlineStr"/>
@@ -39547,7 +39591,7 @@
       </c>
       <c r="C916" t="inlineStr"/>
       <c r="D916" t="n">
-        <v>1.022358951449104</v>
+        <v>1.006483097180243</v>
       </c>
       <c r="E916" t="inlineStr"/>
       <c r="F916" t="inlineStr"/>
@@ -39561,7 +39605,7 @@
       </c>
       <c r="C917" t="inlineStr"/>
       <c r="D917" t="n">
-        <v>1.40254868651924</v>
+        <v>1.383226876726922</v>
       </c>
       <c r="E917" t="inlineStr"/>
       <c r="F917" t="inlineStr"/>
@@ -39575,7 +39619,7 @@
       </c>
       <c r="C918" t="inlineStr"/>
       <c r="D918" t="n">
-        <v>1.864207650532976</v>
+        <v>1.840701466176461</v>
       </c>
       <c r="E918" t="inlineStr"/>
       <c r="F918" t="inlineStr"/>
@@ -39589,10 +39633,38 @@
       </c>
       <c r="C919" t="inlineStr"/>
       <c r="D919" t="n">
-        <v>2.76942130546187</v>
+        <v>2.737710465097126</v>
       </c>
       <c r="E919" t="inlineStr"/>
       <c r="F919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B920" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C920" t="inlineStr"/>
+      <c r="D920" t="n">
+        <v>2.809471185010779</v>
+      </c>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B921" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C921" t="inlineStr"/>
+      <c r="D921" t="n">
+        <v>3.257975684471111</v>
+      </c>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
